--- a/results/flows/flow_analysis_stats.xlsx
+++ b/results/flows/flow_analysis_stats.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6185" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="11109" uniqueCount="671">
   <si>
     <t>stat_name</t>
   </si>
@@ -2016,6 +2016,27 @@
   </si>
   <si>
     <t>Caddo Parish</t>
+  </si>
+  <si>
+    <t>Stephens County</t>
+  </si>
+  <si>
+    <t>Thomas County</t>
+  </si>
+  <si>
+    <t>Hardeman County</t>
+  </si>
+  <si>
+    <t>Schoolcraft County</t>
+  </si>
+  <si>
+    <t>Clinch County</t>
+  </si>
+  <si>
+    <t>Ochiltree County</t>
+  </si>
+  <si>
+    <t>Costilla County</t>
   </si>
 </sst>
 </file>
@@ -2139,7 +2160,7 @@
         <v>84</v>
       </c>
       <c r="B6" s="1">
-        <v>96.615158081054688</v>
+        <v>96.455696105957031</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -2223,7 +2244,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>2718</v>
+        <v>2765</v>
       </c>
       <c r="C12" t="s">
         <v>52</v>
@@ -2265,7 +2286,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
         <v>55</v>
@@ -2279,7 +2300,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
         <v>56</v>
@@ -2349,7 +2370,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>-0.098447464406490326</v>
+        <v>-0.10001588612794876</v>
       </c>
       <c r="C21" t="s">
         <v>61</v>
@@ -2363,7 +2384,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>0.15100958943367004</v>
+        <v>0.15541316568851471</v>
       </c>
       <c r="C22" t="s">
         <v>62</v>
@@ -2391,7 +2412,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>0.68777406215667725</v>
+        <v>0.69774353504180908</v>
       </c>
       <c r="C24" t="s">
         <v>64</v>
@@ -2405,7 +2426,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>-0.17529679834842682</v>
+        <v>-0.17683963477611542</v>
       </c>
       <c r="C25" t="s">
         <v>65</v>
@@ -2419,7 +2440,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>-0.095014661550521851</v>
+        <v>-0.095899395644664765</v>
       </c>
       <c r="C26" t="s">
         <v>66</v>
@@ -2433,7 +2454,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>-0.014865120872855186</v>
+        <v>-0.015296736732125282</v>
       </c>
       <c r="C27" t="s">
         <v>67</v>
@@ -2545,7 +2566,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>-4.0493249893188477</v>
+        <v>-4.3297147750854492</v>
       </c>
       <c r="C35" t="s">
         <v>75</v>
@@ -2559,7 +2580,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1">
-        <v>14.111865043640137</v>
+        <v>14.943398475646973</v>
       </c>
       <c r="C36" t="s">
         <v>76</v>
@@ -2573,7 +2594,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1">
-        <v>-1.7353004217147827</v>
+        <v>-1.7512381076812744</v>
       </c>
       <c r="C37" t="s">
         <v>77</v>
@@ -3524,10 +3545,10 @@
         <v>0.0072731385007500648</v>
       </c>
       <c r="H2" s="1">
-        <v>99.926414489746094</v>
+        <v>99.855331420898438</v>
       </c>
       <c r="I2" s="1">
-        <v>95.215309143066406</v>
+        <v>94.93487548828125</v>
       </c>
       <c r="J2" s="1">
         <v>-0.22885067760944367</v>
@@ -3571,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>99.889625549316406</v>
+        <v>99.819168090820313</v>
       </c>
       <c r="I3" s="1">
         <v>100</v>
@@ -3618,10 +3639,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>99.4481201171875</v>
+        <v>99.385169982910156</v>
       </c>
       <c r="I4" s="1">
-        <v>99.779167175292969</v>
+        <v>99.746742248535156</v>
       </c>
       <c r="J4" s="1">
         <v>-0.40128910541534424</v>
@@ -3665,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>99.227371215820313</v>
+        <v>99.168174743652344</v>
       </c>
       <c r="I5" s="1">
-        <v>98.454177856445313</v>
+        <v>98.263389587402344</v>
       </c>
       <c r="J5" s="1">
         <v>-0.482362300157547</v>
@@ -3712,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>99.116996765136719</v>
+        <v>99.023506164550781</v>
       </c>
       <c r="I6" s="1">
-        <v>99.705558776855469</v>
+        <v>99.674385070800781</v>
       </c>
       <c r="J6" s="1">
         <v>-0.52002179622650146</v>
@@ -3759,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>97.902870178222656</v>
+        <v>97.793853759765625</v>
       </c>
       <c r="I7" s="1">
-        <v>99.374313354492188</v>
+        <v>99.276412963867188</v>
       </c>
       <c r="J7" s="1">
         <v>-0.36776641011238098</v>
@@ -3806,10 +3827,10 @@
         <v>1.3394068218985922e-06</v>
       </c>
       <c r="H8" s="1">
-        <v>97.019866943359375</v>
+        <v>96.853523254394531</v>
       </c>
       <c r="I8" s="1">
-        <v>97.092384338378906</v>
+        <v>96.852386474609375</v>
       </c>
       <c r="J8" s="1">
         <v>-0.1914132684469223</v>
@@ -3836,7 +3857,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3891,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="1">
-        <v>99.889625549316406</v>
+        <v>99.819168090820313</v>
       </c>
       <c r="I2" s="1">
         <v>100</v>
@@ -3899,3424 +3920,3714 @@
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>20017</v>
+        <v>29033</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="D3" s="1">
-        <v>0.42066857218742371</v>
+        <v>0.58515948057174683</v>
       </c>
       <c r="E3" s="1">
-        <v>0.0064287125132977962</v>
+        <v>0.007855856791138649</v>
       </c>
       <c r="F3" s="1">
-        <v>65.435897827148438</v>
+        <v>74.487037658691406</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>99.742454528808594</v>
+        <v>99.891502380371094</v>
       </c>
       <c r="I3" s="1">
-        <v>99.96319580078125</v>
+        <v>99.963821411132813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>12065</v>
+        <v>20017</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D4" s="1">
-        <v>0.31172969937324524</v>
+        <v>0.42066857218742371</v>
       </c>
       <c r="E4" s="1">
-        <v>0.0049780327826738358</v>
+        <v>0.0064287125132977962</v>
       </c>
       <c r="F4" s="1">
-        <v>62.621063232421875</v>
+        <v>65.435897827148438</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>99.374542236328125</v>
+        <v>99.67449951171875</v>
       </c>
       <c r="I4" s="1">
-        <v>99.9263916015625</v>
+        <v>99.927642822265625</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>13141</v>
+        <v>12065</v>
       </c>
       <c r="B5" t="s">
-        <v>205</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D5" s="1">
-        <v>0.36096420884132385</v>
+        <v>0.31172969937324524</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0061808452010154724</v>
+        <v>0.0049780327826738358</v>
       </c>
       <c r="F5" s="1">
-        <v>58.400459289550781</v>
+        <v>62.621063232421875</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>99.632080078125</v>
+        <v>99.312835693359375</v>
       </c>
       <c r="I5" s="1">
-        <v>99.88958740234375</v>
+        <v>99.891464233398438</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>5129</v>
+        <v>13141</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C6" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D6" s="1">
-        <v>0.44076985120773316</v>
+        <v>0.36096420884132385</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0079335533082485199</v>
+        <v>0.0061808452010154724</v>
       </c>
       <c r="F6" s="1">
-        <v>55.557685852050781</v>
+        <v>58.400459289550781</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>99.8160400390625</v>
+        <v>99.566001892089844</v>
       </c>
       <c r="I6" s="1">
-        <v>99.852775573730469</v>
+        <v>99.85528564453125</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>46077</v>
+        <v>5129</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D7" s="1">
-        <v>0.49427169561386108</v>
+        <v>0.44076985120773316</v>
       </c>
       <c r="E7" s="1">
-        <v>0.0089177517220377922</v>
+        <v>0.0079335533082485199</v>
       </c>
       <c r="F7" s="1">
-        <v>55.425594329833984</v>
+        <v>55.557685852050781</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>99.852836608886719</v>
+        <v>99.746833801269531</v>
       </c>
       <c r="I7" s="1">
-        <v>99.815971374511719</v>
+        <v>99.819099426269531</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>35033</v>
+        <v>46077</v>
       </c>
       <c r="B8" t="s">
-        <v>206</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D8" s="1">
-        <v>0.33095294237136841</v>
+        <v>0.49427169561386108</v>
       </c>
       <c r="E8" s="1">
-        <v>0.0060428320430219174</v>
+        <v>0.0089177517220377922</v>
       </c>
       <c r="F8" s="1">
-        <v>54.767852783203125</v>
+        <v>55.425594329833984</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>99.4481201171875</v>
+        <v>99.783004760742188</v>
       </c>
       <c r="I8" s="1">
-        <v>99.779167175292969</v>
+        <v>99.782920837402344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>51183</v>
+        <v>35033</v>
       </c>
       <c r="B9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>225</v>
       </c>
       <c r="D9" s="1">
-        <v>0.26708310842514038</v>
+        <v>0.33095294237136841</v>
       </c>
       <c r="E9" s="1">
-        <v>0.0055307513102889061</v>
+        <v>0.0060428320430219174</v>
       </c>
       <c r="F9" s="1">
-        <v>48.290565490722656</v>
+        <v>54.767852783203125</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>99.006622314453125</v>
+        <v>99.385169982910156</v>
       </c>
       <c r="I9" s="1">
-        <v>99.742362976074219</v>
+        <v>99.746742248535156</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>40053</v>
+        <v>51183</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>203</v>
       </c>
       <c r="C10" t="s">
-        <v>234</v>
+        <v>142</v>
       </c>
       <c r="D10" s="1">
-        <v>0.27423545718193054</v>
+        <v>0.26708310842514038</v>
       </c>
       <c r="E10" s="1">
-        <v>0.0071755941025912762</v>
+        <v>0.0055307513102889061</v>
       </c>
       <c r="F10" s="1">
-        <v>38.217803955078125</v>
+        <v>48.290565490722656</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>99.116996765136719</v>
+        <v>98.915008544921875</v>
       </c>
       <c r="I10" s="1">
-        <v>99.705558776855469</v>
+        <v>99.710563659667969</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>35037</v>
+        <v>40053</v>
       </c>
       <c r="B11" t="s">
-        <v>206</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D11" s="1">
-        <v>0.2398313581943512</v>
+        <v>0.27423545718193054</v>
       </c>
       <c r="E11" s="1">
-        <v>0.0064301067031919956</v>
+        <v>0.0071755941025912762</v>
       </c>
       <c r="F11" s="1">
-        <v>37.298191070556641</v>
+        <v>38.217803955078125</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>98.712287902832031</v>
+        <v>99.023506164550781</v>
       </c>
       <c r="I11" s="1">
-        <v>99.668754577636719</v>
+        <v>99.674385070800781</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>29041</v>
+        <v>35037</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="C12" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="D12" s="1">
-        <v>0.17621800303459168</v>
+        <v>0.2398313581943512</v>
       </c>
       <c r="E12" s="1">
-        <v>0.0055939778685569763</v>
+        <v>0.0064301067031919956</v>
       </c>
       <c r="F12" s="1">
-        <v>31.501377105712891</v>
+        <v>37.298191070556641</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>97.130241394042969</v>
+        <v>98.625679016113281</v>
       </c>
       <c r="I12" s="1">
-        <v>99.631950378417969</v>
+        <v>99.638206481933594</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>21175</v>
+        <v>31089</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="D13" s="1">
-        <v>0.21382062137126923</v>
+        <v>0.27770248055458069</v>
       </c>
       <c r="E13" s="1">
-        <v>0.0069077359512448311</v>
+        <v>0.0076734600588679314</v>
       </c>
       <c r="F13" s="1">
-        <v>30.953792572021484</v>
+        <v>36.189994812011719</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>98.160415649414063</v>
+        <v>99.059677124023438</v>
       </c>
       <c r="I13" s="1">
-        <v>99.595138549804688</v>
+        <v>99.602027893066406</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>29211</v>
+        <v>20201</v>
       </c>
       <c r="B14" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="D14" s="1">
-        <v>0.23478955030441284</v>
+        <v>0.18078343570232391</v>
       </c>
       <c r="E14" s="1">
-        <v>0.007844138890504837</v>
+        <v>0.0051077855750918388</v>
       </c>
       <c r="F14" s="1">
-        <v>29.931844711303711</v>
+        <v>35.393699645996094</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>98.528327941894531</v>
+        <v>97.142860412597656</v>
       </c>
       <c r="I14" s="1">
-        <v>99.558334350585938</v>
+        <v>99.565849304199219</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>27133</v>
+        <v>29041</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>591</v>
+        <v>276</v>
       </c>
       <c r="D15" s="1">
-        <v>0.12538956105709076</v>
+        <v>0.17621800303459168</v>
       </c>
       <c r="E15" s="1">
-        <v>0.0042370003648102284</v>
+        <v>0.0055939778685569763</v>
       </c>
       <c r="F15" s="1">
-        <v>29.59394645690918</v>
+        <v>31.501377105712891</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>94.849151611328125</v>
+        <v>96.998191833496094</v>
       </c>
       <c r="I15" s="1">
-        <v>99.521530151367188</v>
+        <v>99.529670715332031</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>51119</v>
+        <v>21175</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="C16" t="s">
-        <v>592</v>
+        <v>253</v>
       </c>
       <c r="D16" s="1">
-        <v>0.14640797674655914</v>
+        <v>0.21382062137126923</v>
       </c>
       <c r="E16" s="1">
-        <v>0.0050413557328283787</v>
+        <v>0.0069077359512448311</v>
       </c>
       <c r="F16" s="1">
-        <v>29.041389465332031</v>
+        <v>30.953792572021484</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>96.136863708496094</v>
+        <v>98.047019958496094</v>
       </c>
       <c r="I16" s="1">
-        <v>99.484725952148438</v>
+        <v>99.493484497070313</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>20157</v>
+        <v>29211</v>
       </c>
       <c r="B17" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="D17" s="1">
-        <v>0.23697632551193237</v>
+        <v>0.23478955030441284</v>
       </c>
       <c r="E17" s="1">
-        <v>0.0085003608837723732</v>
+        <v>0.007844138890504837</v>
       </c>
       <c r="F17" s="1">
-        <v>27.878383636474609</v>
+        <v>29.931844711303711</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>98.56512451171875</v>
+        <v>98.444847106933594</v>
       </c>
       <c r="I17" s="1">
-        <v>99.447921752929688</v>
+        <v>99.457305908203125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>17087</v>
+        <v>27133</v>
       </c>
       <c r="B18" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>250</v>
+        <v>591</v>
       </c>
       <c r="D18" s="1">
-        <v>0.22649125754833222</v>
+        <v>0.12538956105709076</v>
       </c>
       <c r="E18" s="1">
-        <v>0.0081684291362762451</v>
+        <v>0.0042370003648102284</v>
       </c>
       <c r="F18" s="1">
-        <v>27.727640151977539</v>
+        <v>29.59394645690918</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>98.344367980957031</v>
+        <v>94.719711303710938</v>
       </c>
       <c r="I18" s="1">
-        <v>99.411117553710938</v>
+        <v>99.421127319335938</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>13283</v>
+        <v>51119</v>
       </c>
       <c r="B19" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C19" t="s">
-        <v>257</v>
+        <v>592</v>
       </c>
       <c r="D19" s="1">
-        <v>0.20553411543369293</v>
+        <v>0.14640797674655914</v>
       </c>
       <c r="E19" s="1">
-        <v>0.0076912203803658485</v>
+        <v>0.0050413557328283787</v>
       </c>
       <c r="F19" s="1">
-        <v>26.723213195800781</v>
+        <v>29.041389465332031</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>97.902870178222656</v>
+        <v>95.98553466796875</v>
       </c>
       <c r="I19" s="1">
-        <v>99.374313354492188</v>
+        <v>99.38494873046875</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>16077</v>
+        <v>20157</v>
       </c>
       <c r="B20" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D20" s="1">
-        <v>0.21255423128604889</v>
+        <v>0.23697632551193237</v>
       </c>
       <c r="E20" s="1">
-        <v>0.0084525709971785545</v>
+        <v>0.0085003608837723732</v>
       </c>
       <c r="F20" s="1">
-        <v>25.146696090698242</v>
+        <v>27.878383636474609</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>98.086830139160156</v>
+        <v>98.481010437011719</v>
       </c>
       <c r="I20" s="1">
-        <v>99.337501525878906</v>
+        <v>99.348770141601563</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>49001</v>
+        <v>17087</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="C21" t="s">
-        <v>335</v>
+        <v>250</v>
       </c>
       <c r="D21" s="1">
-        <v>0.11772468686103821</v>
+        <v>0.22649125754833222</v>
       </c>
       <c r="E21" s="1">
-        <v>0.0048926863819360733</v>
+        <v>0.0081684291362762451</v>
       </c>
       <c r="F21" s="1">
-        <v>24.061359405517578</v>
+        <v>27.727640151977539</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>94.444442749023438</v>
+        <v>98.264015197753906</v>
       </c>
       <c r="I21" s="1">
-        <v>99.300697326660156</v>
+        <v>99.312591552734375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>51115</v>
+        <v>13283</v>
       </c>
       <c r="B22" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C22" t="s">
-        <v>593</v>
+        <v>257</v>
       </c>
       <c r="D22" s="1">
-        <v>0.10642700642347336</v>
+        <v>0.20553411543369293</v>
       </c>
       <c r="E22" s="1">
-        <v>0.0044287010096013546</v>
+        <v>0.0076912203803658485</v>
       </c>
       <c r="F22" s="1">
-        <v>24.03120231628418</v>
+        <v>26.723213195800781</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>93.487861633300781</v>
+        <v>97.793853759765625</v>
       </c>
       <c r="I22" s="1">
-        <v>99.263893127441406</v>
+        <v>99.276412963867188</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>21165</v>
+        <v>16077</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="C23" t="s">
-        <v>594</v>
+        <v>254</v>
       </c>
       <c r="D23" s="1">
-        <v>0.13753107190132141</v>
+        <v>0.21255423128604889</v>
       </c>
       <c r="E23" s="1">
-        <v>0.0057946215383708477</v>
+        <v>0.0084525709971785545</v>
       </c>
       <c r="F23" s="1">
-        <v>23.734262466430664</v>
+        <v>25.146696090698242</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>95.548194885253906</v>
+        <v>97.974685668945313</v>
       </c>
       <c r="I23" s="1">
-        <v>99.227088928222656</v>
+        <v>99.240234375</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>13003</v>
+        <v>48197</v>
       </c>
       <c r="B24" t="s">
-        <v>205</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>595</v>
+        <v>666</v>
       </c>
       <c r="D24" s="1">
-        <v>0.13640832901000977</v>
+        <v>0.17461639642715454</v>
       </c>
       <c r="E24" s="1">
-        <v>0.0058265738189220429</v>
+        <v>0.0069649661891162395</v>
       </c>
       <c r="F24" s="1">
-        <v>23.411413192749024</v>
+        <v>25.070674896240234</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>95.474617004394531</v>
+        <v>96.925857543945313</v>
       </c>
       <c r="I24" s="1">
-        <v>99.190284729003906</v>
+        <v>99.204055786132813</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>29087</v>
+        <v>49001</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C25" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="D25" s="1">
-        <v>0.17484112083911896</v>
+        <v>0.11772468686103821</v>
       </c>
       <c r="E25" s="1">
-        <v>0.0078979777172207832</v>
+        <v>0.0048926863819360733</v>
       </c>
       <c r="F25" s="1">
-        <v>22.137454986572266</v>
+        <v>24.061359405517578</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>97.093452453613281</v>
+        <v>94.321884155273438</v>
       </c>
       <c r="I25" s="1">
-        <v>99.153480529785156</v>
+        <v>99.167869567871094</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <v>5137</v>
+        <v>51115</v>
       </c>
       <c r="B26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C26" t="s">
-        <v>248</v>
+        <v>593</v>
       </c>
       <c r="D26" s="1">
-        <v>0.22867059707641602</v>
+        <v>0.10642700642347336</v>
       </c>
       <c r="E26" s="1">
-        <v>0.010562324896454811</v>
+        <v>0.0044287010096013546</v>
       </c>
       <c r="F26" s="1">
-        <v>21.649646759033203</v>
+        <v>24.03120231628418</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>98.417953491210938</v>
+        <v>93.381553649902344</v>
       </c>
       <c r="I26" s="1">
-        <v>99.116676330566406</v>
+        <v>99.131690979003906</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1">
-        <v>5113</v>
+        <v>21165</v>
       </c>
       <c r="B27" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="C27" t="s">
-        <v>153</v>
+        <v>594</v>
       </c>
       <c r="D27" s="1">
-        <v>0.13597044348716736</v>
+        <v>0.13753107190132141</v>
       </c>
       <c r="E27" s="1">
-        <v>0.0063674021512269974</v>
+        <v>0.0057946215383708477</v>
       </c>
       <c r="F27" s="1">
-        <v>21.354146957397461</v>
+        <v>23.734262466430664</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>95.401031494140625</v>
+        <v>95.406867980957031</v>
       </c>
       <c r="I27" s="1">
-        <v>99.079864501953125</v>
+        <v>99.095512390136719</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1">
-        <v>46117</v>
+        <v>13003</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="C28" t="s">
-        <v>316</v>
+        <v>595</v>
       </c>
       <c r="D28" s="1">
-        <v>0.13144411146640778</v>
+        <v>0.13640832901000977</v>
       </c>
       <c r="E28" s="1">
-        <v>0.0063799619674682617</v>
+        <v>0.0058265738189220429</v>
       </c>
       <c r="F28" s="1">
-        <v>20.60264778137207</v>
+        <v>23.411413192749024</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>94.996322631835938</v>
+        <v>95.334541320800781</v>
       </c>
       <c r="I28" s="1">
-        <v>99.043060302734375</v>
+        <v>99.059333801269531</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1">
-        <v>46101</v>
+        <v>29087</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="D29" s="1">
-        <v>0.1171119436621666</v>
+        <v>0.17484112083911896</v>
       </c>
       <c r="E29" s="1">
-        <v>0.0058435490354895592</v>
+        <v>0.0078979777172207832</v>
       </c>
       <c r="F29" s="1">
-        <v>20.041234970092774</v>
+        <v>22.137454986572266</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>94.370857238769531</v>
+        <v>96.962028503417969</v>
       </c>
       <c r="I29" s="1">
-        <v>99.006256103515625</v>
+        <v>99.023155212402344</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1">
-        <v>46033</v>
+        <v>5137</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>204</v>
       </c>
       <c r="C30" t="s">
-        <v>596</v>
+        <v>248</v>
       </c>
       <c r="D30" s="1">
-        <v>0.085961073637008667</v>
+        <v>0.22867059707641602</v>
       </c>
       <c r="E30" s="1">
-        <v>0.0043409694917500019</v>
+        <v>0.010562324896454811</v>
       </c>
       <c r="F30" s="1">
-        <v>19.802274703979492</v>
+        <v>21.649646759033203</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>91.758644104003906</v>
+        <v>98.336349487304688</v>
       </c>
       <c r="I30" s="1">
-        <v>98.969451904296875</v>
+        <v>98.986976623535156</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1">
-        <v>13101</v>
+        <v>5113</v>
       </c>
       <c r="B31" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C31" t="s">
-        <v>597</v>
+        <v>153</v>
       </c>
       <c r="D31" s="1">
-        <v>0.13697288930416107</v>
+        <v>0.13597044348716736</v>
       </c>
       <c r="E31" s="1">
-        <v>0.0075590717606246472</v>
+        <v>0.0063674021512269974</v>
       </c>
       <c r="F31" s="1">
-        <v>18.120332717895508</v>
+        <v>21.354146957397461</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>95.511405944824219</v>
+        <v>95.26220703125</v>
       </c>
       <c r="I31" s="1">
-        <v>98.932647705078125</v>
+        <v>98.950798034667969</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1">
-        <v>47161</v>
+        <v>46117</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
-        <v>598</v>
+        <v>316</v>
       </c>
       <c r="D32" s="1">
-        <v>0.11461866647005081</v>
+        <v>0.13144411146640778</v>
       </c>
       <c r="E32" s="1">
-        <v>0.0069565954618155956</v>
+        <v>0.0063799619674682617</v>
       </c>
       <c r="F32" s="1">
-        <v>16.476259231567383</v>
+        <v>20.60264778137207</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>94.03973388671875</v>
+        <v>94.8643798828125</v>
       </c>
       <c r="I32" s="1">
-        <v>98.895843505859375</v>
+        <v>98.914619445800781</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1">
-        <v>48095</v>
+        <v>46101</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
-        <v>599</v>
+        <v>322</v>
       </c>
       <c r="D33" s="1">
-        <v>0.069867528975009918</v>
+        <v>0.1171119436621666</v>
       </c>
       <c r="E33" s="1">
-        <v>0.0042412257753312588</v>
+        <v>0.0058435490354895592</v>
       </c>
       <c r="F33" s="1">
-        <v>16.473428726196289</v>
+        <v>20.041234970092774</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>89.845474243164063</v>
+        <v>94.249549865722656</v>
       </c>
       <c r="I33" s="1">
-        <v>98.859039306640625</v>
+        <v>98.878440856933594</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1">
-        <v>37137</v>
+        <v>46033</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="D34" s="1">
-        <v>0.14306840300559998</v>
+        <v>0.085961073637008667</v>
       </c>
       <c r="E34" s="1">
-        <v>0.0091681871563196182</v>
+        <v>0.0043409694917500019</v>
       </c>
       <c r="F34" s="1">
-        <v>15.604873657226563</v>
+        <v>19.802274703979492</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>95.916114807128906</v>
+        <v>91.681732177734375</v>
       </c>
       <c r="I34" s="1">
-        <v>98.822227478027344</v>
+        <v>98.842254638671875</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1">
-        <v>30077</v>
+        <v>20193</v>
       </c>
       <c r="B35" t="s">
-        <v>207</v>
+        <v>163</v>
       </c>
       <c r="C35" t="s">
-        <v>440</v>
+        <v>665</v>
       </c>
       <c r="D35" s="1">
-        <v>0.093579158186912537</v>
+        <v>0.21395087242126465</v>
       </c>
       <c r="E35" s="1">
-        <v>0.0061001232825219631</v>
+        <v>0.011292941868305206</v>
       </c>
       <c r="F35" s="1">
-        <v>15.340535163879395</v>
+        <v>18.945539474487305</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>92.457687377929688</v>
+        <v>98.083183288574219</v>
       </c>
       <c r="I35" s="1">
-        <v>98.785423278808594</v>
+        <v>98.806076049804688</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1">
-        <v>13309</v>
+        <v>13101</v>
       </c>
       <c r="B36" t="s">
         <v>205</v>
       </c>
       <c r="C36" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D36" s="1">
-        <v>0.10337970405817032</v>
+        <v>0.13697288930416107</v>
       </c>
       <c r="E36" s="1">
-        <v>0.0072273816913366318</v>
+        <v>0.0075590717606246472</v>
       </c>
       <c r="F36" s="1">
-        <v>14.30389404296875</v>
+        <v>18.120332717895508</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>93.414276123046875</v>
+        <v>95.370704650878906</v>
       </c>
       <c r="I36" s="1">
-        <v>98.748619079589844</v>
+        <v>98.7698974609375</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1">
-        <v>41063</v>
+        <v>47161</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="D37" s="1">
-        <v>0.13429366052150726</v>
+        <v>0.11461866647005081</v>
       </c>
       <c r="E37" s="1">
-        <v>0.0094610955566167832</v>
+        <v>0.0069565954618155956</v>
       </c>
       <c r="F37" s="1">
-        <v>14.194303512573242</v>
+        <v>16.476259231567383</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>95.217071533203125</v>
+        <v>93.924049377441406</v>
       </c>
       <c r="I37" s="1">
-        <v>98.711814880371094</v>
+        <v>98.733718872070313</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1">
-        <v>48011</v>
+        <v>48095</v>
       </c>
       <c r="B38" t="s">
         <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D38" s="1">
-        <v>0.057685989886522293</v>
+        <v>0.069867528975009918</v>
       </c>
       <c r="E38" s="1">
-        <v>0.0040838923305273056</v>
+        <v>0.0042412257753312588</v>
       </c>
       <c r="F38" s="1">
-        <v>14.125247955322266</v>
+        <v>16.473428726196289</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>88.337013244628906</v>
+        <v>89.764915466308594</v>
       </c>
       <c r="I38" s="1">
-        <v>98.675010681152344</v>
+        <v>98.697540283203125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1">
-        <v>19063</v>
+        <v>37137</v>
       </c>
       <c r="B39" t="s">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="D39" s="1">
-        <v>0.088672488927841187</v>
+        <v>0.14306840300559998</v>
       </c>
       <c r="E39" s="1">
-        <v>0.0062795281410217285</v>
+        <v>0.0091681871563196182</v>
       </c>
       <c r="F39" s="1">
-        <v>14.120883941650391</v>
+        <v>15.604873657226563</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>92.052978515625</v>
+        <v>95.768531799316406</v>
       </c>
       <c r="I39" s="1">
-        <v>98.638206481933594</v>
+        <v>98.661361694335938</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1">
-        <v>40127</v>
+        <v>30077</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>207</v>
       </c>
       <c r="C40" t="s">
-        <v>605</v>
+        <v>440</v>
       </c>
       <c r="D40" s="1">
-        <v>0.10032633692026138</v>
+        <v>0.093579158186912537</v>
       </c>
       <c r="E40" s="1">
-        <v>0.0071575003676116467</v>
+        <v>0.0061001232825219631</v>
       </c>
       <c r="F40" s="1">
-        <v>14.016951560974121</v>
+        <v>15.340535163879395</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>92.972770690917969</v>
+        <v>92.368896484375</v>
       </c>
       <c r="I40" s="1">
-        <v>98.601402282714844</v>
+        <v>98.62518310546875</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1">
-        <v>26003</v>
+        <v>13309</v>
       </c>
       <c r="B41" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C41" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D41" s="1">
-        <v>0.073049724102020264</v>
+        <v>0.10337970405817032</v>
       </c>
       <c r="E41" s="1">
-        <v>0.0054310844279825688</v>
+        <v>0.0072273816913366318</v>
       </c>
       <c r="F41" s="1">
-        <v>13.450302124023438</v>
+        <v>14.30389404296875</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>90.139808654785156</v>
+        <v>93.309219360351563</v>
       </c>
       <c r="I41" s="1">
-        <v>98.564590454101563</v>
+        <v>98.589004516601563</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1">
-        <v>46025</v>
+        <v>41063</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>602</v>
       </c>
       <c r="D42" s="1">
-        <v>0.23947767913341522</v>
+        <v>0.13429366052150726</v>
       </c>
       <c r="E42" s="1">
-        <v>0.019847434014081955</v>
+        <v>0.0094610955566167832</v>
       </c>
       <c r="F42" s="1">
-        <v>12.065926551818848</v>
+        <v>14.194303512573242</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>98.675498962402344</v>
+        <v>95.081375122070313</v>
       </c>
       <c r="I42" s="1">
-        <v>98.527786254882813</v>
+        <v>98.552818298339844</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <v>51097</v>
+        <v>48011</v>
       </c>
       <c r="B43" t="s">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="D43" s="1">
-        <v>0.057427786290645599</v>
+        <v>0.057685989886522293</v>
       </c>
       <c r="E43" s="1">
-        <v>0.004794703796505928</v>
+        <v>0.0040838923305273056</v>
       </c>
       <c r="F43" s="1">
-        <v>11.977337837219238</v>
+        <v>14.125247955322266</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>88.300224304199219</v>
+        <v>88.282096862792969</v>
       </c>
       <c r="I43" s="1">
-        <v>98.490982055664063</v>
+        <v>98.516639709472656</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <v>29149</v>
+        <v>19063</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="C44" t="s">
-        <v>231</v>
+        <v>604</v>
       </c>
       <c r="D44" s="1">
-        <v>0.29371407628059387</v>
+        <v>0.088672488927841187</v>
       </c>
       <c r="E44" s="1">
-        <v>0.02547084353864193</v>
+        <v>0.0062795281410217285</v>
       </c>
       <c r="F44" s="1">
-        <v>11.531383514404297</v>
+        <v>14.120883941650391</v>
       </c>
       <c r="G44" s="1">
         <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>99.227371215820313</v>
+        <v>91.9710693359375</v>
       </c>
       <c r="I44" s="1">
-        <v>98.454177856445313</v>
+        <v>98.480461120605469</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <v>47137</v>
+        <v>40127</v>
       </c>
       <c r="B45" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C45" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D45" s="1">
-        <v>0.11118036508560181</v>
+        <v>0.10032633692026138</v>
       </c>
       <c r="E45" s="1">
-        <v>0.0096457488834857941</v>
+        <v>0.0071575003676116467</v>
       </c>
       <c r="F45" s="1">
-        <v>11.526358604431152</v>
+        <v>14.016951560974121</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>93.745399475097656</v>
+        <v>92.875228881835938</v>
       </c>
       <c r="I45" s="1">
-        <v>98.417373657226563</v>
+        <v>98.444282531738281</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1">
-        <v>31039</v>
+        <v>26003</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>324</v>
+        <v>606</v>
       </c>
       <c r="D46" s="1">
-        <v>0.042283102869987488</v>
+        <v>0.073049724102020264</v>
       </c>
       <c r="E46" s="1">
-        <v>0.0039331247098743916</v>
+        <v>0.0054310844279825688</v>
       </c>
       <c r="F46" s="1">
-        <v>10.750511169433594</v>
+        <v>13.450302124023438</v>
       </c>
       <c r="G46" s="1">
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>86.313468933105469</v>
+        <v>90.054252624511719</v>
       </c>
       <c r="I46" s="1">
-        <v>98.380569458007813</v>
+        <v>98.408103942871094</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1">
-        <v>4013</v>
+        <v>46025</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D47" s="1">
-        <v>0.25536218285560608</v>
+        <v>0.23947767913341522</v>
       </c>
       <c r="E47" s="1">
-        <v>0.023844193667173386</v>
+        <v>0.019847434014081955</v>
       </c>
       <c r="F47" s="1">
-        <v>10.709616661071777</v>
+        <v>12.065926551818848</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>98.896247863769531</v>
+        <v>98.589508056640625</v>
       </c>
       <c r="I47" s="1">
-        <v>98.343765258789063</v>
+        <v>98.371925354003906</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1">
-        <v>41037</v>
+        <v>51097</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="C48" t="s">
-        <v>528</v>
+        <v>607</v>
       </c>
       <c r="D48" s="1">
-        <v>0.067388497292995453</v>
+        <v>0.057427786290645599</v>
       </c>
       <c r="E48" s="1">
-        <v>0.0064557897858321667</v>
+        <v>0.004794703796505928</v>
       </c>
       <c r="F48" s="1">
-        <v>10.438459396362305</v>
+        <v>11.977337837219238</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>89.587928771972656</v>
+        <v>88.245933532714844</v>
       </c>
       <c r="I48" s="1">
-        <v>98.306953430175781</v>
+        <v>98.335746765136719</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1">
-        <v>30095</v>
+        <v>26153</v>
       </c>
       <c r="B49" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>609</v>
+        <v>667</v>
       </c>
       <c r="D49" s="1">
-        <v>0.087329946458339691</v>
+        <v>0.077755890786647797</v>
       </c>
       <c r="E49" s="1">
-        <v>0.0084611475467681885</v>
+        <v>0.0066549861803650856</v>
       </c>
       <c r="F49" s="1">
-        <v>10.3212890625</v>
+        <v>11.683855056762695</v>
       </c>
       <c r="G49" s="1">
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>91.832229614257813</v>
+        <v>91.030738830566406</v>
       </c>
       <c r="I49" s="1">
-        <v>98.270149230957031</v>
+        <v>98.299568176269531</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1">
-        <v>12071</v>
+        <v>29149</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C50" t="s">
-        <v>143</v>
+        <v>231</v>
       </c>
       <c r="D50" s="1">
-        <v>0.2340986579656601</v>
+        <v>0.29371407628059387</v>
       </c>
       <c r="E50" s="1">
-        <v>0.024382967501878739</v>
+        <v>0.02547084353864193</v>
       </c>
       <c r="F50" s="1">
-        <v>9.6009092330932617</v>
+        <v>11.531383514404297</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>98.491539001464844</v>
+        <v>99.168174743652344</v>
       </c>
       <c r="I50" s="1">
-        <v>98.233345031738281</v>
+        <v>98.263389587402344</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1">
-        <v>48059</v>
+        <v>47137</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="C51" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D51" s="1">
-        <v>0.0556807741522789</v>
+        <v>0.11118036508560181</v>
       </c>
       <c r="E51" s="1">
-        <v>0.0058147888630628586</v>
+        <v>0.0096457488834857941</v>
       </c>
       <c r="F51" s="1">
-        <v>9.5757169723510742</v>
+        <v>11.526358604431152</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>88.005889892578125</v>
+        <v>93.634719848632813</v>
       </c>
       <c r="I51" s="1">
-        <v>98.196540832519531</v>
+        <v>98.227203369140625</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1">
-        <v>27081</v>
+        <v>31039</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C52" t="s">
-        <v>123</v>
+        <v>324</v>
       </c>
       <c r="D52" s="1">
-        <v>0.055978231132030487</v>
+        <v>0.042283102869987488</v>
       </c>
       <c r="E52" s="1">
-        <v>0.0059118722565472126</v>
+        <v>0.0039331247098743916</v>
       </c>
       <c r="F52" s="1">
-        <v>9.4687824249267578</v>
+        <v>10.750511169433594</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>88.042678833007813</v>
+        <v>86.220611572265625</v>
       </c>
       <c r="I52" s="1">
-        <v>98.159736633300781</v>
+        <v>98.191024780273438</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1">
-        <v>21221</v>
+        <v>4013</v>
       </c>
       <c r="B53" t="s">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="C53" t="s">
-        <v>611</v>
+        <v>138</v>
       </c>
       <c r="D53" s="1">
-        <v>0.10154621303081512</v>
+        <v>0.25536218285560608</v>
       </c>
       <c r="E53" s="1">
-        <v>0.010782086290419102</v>
+        <v>0.023844193667173386</v>
       </c>
       <c r="F53" s="1">
-        <v>9.4180488586425781</v>
+        <v>10.709616661071777</v>
       </c>
       <c r="G53" s="1">
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>93.156730651855469</v>
+        <v>98.806510925292969</v>
       </c>
       <c r="I53" s="1">
-        <v>98.122932434082031</v>
+        <v>98.15484619140625</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1">
-        <v>40045</v>
+        <v>41037</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s">
-        <v>357</v>
+        <v>528</v>
       </c>
       <c r="D54" s="1">
-        <v>0.063798882067203522</v>
+        <v>0.067388497292995453</v>
       </c>
       <c r="E54" s="1">
-        <v>0.0073135704733431339</v>
+        <v>0.0064557897858321667</v>
       </c>
       <c r="F54" s="1">
-        <v>8.7233562469482422</v>
+        <v>10.438459396362305</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>88.999267578125</v>
+        <v>89.511756896972656</v>
       </c>
       <c r="I54" s="1">
-        <v>98.08612060546875</v>
+        <v>98.118667602539063</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1">
-        <v>27001</v>
+        <v>30095</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="C55" t="s">
-        <v>236</v>
+        <v>609</v>
       </c>
       <c r="D55" s="1">
-        <v>0.27365186810493469</v>
+        <v>0.087329946458339691</v>
       </c>
       <c r="E55" s="1">
-        <v>0.032817408442497254</v>
+        <v>0.0084611475467681885</v>
       </c>
       <c r="F55" s="1">
-        <v>8.3386192321777344</v>
+        <v>10.3212890625</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>99.043411254882813</v>
+        <v>91.754066467285156</v>
       </c>
       <c r="I55" s="1">
-        <v>98.04931640625</v>
+        <v>98.082489013671875</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1">
-        <v>51141</v>
+        <v>12071</v>
       </c>
       <c r="B56" t="s">
-        <v>203</v>
+        <v>129</v>
       </c>
       <c r="C56" t="s">
-        <v>612</v>
+        <v>143</v>
       </c>
       <c r="D56" s="1">
-        <v>0.044223267585039139</v>
+        <v>0.2340986579656601</v>
       </c>
       <c r="E56" s="1">
-        <v>0.0053152749314904213</v>
+        <v>0.024382967501878739</v>
       </c>
       <c r="F56" s="1">
-        <v>8.3200340270996094</v>
+        <v>9.6009092330932617</v>
       </c>
       <c r="G56" s="1">
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>86.607803344726563</v>
+        <v>98.408676147460938</v>
       </c>
       <c r="I56" s="1">
-        <v>98.01251220703125</v>
+        <v>98.046310424804688</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1">
-        <v>20163</v>
+        <v>48059</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="C57" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D57" s="1">
-        <v>0.036097969859838486</v>
+        <v>0.0556807741522789</v>
       </c>
       <c r="E57" s="1">
-        <v>0.0045087593607604504</v>
+        <v>0.0058147888630628586</v>
       </c>
       <c r="F57" s="1">
-        <v>8.0061864852905273</v>
+        <v>9.5757169723510742</v>
       </c>
       <c r="G57" s="1">
-        <v>1.1102230246251565e-15</v>
+        <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>85.467254638671875</v>
+        <v>87.95660400390625</v>
       </c>
       <c r="I57" s="1">
-        <v>97.9757080078125</v>
+        <v>98.0101318359375</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1">
-        <v>29181</v>
+        <v>27081</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="C58" t="s">
-        <v>614</v>
+        <v>123</v>
       </c>
       <c r="D58" s="1">
-        <v>0.056840710341930389</v>
+        <v>0.055978231132030487</v>
       </c>
       <c r="E58" s="1">
-        <v>0.007214017678052187</v>
+        <v>0.0059118722565472126</v>
       </c>
       <c r="F58" s="1">
-        <v>7.8792033195495605</v>
+        <v>9.4687824249267578</v>
       </c>
       <c r="G58" s="1">
-        <v>3.3306690738754696e-15</v>
+        <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>88.189842224121094</v>
+        <v>87.992767333984375</v>
       </c>
       <c r="I58" s="1">
-        <v>97.93890380859375</v>
+        <v>97.973953247070313</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1">
-        <v>49049</v>
+        <v>21221</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="C59" t="s">
-        <v>158</v>
+        <v>611</v>
       </c>
       <c r="D59" s="1">
-        <v>0.13567611575126648</v>
+        <v>0.10154621303081512</v>
       </c>
       <c r="E59" s="1">
-        <v>0.01781315915286541</v>
+        <v>0.010782086290419102</v>
       </c>
       <c r="F59" s="1">
-        <v>7.6166229248046875</v>
+        <v>9.4180488586425781</v>
       </c>
       <c r="G59" s="1">
-        <v>2.5979218776228663e-14</v>
+        <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>95.364234924316406</v>
+        <v>93.056060791015625</v>
       </c>
       <c r="I59" s="1">
-        <v>97.902099609375</v>
+        <v>97.937774658203125</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1">
-        <v>12105</v>
+        <v>40045</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>357</v>
       </c>
       <c r="D60" s="1">
-        <v>0.14454184472560883</v>
+        <v>0.063798882067203522</v>
       </c>
       <c r="E60" s="1">
-        <v>0.019884031265974045</v>
+        <v>0.0073135704733431339</v>
       </c>
       <c r="F60" s="1">
-        <v>7.2692422866821289</v>
+        <v>8.7233562469482422</v>
       </c>
       <c r="G60" s="1">
-        <v>3.6148861681795097e-13</v>
+        <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>95.952903747558594</v>
+        <v>88.933090209960938</v>
       </c>
       <c r="I60" s="1">
-        <v>97.86529541015625</v>
+        <v>97.901588439941406</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1">
-        <v>32017</v>
+        <v>27001</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c r="D61" s="1">
-        <v>0.074501462280750275</v>
+        <v>0.27365186810493469</v>
       </c>
       <c r="E61" s="1">
-        <v>0.010372956283390522</v>
+        <v>0.032817408442497254</v>
       </c>
       <c r="F61" s="1">
-        <v>7.1822786331176758</v>
+        <v>8.3386192321777344</v>
       </c>
       <c r="G61" s="1">
-        <v>6.8567374000849668e-13</v>
+        <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>90.507728576660156</v>
+        <v>98.951171875</v>
       </c>
       <c r="I61" s="1">
-        <v>97.828483581542969</v>
+        <v>97.865409851074219</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1">
-        <v>8055</v>
+        <v>51141</v>
       </c>
       <c r="B62" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C62" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D62" s="1">
-        <v>0.06353113055229187</v>
+        <v>0.044223267585039139</v>
       </c>
       <c r="E62" s="1">
-        <v>0.0090442262589931488</v>
+        <v>0.0053152749314904213</v>
       </c>
       <c r="F62" s="1">
-        <v>7.0244960784912109</v>
+        <v>8.3200340270996094</v>
       </c>
       <c r="G62" s="1">
-        <v>2.1485035972546029e-12</v>
+        <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>88.925682067871094</v>
+        <v>86.546112060546875</v>
       </c>
       <c r="I62" s="1">
-        <v>97.791679382324219</v>
+        <v>97.829231262207031</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1">
-        <v>26013</v>
+        <v>20163</v>
       </c>
       <c r="B63" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="C63" t="s">
-        <v>212</v>
+        <v>613</v>
       </c>
       <c r="D63" s="1">
-        <v>0.68777406215667725</v>
+        <v>0.036097969859838486</v>
       </c>
       <c r="E63" s="1">
-        <v>0.098883107304573059</v>
+        <v>0.0045087593607604504</v>
       </c>
       <c r="F63" s="1">
-        <v>6.9554252624511719</v>
+        <v>8.0061864852905273</v>
       </c>
       <c r="G63" s="1">
-        <v>3.5149660959632456e-12</v>
+        <v>1.1102230246251565e-15</v>
       </c>
       <c r="H63" s="1">
-        <v>100</v>
+        <v>85.388786315917969</v>
       </c>
       <c r="I63" s="1">
-        <v>97.754875183105469</v>
+        <v>97.793052673339844</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1">
-        <v>28019</v>
+        <v>29181</v>
       </c>
       <c r="B64" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>569</v>
+        <v>614</v>
       </c>
       <c r="D64" s="1">
-        <v>0.083308331668376923</v>
+        <v>0.056840710341930389</v>
       </c>
       <c r="E64" s="1">
-        <v>0.012146536260843277</v>
+        <v>0.007214017678052187</v>
       </c>
       <c r="F64" s="1">
-        <v>6.8586082458496094</v>
+        <v>7.8792033195495605</v>
       </c>
       <c r="G64" s="1">
-        <v>6.9535488478322804e-12</v>
+        <v>3.3306690738754696e-15</v>
       </c>
       <c r="H64" s="1">
-        <v>91.501106262207031</v>
+        <v>88.137435913085938</v>
       </c>
       <c r="I64" s="1">
-        <v>97.718070983886719</v>
+        <v>97.756874084472656</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1">
-        <v>5147</v>
+        <v>19003</v>
       </c>
       <c r="B65" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="C65" t="s">
-        <v>616</v>
+        <v>442</v>
       </c>
       <c r="D65" s="1">
-        <v>0.039175957441329956</v>
+        <v>0.042434956878423691</v>
       </c>
       <c r="E65" s="1">
-        <v>0.0057349842973053455</v>
+        <v>0.0054094837978482246</v>
       </c>
       <c r="F65" s="1">
-        <v>6.8310489654541016</v>
+        <v>7.844548225402832</v>
       </c>
       <c r="G65" s="1">
-        <v>8.4297013813738886e-12</v>
+        <v>4.4408920985006262e-15</v>
       </c>
       <c r="H65" s="1">
-        <v>85.908760070800781</v>
+        <v>86.256782531738281</v>
       </c>
       <c r="I65" s="1">
-        <v>97.681266784667969</v>
+        <v>97.720695495605469</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1">
-        <v>48257</v>
+        <v>49049</v>
       </c>
       <c r="B66" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="C66" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="D66" s="1">
-        <v>0.15212938189506531</v>
+        <v>0.13567611575126648</v>
       </c>
       <c r="E66" s="1">
-        <v>0.022296907380223274</v>
+        <v>0.01781315915286541</v>
       </c>
       <c r="F66" s="1">
-        <v>6.8228917121887207</v>
+        <v>7.6166229248046875</v>
       </c>
       <c r="G66" s="1">
-        <v>8.9226404043074581e-12</v>
+        <v>2.5979218776228663e-14</v>
       </c>
       <c r="H66" s="1">
-        <v>96.431198120117188</v>
+        <v>95.226036071777344</v>
       </c>
       <c r="I66" s="1">
-        <v>97.644462585449219</v>
+        <v>97.684516906738281</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1">
-        <v>48019</v>
+        <v>12105</v>
       </c>
       <c r="B67" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="C67" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="D67" s="1">
-        <v>0.23017928004264832</v>
+        <v>0.14454184472560883</v>
       </c>
       <c r="E67" s="1">
-        <v>0.034968111664056778</v>
+        <v>0.019884031265974045</v>
       </c>
       <c r="F67" s="1">
-        <v>6.5825481414794922</v>
+        <v>7.2692422866821289</v>
       </c>
       <c r="G67" s="1">
-        <v>4.6245229867736271e-11</v>
+        <v>3.6148861681795097e-13</v>
       </c>
       <c r="H67" s="1">
-        <v>98.454742431640625</v>
+        <v>95.804702758789063</v>
       </c>
       <c r="I67" s="1">
-        <v>97.607658386230469</v>
+        <v>97.648338317871094</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1">
-        <v>5149</v>
+        <v>32017</v>
       </c>
       <c r="B68" t="s">
-        <v>204</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>617</v>
+        <v>123</v>
       </c>
       <c r="D68" s="1">
-        <v>0.076603502035140991</v>
+        <v>0.074501462280750275</v>
       </c>
       <c r="E68" s="1">
-        <v>0.012356518767774105</v>
+        <v>0.010372956283390522</v>
       </c>
       <c r="F68" s="1">
-        <v>6.1994404792785645</v>
+        <v>7.1822786331176758</v>
       </c>
       <c r="G68" s="1">
-        <v>5.6664251069094007e-10</v>
+        <v>6.8567374000849668e-13</v>
       </c>
       <c r="H68" s="1">
-        <v>90.912437438964844</v>
+        <v>90.415916442871094</v>
       </c>
       <c r="I68" s="1">
-        <v>97.570846557617188</v>
+        <v>97.612159729003906</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1">
-        <v>42101</v>
+        <v>8055</v>
       </c>
       <c r="B69" t="s">
-        <v>132</v>
+        <v>210</v>
       </c>
       <c r="C69" t="s">
-        <v>148</v>
+        <v>615</v>
       </c>
       <c r="D69" s="1">
-        <v>0.18830960988998413</v>
+        <v>0.06353113055229187</v>
       </c>
       <c r="E69" s="1">
-        <v>0.030858449637889862</v>
+        <v>0.0090442262589931488</v>
       </c>
       <c r="F69" s="1">
-        <v>6.1023678779602051</v>
+        <v>7.0244960784912109</v>
       </c>
       <c r="G69" s="1">
-        <v>1.0450849075027691e-09</v>
+        <v>2.1485035972546029e-12</v>
       </c>
       <c r="H69" s="1">
-        <v>97.571746826171875</v>
+        <v>88.860755920410156</v>
       </c>
       <c r="I69" s="1">
-        <v>97.534042358398438</v>
+        <v>97.575973510742188</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1">
-        <v>41013</v>
+        <v>26013</v>
       </c>
       <c r="B70" t="s">
-        <v>102</v>
+        <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>389</v>
+        <v>212</v>
       </c>
       <c r="D70" s="1">
-        <v>0.14907023310661316</v>
+        <v>0.68777406215667725</v>
       </c>
       <c r="E70" s="1">
-        <v>0.025144163519144058</v>
+        <v>0.098883107304573059</v>
       </c>
       <c r="F70" s="1">
-        <v>5.928621768951416</v>
+        <v>6.9554252624511719</v>
       </c>
       <c r="G70" s="1">
-        <v>3.0548783502837296e-09</v>
+        <v>3.5149660959632456e-12</v>
       </c>
       <c r="H70" s="1">
-        <v>96.284034729003906</v>
+        <v>99.963836669921875</v>
       </c>
       <c r="I70" s="1">
-        <v>97.497238159179688</v>
+        <v>97.539794921875</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1">
-        <v>38029</v>
+        <v>28019</v>
       </c>
       <c r="B71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C71" t="s">
-        <v>308</v>
+        <v>569</v>
       </c>
       <c r="D71" s="1">
-        <v>0.11767695844173431</v>
+        <v>0.083308331668376923</v>
       </c>
       <c r="E71" s="1">
-        <v>0.020035386085510254</v>
+        <v>0.012146536260843277</v>
       </c>
       <c r="F71" s="1">
-        <v>5.8734560012817383</v>
+        <v>6.8586082458496094</v>
       </c>
       <c r="G71" s="1">
-        <v>4.2680232681391317e-09</v>
+        <v>6.9535488478322804e-12</v>
       </c>
       <c r="H71" s="1">
-        <v>94.40765380859375</v>
+        <v>91.428573608398438</v>
       </c>
       <c r="I71" s="1">
-        <v>97.460433959960938</v>
+        <v>97.503616333007813</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1">
-        <v>34009</v>
+        <v>5147</v>
       </c>
       <c r="B72" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="C72" t="s">
-        <v>220</v>
+        <v>616</v>
       </c>
       <c r="D72" s="1">
-        <v>0.38681164383888245</v>
+        <v>0.039175957441329956</v>
       </c>
       <c r="E72" s="1">
-        <v>0.069756634533405304</v>
+        <v>0.0057349842973053455</v>
       </c>
       <c r="F72" s="1">
-        <v>5.5451593399047852</v>
+        <v>6.8310489654541016</v>
       </c>
       <c r="G72" s="1">
-        <v>2.9368660392492529e-08</v>
+        <v>8.4297013813738886e-12</v>
       </c>
       <c r="H72" s="1">
-        <v>99.668876647949219</v>
+        <v>85.822784423828125</v>
       </c>
       <c r="I72" s="1">
-        <v>97.423629760742188</v>
+        <v>97.467437744140625</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1">
-        <v>22021</v>
+        <v>48257</v>
       </c>
       <c r="B73" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="C73" t="s">
-        <v>618</v>
+        <v>185</v>
       </c>
       <c r="D73" s="1">
-        <v>0.046430505812168121</v>
+        <v>0.15212938189506531</v>
       </c>
       <c r="E73" s="1">
-        <v>0.008438323624432087</v>
+        <v>0.022296907380223274</v>
       </c>
       <c r="F73" s="1">
-        <v>5.5023374557495117</v>
+        <v>6.8228917121887207</v>
       </c>
       <c r="G73" s="1">
-        <v>3.7478869785445568e-08</v>
+        <v>8.9226404043074581e-12</v>
       </c>
       <c r="H73" s="1">
-        <v>86.865341186523438</v>
+        <v>96.274864196777344</v>
       </c>
       <c r="I73" s="1">
-        <v>97.386825561523438</v>
+        <v>97.431259155273438</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1">
-        <v>12115</v>
+        <v>48019</v>
       </c>
       <c r="B74" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="C74" t="s">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="D74" s="1">
-        <v>0.21304696798324585</v>
+        <v>0.23017928004264832</v>
       </c>
       <c r="E74" s="1">
-        <v>0.039894048124551773</v>
+        <v>0.034968111664056778</v>
       </c>
       <c r="F74" s="1">
-        <v>5.3403196334838867</v>
+        <v>6.5825481414794922</v>
       </c>
       <c r="G74" s="1">
-        <v>9.2782848071237822e-08</v>
+        <v>4.6245229867736271e-11</v>
       </c>
       <c r="H74" s="1">
-        <v>98.123619079589844</v>
+        <v>98.372512817382813</v>
       </c>
       <c r="I74" s="1">
-        <v>97.350021362304688</v>
+        <v>97.39508056640625</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1">
-        <v>12021</v>
+        <v>5149</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="C75" t="s">
-        <v>141</v>
+        <v>617</v>
       </c>
       <c r="D75" s="1">
-        <v>0.21074710786342621</v>
+        <v>0.076603502035140991</v>
       </c>
       <c r="E75" s="1">
-        <v>0.040968708693981171</v>
+        <v>0.012356518767774105</v>
       </c>
       <c r="F75" s="1">
-        <v>5.144099235534668</v>
+        <v>6.1994404792785645</v>
       </c>
       <c r="G75" s="1">
-        <v>2.6880741188506363e-07</v>
+        <v>5.6664251069094007e-10</v>
       </c>
       <c r="H75" s="1">
-        <v>97.976455688476563</v>
+        <v>90.813743591308594</v>
       </c>
       <c r="I75" s="1">
-        <v>97.313209533691406</v>
+        <v>97.358901977539063</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1">
-        <v>21053</v>
+        <v>42101</v>
       </c>
       <c r="B76" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="C76" t="s">
-        <v>445</v>
+        <v>148</v>
       </c>
       <c r="D76" s="1">
-        <v>0.028311515226960182</v>
+        <v>0.18830960988998413</v>
       </c>
       <c r="E76" s="1">
-        <v>0.0055641741491854191</v>
+        <v>0.030858449637889862</v>
       </c>
       <c r="F76" s="1">
-        <v>5.0881791114807129</v>
+        <v>6.1023678779602051</v>
       </c>
       <c r="G76" s="1">
-        <v>3.6151786275695486e-07</v>
+        <v>1.0450849075027691e-09</v>
       </c>
       <c r="H76" s="1">
-        <v>84.363502502441406</v>
+        <v>97.468353271484375</v>
       </c>
       <c r="I76" s="1">
-        <v>97.276405334472656</v>
+        <v>97.322723388671875</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1">
-        <v>8049</v>
+        <v>41013</v>
       </c>
       <c r="B77" t="s">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="C77" t="s">
-        <v>255</v>
+        <v>389</v>
       </c>
       <c r="D77" s="1">
-        <v>0.2124524712562561</v>
+        <v>0.14907023310661316</v>
       </c>
       <c r="E77" s="1">
-        <v>0.042266871780157089</v>
+        <v>0.025144163519144058</v>
       </c>
       <c r="F77" s="1">
-        <v>5.0264534950256348</v>
+        <v>5.928621768951416</v>
       </c>
       <c r="G77" s="1">
-        <v>4.9963358605964459e-07</v>
+        <v>3.0548783502837296e-09</v>
       </c>
       <c r="H77" s="1">
-        <v>98.050033569335938</v>
+        <v>96.130195617675781</v>
       </c>
       <c r="I77" s="1">
-        <v>97.239601135253906</v>
+        <v>97.286544799804688</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1">
-        <v>16001</v>
+        <v>38029</v>
       </c>
       <c r="B78" t="s">
-        <v>202</v>
+        <v>288</v>
       </c>
       <c r="C78" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="D78" s="1">
-        <v>0.17050167918205261</v>
+        <v>0.11767695844173431</v>
       </c>
       <c r="E78" s="1">
-        <v>0.03413931280374527</v>
+        <v>0.020035386085510254</v>
       </c>
       <c r="F78" s="1">
-        <v>4.9942913055419922</v>
+        <v>5.8734560012817383</v>
       </c>
       <c r="G78" s="1">
-        <v>5.9052206324849976e-07</v>
+        <v>4.2680232681391317e-09</v>
       </c>
       <c r="H78" s="1">
-        <v>96.946281433105469</v>
+        <v>94.285713195800781</v>
       </c>
       <c r="I78" s="1">
-        <v>97.202796936035156</v>
+        <v>97.250358581542969</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1">
-        <v>53033</v>
+        <v>13065</v>
       </c>
       <c r="B79" t="s">
-        <v>131</v>
+        <v>205</v>
       </c>
       <c r="C79" t="s">
-        <v>147</v>
+        <v>668</v>
       </c>
       <c r="D79" s="1">
-        <v>0.20595867931842804</v>
+        <v>0.049085929989814758</v>
       </c>
       <c r="E79" s="1">
-        <v>0.041703503578901291</v>
+        <v>0.0087076388299465179</v>
       </c>
       <c r="F79" s="1">
-        <v>4.9386420249938965</v>
+        <v>5.6371111869812012</v>
       </c>
       <c r="G79" s="1">
-        <v>7.8668472269782797e-07</v>
+        <v>1.7292647314093301e-08</v>
       </c>
       <c r="H79" s="1">
-        <v>97.939659118652344</v>
+        <v>87.160942077636719</v>
       </c>
       <c r="I79" s="1">
-        <v>97.165992736816406</v>
+        <v>97.214179992675781</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1">
-        <v>12015</v>
+        <v>34009</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C80" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="D80" s="1">
-        <v>0.15423212945461273</v>
+        <v>0.38681164383888245</v>
       </c>
       <c r="E80" s="1">
-        <v>0.031367182731628418</v>
+        <v>0.069756634533405304</v>
       </c>
       <c r="F80" s="1">
-        <v>4.9169902801513672</v>
+        <v>5.5451593399047852</v>
       </c>
       <c r="G80" s="1">
-        <v>8.7884910726643284e-07</v>
+        <v>2.9368660392492529e-08</v>
       </c>
       <c r="H80" s="1">
-        <v>96.504783630371094</v>
+        <v>99.6021728515625</v>
       </c>
       <c r="I80" s="1">
-        <v>97.129188537597656</v>
+        <v>97.178001403808594</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1">
-        <v>6025</v>
+        <v>22021</v>
       </c>
       <c r="B81" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="C81" t="s">
-        <v>150</v>
+        <v>618</v>
       </c>
       <c r="D81" s="1">
-        <v>0.17177577316761017</v>
+        <v>0.046430505812168121</v>
       </c>
       <c r="E81" s="1">
-        <v>0.035536270588636398</v>
+        <v>0.008438323624432087</v>
       </c>
       <c r="F81" s="1">
-        <v>4.8338155746459961</v>
+        <v>5.5023374557495117</v>
       </c>
       <c r="G81" s="1">
-        <v>1.3394068218985922e-06</v>
+        <v>3.7478869785445568e-08</v>
       </c>
       <c r="H81" s="1">
-        <v>97.019866943359375</v>
+        <v>86.799278259277344</v>
       </c>
       <c r="I81" s="1">
-        <v>97.092384338378906</v>
+        <v>97.141822814941406</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1">
-        <v>6057</v>
+        <v>12115</v>
       </c>
       <c r="B82" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="C82" t="s">
-        <v>229</v>
+        <v>145</v>
       </c>
       <c r="D82" s="1">
-        <v>0.30185693502426148</v>
+        <v>0.21304696798324585</v>
       </c>
       <c r="E82" s="1">
-        <v>0.06289903074502945</v>
+        <v>0.039894048124551773</v>
       </c>
       <c r="F82" s="1">
-        <v>4.7990713119506836</v>
+        <v>5.3403196334838867</v>
       </c>
       <c r="G82" s="1">
-        <v>1.5940303228489938e-06</v>
+        <v>9.2782848071237822e-08</v>
       </c>
       <c r="H82" s="1">
-        <v>99.300956726074219</v>
+        <v>98.010848999023438</v>
       </c>
       <c r="I82" s="1">
-        <v>97.055572509765625</v>
+        <v>97.105644226074219</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1">
-        <v>37055</v>
+        <v>12021</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="C83" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="D83" s="1">
-        <v>0.35068994760513306</v>
+        <v>0.21074710786342621</v>
       </c>
       <c r="E83" s="1">
-        <v>0.074259854853153229</v>
+        <v>0.040968708693981171</v>
       </c>
       <c r="F83" s="1">
-        <v>4.7224702835083008</v>
+        <v>5.144099235534668</v>
       </c>
       <c r="G83" s="1">
-        <v>2.3299714939639671e-06</v>
+        <v>2.6880741188506363e-07</v>
       </c>
       <c r="H83" s="1">
-        <v>99.558502197265625</v>
+        <v>97.866188049316406</v>
       </c>
       <c r="I83" s="1">
-        <v>97.018768310546875</v>
+        <v>97.069465637207031</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1">
-        <v>21051</v>
+        <v>21053</v>
       </c>
       <c r="B84" t="s">
         <v>164</v>
       </c>
       <c r="C84" t="s">
-        <v>273</v>
+        <v>445</v>
       </c>
       <c r="D84" s="1">
-        <v>0.081519052386283875</v>
+        <v>0.028311515226960182</v>
       </c>
       <c r="E84" s="1">
-        <v>0.017283216118812561</v>
+        <v>0.0055641741491854191</v>
       </c>
       <c r="F84" s="1">
-        <v>4.7166600227355957</v>
+        <v>5.0881791114807129</v>
       </c>
       <c r="G84" s="1">
-        <v>2.3974780560820364e-06</v>
+        <v>3.6151786275695486e-07</v>
       </c>
       <c r="H84" s="1">
-        <v>91.427520751953125</v>
+        <v>84.267631530761719</v>
       </c>
       <c r="I84" s="1">
-        <v>96.981964111328125</v>
+        <v>97.033287048339844</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1">
-        <v>19195</v>
+        <v>8049</v>
       </c>
       <c r="B85" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D85" s="1">
-        <v>0.20450815558433533</v>
+        <v>0.2124524712562561</v>
       </c>
       <c r="E85" s="1">
-        <v>0.043397333472967148</v>
+        <v>0.042266871780157089</v>
       </c>
       <c r="F85" s="1">
-        <v>4.7124590873718262</v>
+        <v>5.0264534950256348</v>
       </c>
       <c r="G85" s="1">
-        <v>2.4474522888340289e-06</v>
+        <v>4.9963358605964459e-07</v>
       </c>
       <c r="H85" s="1">
-        <v>97.82928466796875</v>
+        <v>97.938514709472656</v>
       </c>
       <c r="I85" s="1">
-        <v>96.945159912109375</v>
+        <v>96.997108459472656</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1">
-        <v>32031</v>
+        <v>16001</v>
       </c>
       <c r="B86" t="s">
-        <v>127</v>
+        <v>202</v>
       </c>
       <c r="C86" t="s">
-        <v>139</v>
+        <v>279</v>
       </c>
       <c r="D86" s="1">
-        <v>0.22138416767120361</v>
+        <v>0.17050167918205261</v>
       </c>
       <c r="E86" s="1">
-        <v>0.047240827232599258</v>
+        <v>0.03413931280374527</v>
       </c>
       <c r="F86" s="1">
-        <v>4.6862888336181641</v>
+        <v>4.9942913055419922</v>
       </c>
       <c r="G86" s="1">
-        <v>2.7820358354802011e-06</v>
+        <v>5.9052206324849976e-07</v>
       </c>
       <c r="H86" s="1">
-        <v>98.19720458984375</v>
+        <v>96.781196594238281</v>
       </c>
       <c r="I86" s="1">
-        <v>96.908355712890625</v>
+        <v>96.960929870605469</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1">
-        <v>32003</v>
+        <v>53033</v>
       </c>
       <c r="B87" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C87" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D87" s="1">
-        <v>0.13999383151531219</v>
+        <v>0.20595867931842804</v>
       </c>
       <c r="E87" s="1">
-        <v>0.030985316261649132</v>
+        <v>0.041703503578901291</v>
       </c>
       <c r="F87" s="1">
-        <v>4.5180702209472656</v>
+        <v>4.9386420249938965</v>
       </c>
       <c r="G87" s="1">
-        <v>6.2405788412434049e-06</v>
+        <v>7.8668472269782797e-07</v>
       </c>
       <c r="H87" s="1">
-        <v>95.805740356445313</v>
+        <v>97.83001708984375</v>
       </c>
       <c r="I87" s="1">
-        <v>96.871551513671875</v>
+        <v>96.92474365234375</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1">
-        <v>13103</v>
+        <v>12015</v>
       </c>
       <c r="B88" t="s">
-        <v>205</v>
+        <v>129</v>
       </c>
       <c r="C88" t="s">
-        <v>409</v>
+        <v>151</v>
       </c>
       <c r="D88" s="1">
-        <v>0.13496731221675873</v>
+        <v>0.15423212945461273</v>
       </c>
       <c r="E88" s="1">
-        <v>0.030077440664172173</v>
+        <v>0.031367182731628418</v>
       </c>
       <c r="F88" s="1">
-        <v>4.4873270988464356</v>
+        <v>4.9169902801513672</v>
       </c>
       <c r="G88" s="1">
-        <v>7.2122302299248986e-06</v>
+        <v>8.7884910726643284e-07</v>
       </c>
       <c r="H88" s="1">
-        <v>95.253860473632813</v>
+        <v>96.347198486328125</v>
       </c>
       <c r="I88" s="1">
-        <v>96.834747314453125</v>
+        <v>96.888565063476563</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1">
-        <v>13287</v>
+        <v>6025</v>
       </c>
       <c r="B89" t="s">
-        <v>205</v>
+        <v>99</v>
       </c>
       <c r="C89" t="s">
-        <v>499</v>
+        <v>150</v>
       </c>
       <c r="D89" s="1">
-        <v>0.031255222856998444</v>
+        <v>0.17177577316761017</v>
       </c>
       <c r="E89" s="1">
-        <v>0.0069806715473532677</v>
+        <v>0.035536270588636398</v>
       </c>
       <c r="F89" s="1">
-        <v>4.4773950576782227</v>
+        <v>4.8338155746459961</v>
       </c>
       <c r="G89" s="1">
-        <v>7.5559350989351515e-06</v>
+        <v>1.3394068218985922e-06</v>
       </c>
       <c r="H89" s="1">
-        <v>84.878585815429688</v>
+        <v>96.853523254394531</v>
       </c>
       <c r="I89" s="1">
-        <v>96.797935485839844</v>
+        <v>96.852386474609375</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1">
-        <v>48399</v>
+        <v>6057</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C90" t="s">
-        <v>619</v>
+        <v>229</v>
       </c>
       <c r="D90" s="1">
-        <v>0.03391440212726593</v>
+        <v>0.30185693502426148</v>
       </c>
       <c r="E90" s="1">
-        <v>0.0078147752210497856</v>
+        <v>0.06289903074502945</v>
       </c>
       <c r="F90" s="1">
-        <v>4.3397793769836426</v>
+        <v>4.7990713119506836</v>
       </c>
       <c r="G90" s="1">
-        <v>1.4262584045354743e-05</v>
+        <v>1.5940303228489938e-06</v>
       </c>
       <c r="H90" s="1">
-        <v>85.246505737304688</v>
+        <v>99.240509033203125</v>
       </c>
       <c r="I90" s="1">
-        <v>96.761131286621094</v>
+        <v>96.816207885742188</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1">
-        <v>45037</v>
+        <v>37055</v>
       </c>
       <c r="B91" t="s">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="C91" t="s">
-        <v>620</v>
+        <v>222</v>
       </c>
       <c r="D91" s="1">
-        <v>0.11463789641857147</v>
+        <v>0.35068994760513306</v>
       </c>
       <c r="E91" s="1">
-        <v>0.026463449001312256</v>
+        <v>0.074259854853153229</v>
       </c>
       <c r="F91" s="1">
-        <v>4.3319334983825684</v>
+        <v>4.7224702835083008</v>
       </c>
       <c r="G91" s="1">
-        <v>1.4780558558413759e-05</v>
+        <v>2.3299714939639671e-06</v>
       </c>
       <c r="H91" s="1">
-        <v>94.076530456542969</v>
+        <v>99.493667602539063</v>
       </c>
       <c r="I91" s="1">
-        <v>96.724327087402344</v>
+        <v>96.780029296875</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1">
-        <v>10005</v>
+        <v>21051</v>
       </c>
       <c r="B92" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="C92" t="s">
-        <v>142</v>
+        <v>273</v>
       </c>
       <c r="D92" s="1">
-        <v>0.17688572406768799</v>
+        <v>0.081519052386283875</v>
       </c>
       <c r="E92" s="1">
-        <v>0.042678680270910263</v>
+        <v>0.017283216118812561</v>
       </c>
       <c r="F92" s="1">
-        <v>4.14459228515625</v>
+        <v>4.7166600227355957</v>
       </c>
       <c r="G92" s="1">
-        <v>3.4041884646285325e-05</v>
+        <v>2.3974780560820364e-06</v>
       </c>
       <c r="H92" s="1">
-        <v>97.167037963867188</v>
+        <v>91.356239318847656</v>
       </c>
       <c r="I92" s="1">
-        <v>96.687522888183594</v>
+        <v>96.743850708007813</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1">
-        <v>16085</v>
+        <v>19195</v>
       </c>
       <c r="B93" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="C93" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="D93" s="1">
-        <v>0.65754300355911255</v>
+        <v>0.20450815558433533</v>
       </c>
       <c r="E93" s="1">
-        <v>0.16319465637207031</v>
+        <v>0.043397333472967148</v>
       </c>
       <c r="F93" s="1">
-        <v>4.0291943550109863</v>
+        <v>4.7124590873718262</v>
       </c>
       <c r="G93" s="1">
-        <v>5.596833216259256e-05</v>
+        <v>2.4474522888340289e-06</v>
       </c>
       <c r="H93" s="1">
-        <v>99.963211059570313</v>
+        <v>97.721519470214844</v>
       </c>
       <c r="I93" s="1">
-        <v>96.650718688964844</v>
+        <v>96.707672119140625</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1">
-        <v>41017</v>
+        <v>32031</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C94" t="s">
-        <v>621</v>
+        <v>139</v>
       </c>
       <c r="D94" s="1">
-        <v>0.13934269547462463</v>
+        <v>0.22138416767120361</v>
       </c>
       <c r="E94" s="1">
-        <v>0.034868370741605759</v>
+        <v>0.047240827232599258</v>
       </c>
       <c r="F94" s="1">
-        <v>3.9962491989135742</v>
+        <v>4.6862888336181641</v>
       </c>
       <c r="G94" s="1">
-        <v>6.4353989728260785e-05</v>
+        <v>2.7820358354802011e-06</v>
       </c>
       <c r="H94" s="1">
-        <v>95.768951416015625</v>
+        <v>98.119346618652344</v>
       </c>
       <c r="I94" s="1">
-        <v>96.613914489746094</v>
+        <v>96.671493530273438</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1">
-        <v>13035</v>
+        <v>32003</v>
       </c>
       <c r="B95" t="s">
-        <v>205</v>
+        <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>242</v>
+        <v>152</v>
       </c>
       <c r="D95" s="1">
-        <v>0.24290627241134644</v>
+        <v>0.13999383151531219</v>
       </c>
       <c r="E95" s="1">
-        <v>0.061875645071268082</v>
+        <v>0.030985316261649132</v>
       </c>
       <c r="F95" s="1">
-        <v>3.9257171154022217</v>
+        <v>4.5180702209472656</v>
       </c>
       <c r="G95" s="1">
-        <v>8.6471729446202517e-05</v>
+        <v>6.2405788412434049e-06</v>
       </c>
       <c r="H95" s="1">
-        <v>98.749076843261719</v>
+        <v>95.6600341796875</v>
       </c>
       <c r="I95" s="1">
-        <v>96.577110290527344</v>
+        <v>96.63531494140625</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1">
-        <v>12081</v>
+        <v>13103</v>
       </c>
       <c r="B96" t="s">
-        <v>129</v>
+        <v>205</v>
       </c>
       <c r="C96" t="s">
-        <v>149</v>
+        <v>409</v>
       </c>
       <c r="D96" s="1">
-        <v>0.17033989727497101</v>
+        <v>0.13496731221675873</v>
       </c>
       <c r="E96" s="1">
-        <v>0.0436834916472435</v>
+        <v>0.030077440664172173</v>
       </c>
       <c r="F96" s="1">
-        <v>3.8994112014770508</v>
+        <v>4.4873270988464356</v>
       </c>
       <c r="G96" s="1">
-        <v>9.6426891104783863e-05</v>
+        <v>7.2122302299248986e-06</v>
       </c>
       <c r="H96" s="1">
-        <v>96.909492492675781</v>
+        <v>95.117538452148438</v>
       </c>
       <c r="I96" s="1">
-        <v>96.540298461914063</v>
+        <v>96.599128723144531</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1">
-        <v>25001</v>
+        <v>13287</v>
       </c>
       <c r="B97" t="s">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C97" t="s">
-        <v>232</v>
+        <v>499</v>
       </c>
       <c r="D97" s="1">
-        <v>0.29252177476882935</v>
+        <v>0.031255222856998444</v>
       </c>
       <c r="E97" s="1">
-        <v>0.075748614966869354</v>
+        <v>0.0069806715473532677</v>
       </c>
       <c r="F97" s="1">
-        <v>3.8617441654205322</v>
+        <v>4.4773950576782227</v>
       </c>
       <c r="G97" s="1">
-        <v>0.00011258042650297284</v>
+        <v>7.5559350989351515e-06</v>
       </c>
       <c r="H97" s="1">
-        <v>99.190582275390625</v>
+        <v>84.773963928222656</v>
       </c>
       <c r="I97" s="1">
-        <v>96.503494262695313</v>
+        <v>96.562950134277344</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1">
-        <v>5005</v>
+        <v>48399</v>
       </c>
       <c r="B98" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="C98" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D98" s="1">
-        <v>0.13564077019691467</v>
+        <v>0.03391440212726593</v>
       </c>
       <c r="E98" s="1">
-        <v>0.036293763667345047</v>
+        <v>0.0078147752210497856</v>
       </c>
       <c r="F98" s="1">
-        <v>3.737302303314209</v>
+        <v>4.3397793769836426</v>
       </c>
       <c r="G98" s="1">
-        <v>0.00018600524344947189</v>
+        <v>1.4262584045354743e-05</v>
       </c>
       <c r="H98" s="1">
-        <v>95.327445983886719</v>
+        <v>85.171791076660156</v>
       </c>
       <c r="I98" s="1">
-        <v>96.466690063476563</v>
+        <v>96.526771545410156</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1">
-        <v>47047</v>
+        <v>45037</v>
       </c>
       <c r="B99" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="C99" t="s">
-        <v>552</v>
+        <v>620</v>
       </c>
       <c r="D99" s="1">
-        <v>0.061802919954061508</v>
+        <v>0.11463789641857147</v>
       </c>
       <c r="E99" s="1">
-        <v>0.016977639868855476</v>
+        <v>0.026463449001312256</v>
       </c>
       <c r="F99" s="1">
-        <v>3.640254020690918</v>
+        <v>4.3319334983825684</v>
       </c>
       <c r="G99" s="1">
-        <v>0.00027236918685957789</v>
+        <v>1.4780558558413759e-05</v>
       </c>
       <c r="H99" s="1">
-        <v>88.741722106933594</v>
+        <v>93.960220336914063</v>
       </c>
       <c r="I99" s="1">
-        <v>96.429885864257813</v>
+        <v>96.490592956542969</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1">
-        <v>48297</v>
+        <v>48357</v>
       </c>
       <c r="B100" t="s">
         <v>100</v>
       </c>
       <c r="C100" t="s">
-        <v>623</v>
+        <v>669</v>
       </c>
       <c r="D100" s="1">
-        <v>0.1133943572640419</v>
+        <v>0.025332914665341377</v>
       </c>
       <c r="E100" s="1">
-        <v>0.031723447144031525</v>
+        <v>0.0058722393587231636</v>
       </c>
       <c r="F100" s="1">
-        <v>3.574465274810791</v>
+        <v>4.3140125274658203</v>
       </c>
       <c r="G100" s="1">
-        <v>0.00035094437771476805</v>
+        <v>1.6031784980441444e-05</v>
       </c>
       <c r="H100" s="1">
-        <v>93.892570495605469</v>
+        <v>83.797470092773438</v>
       </c>
       <c r="I100" s="1">
-        <v>96.393081665039063</v>
+        <v>96.454414367675781</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1">
-        <v>53063</v>
+        <v>10005</v>
       </c>
       <c r="B101" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C101" t="s">
-        <v>624</v>
+        <v>142</v>
       </c>
       <c r="D101" s="1">
-        <v>0.071516834199428558</v>
+        <v>0.17688572406768799</v>
       </c>
       <c r="E101" s="1">
-        <v>0.020068997517228127</v>
+        <v>0.042678680270910263</v>
       </c>
       <c r="F101" s="1">
-        <v>3.5635478496551514</v>
+        <v>4.14459228515625</v>
       </c>
       <c r="G101" s="1">
-        <v>0.000365875952411443</v>
+        <v>3.4041884646285325e-05</v>
       </c>
       <c r="H101" s="1">
-        <v>90.029434204101563</v>
+        <v>97.034355163574219</v>
       </c>
       <c r="I101" s="1">
-        <v>96.356277465820313</v>
+        <v>96.418235778808594</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1">
-        <v>12111</v>
+        <v>16085</v>
       </c>
       <c r="B102" t="s">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C102" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="D102" s="1">
-        <v>0.11532605439424515</v>
+        <v>0.65754300355911255</v>
       </c>
       <c r="E102" s="1">
-        <v>0.033698059618473053</v>
+        <v>0.16319465637207031</v>
       </c>
       <c r="F102" s="1">
-        <v>3.422335147857666</v>
+        <v>4.0291943550109863</v>
       </c>
       <c r="G102" s="1">
-        <v>0.00062085734680294991</v>
+        <v>5.596833216259256e-05</v>
       </c>
       <c r="H102" s="1">
-        <v>94.22369384765625</v>
+        <v>99.927665710449219</v>
       </c>
       <c r="I102" s="1">
-        <v>96.319473266601563</v>
+        <v>96.382057189941406</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1">
-        <v>12109</v>
+        <v>41017</v>
       </c>
       <c r="B103" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C103" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D103" s="1">
-        <v>0.15055170655250549</v>
+        <v>0.13934269547462463</v>
       </c>
       <c r="E103" s="1">
-        <v>0.045278880745172501</v>
+        <v>0.034868370741605759</v>
       </c>
       <c r="F103" s="1">
-        <v>3.3249874114990234</v>
+        <v>3.9962491989135742</v>
       </c>
       <c r="G103" s="1">
-        <v>0.0008842253009788692</v>
+        <v>6.4353989728260785e-05</v>
       </c>
       <c r="H103" s="1">
-        <v>96.357612609863281</v>
+        <v>95.623870849609375</v>
       </c>
       <c r="I103" s="1">
-        <v>96.282661437988281</v>
+        <v>96.345878601074219</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1">
-        <v>47185</v>
+        <v>13035</v>
       </c>
       <c r="B104" t="s">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="C104" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="D104" s="1">
-        <v>0.18495158851146698</v>
+        <v>0.24290627241134644</v>
       </c>
       <c r="E104" s="1">
-        <v>0.055880848318338394</v>
+        <v>0.061875645071268082</v>
       </c>
       <c r="F104" s="1">
-        <v>3.3097491264343262</v>
+        <v>3.9257171154022217</v>
       </c>
       <c r="G104" s="1">
-        <v>0.00093379628378897905</v>
+        <v>8.6471729446202517e-05</v>
       </c>
       <c r="H104" s="1">
-        <v>97.387786865234375</v>
+        <v>98.661842346191406</v>
       </c>
       <c r="I104" s="1">
-        <v>96.245857238769531</v>
+        <v>96.3096923828125</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1">
-        <v>13171</v>
+        <v>12081</v>
       </c>
       <c r="B105" t="s">
-        <v>205</v>
+        <v>129</v>
       </c>
       <c r="C105" t="s">
-        <v>576</v>
+        <v>149</v>
       </c>
       <c r="D105" s="1">
-        <v>0.14492945373058319</v>
+        <v>0.17033989727497101</v>
       </c>
       <c r="E105" s="1">
-        <v>0.044260572642087936</v>
+        <v>0.0436834916472435</v>
       </c>
       <c r="F105" s="1">
-        <v>3.2744596004486084</v>
+        <v>3.8994112014770508</v>
       </c>
       <c r="G105" s="1">
-        <v>0.001058642752468586</v>
+        <v>9.6426891104783863e-05</v>
       </c>
       <c r="H105" s="1">
-        <v>95.989700317382813</v>
+        <v>96.745025634765625</v>
       </c>
       <c r="I105" s="1">
-        <v>96.209053039550781</v>
+        <v>96.273513793945313</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1">
-        <v>6065</v>
+        <v>25001</v>
       </c>
       <c r="B106" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="C106" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="D106" s="1">
-        <v>0.098317854106426239</v>
+        <v>0.29252177476882935</v>
       </c>
       <c r="E106" s="1">
-        <v>0.030078686773777008</v>
+        <v>0.075748614966869354</v>
       </c>
       <c r="F106" s="1">
-        <v>3.268688440322876</v>
+        <v>3.8617441654205322</v>
       </c>
       <c r="G106" s="1">
-        <v>0.0010804720222949982</v>
+        <v>0.00011258042650297284</v>
       </c>
       <c r="H106" s="1">
-        <v>92.825607299804688</v>
+        <v>99.132003784179688</v>
       </c>
       <c r="I106" s="1">
-        <v>96.172248840332031</v>
+        <v>96.237335205078125</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1">
-        <v>12009</v>
+        <v>5005</v>
       </c>
       <c r="B107" t="s">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="C107" t="s">
-        <v>189</v>
+        <v>622</v>
       </c>
       <c r="D107" s="1">
-        <v>0.073807381093502045</v>
+        <v>0.13564077019691467</v>
       </c>
       <c r="E107" s="1">
-        <v>0.022741802036762238</v>
+        <v>0.036293763667345047</v>
       </c>
       <c r="F107" s="1">
-        <v>3.2454500198364258</v>
+        <v>3.737302303314209</v>
       </c>
       <c r="G107" s="1">
-        <v>0.0011726514203473926</v>
+        <v>0.00018600524344947189</v>
       </c>
       <c r="H107" s="1">
-        <v>90.360557556152344</v>
+        <v>95.189872741699219</v>
       </c>
       <c r="I107" s="1">
-        <v>96.135444641113281</v>
+        <v>96.201156616210938</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1">
-        <v>37053</v>
+        <v>8023</v>
       </c>
       <c r="B108" t="s">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="C108" t="s">
-        <v>626</v>
+        <v>670</v>
       </c>
       <c r="D108" s="1">
-        <v>0.10937231779098511</v>
+        <v>0.033381186425685883</v>
       </c>
       <c r="E108" s="1">
-        <v>0.034154307097196579</v>
+        <v>0.0091254469007253647</v>
       </c>
       <c r="F108" s="1">
-        <v>3.2022993564605713</v>
+        <v>3.6580331325531006</v>
       </c>
       <c r="G108" s="1">
-        <v>0.0013633524067699909</v>
+        <v>0.0002541581925470382</v>
       </c>
       <c r="H108" s="1">
-        <v>93.635025024414063</v>
+        <v>85.06329345703125</v>
       </c>
       <c r="I108" s="1">
-        <v>96.098640441894531</v>
+        <v>96.16497802734375</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1">
-        <v>41057</v>
+        <v>47047</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C109" t="s">
-        <v>627</v>
+        <v>552</v>
       </c>
       <c r="D109" s="1">
-        <v>0.13886702060699463</v>
+        <v>0.061802919954061508</v>
       </c>
       <c r="E109" s="1">
-        <v>0.043611034750938416</v>
+        <v>0.016977639868855476</v>
       </c>
       <c r="F109" s="1">
-        <v>3.1842174530029297</v>
+        <v>3.640254020690918</v>
       </c>
       <c r="G109" s="1">
-        <v>0.0014514593640342355</v>
+        <v>0.00027236918685957789</v>
       </c>
       <c r="H109" s="1">
-        <v>95.695365905761719</v>
+        <v>88.679924011230469</v>
       </c>
       <c r="I109" s="1">
-        <v>96.061836242675781</v>
+        <v>96.128799438476563</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1">
-        <v>1129</v>
+        <v>48297</v>
       </c>
       <c r="B110" t="s">
-        <v>208</v>
+        <v>100</v>
       </c>
       <c r="C110" t="s">
-        <v>169</v>
+        <v>623</v>
       </c>
       <c r="D110" s="1">
-        <v>0.058008730411529541</v>
+        <v>0.1133943572640419</v>
       </c>
       <c r="E110" s="1">
-        <v>0.01824527233839035</v>
+        <v>0.031723447144031525</v>
       </c>
       <c r="F110" s="1">
-        <v>3.1793842315673828</v>
+        <v>3.574465274810791</v>
       </c>
       <c r="G110" s="1">
-        <v>0.0014758830657228827</v>
+        <v>0.00035094437771476805</v>
       </c>
       <c r="H110" s="1">
-        <v>88.373802185058594</v>
+        <v>93.779388427734375</v>
       </c>
       <c r="I110" s="1">
-        <v>96.0250244140625</v>
+        <v>96.092620849609375</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1">
-        <v>13157</v>
+        <v>53063</v>
       </c>
       <c r="B111" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="C111" t="s">
-        <v>418</v>
+        <v>624</v>
       </c>
       <c r="D111" s="1">
-        <v>0.10046999156475067</v>
+        <v>0.071516834199428558</v>
       </c>
       <c r="E111" s="1">
-        <v>0.031680602580308914</v>
+        <v>0.020068997517228127</v>
       </c>
       <c r="F111" s="1">
-        <v>3.1713409423828125</v>
+        <v>3.5635478496551514</v>
       </c>
       <c r="G111" s="1">
-        <v>0.0015173694118857384</v>
+        <v>0.000365875952411443</v>
       </c>
       <c r="H111" s="1">
-        <v>93.009567260742188</v>
+        <v>89.945747375488281</v>
       </c>
       <c r="I111" s="1">
-        <v>95.98822021484375</v>
+        <v>96.056442260742188</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1">
-        <v>13291</v>
+        <v>12111</v>
       </c>
       <c r="B112" t="s">
-        <v>205</v>
+        <v>129</v>
       </c>
       <c r="C112" t="s">
-        <v>356</v>
+        <v>187</v>
       </c>
       <c r="D112" s="1">
-        <v>0.054337598383426666</v>
+        <v>0.11532605439424515</v>
       </c>
       <c r="E112" s="1">
-        <v>0.017224289476871491</v>
+        <v>0.033698059618473053</v>
       </c>
       <c r="F112" s="1">
-        <v>3.154707670211792</v>
+        <v>3.422335147857666</v>
       </c>
       <c r="G112" s="1">
-        <v>0.0016065898817032576</v>
+        <v>0.00062085734680294991</v>
       </c>
       <c r="H112" s="1">
-        <v>87.821929931640625</v>
+        <v>94.104881286621094</v>
       </c>
       <c r="I112" s="1">
-        <v>95.951416015625</v>
+        <v>96.020263671875</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1">
-        <v>24047</v>
+        <v>12109</v>
       </c>
       <c r="B113" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="C113" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D113" s="1">
-        <v>0.11414248496294022</v>
+        <v>0.15055170655250549</v>
       </c>
       <c r="E113" s="1">
-        <v>0.036450985819101334</v>
+        <v>0.045278880745172501</v>
       </c>
       <c r="F113" s="1">
-        <v>3.1313962936401367</v>
+        <v>3.3249874114990234</v>
       </c>
       <c r="G113" s="1">
-        <v>0.0017397721530869603</v>
+        <v>0.0008842253009788692</v>
       </c>
       <c r="H113" s="1">
-        <v>93.966148376464844</v>
+        <v>96.202529907226563</v>
       </c>
       <c r="I113" s="1">
-        <v>95.91461181640625</v>
+        <v>95.984077453613281</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1">
-        <v>6001</v>
+        <v>47185</v>
       </c>
       <c r="B114" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C114" t="s">
-        <v>156</v>
+        <v>270</v>
       </c>
       <c r="D114" s="1">
-        <v>0.11582379043102264</v>
+        <v>0.18495158851146698</v>
       </c>
       <c r="E114" s="1">
-        <v>0.0372498519718647</v>
+        <v>0.055880848318338394</v>
       </c>
       <c r="F114" s="1">
-        <v>3.1093759536743164</v>
+        <v>3.3097491264343262</v>
       </c>
       <c r="G114" s="1">
-        <v>0.001874829875305295</v>
+        <v>0.00093379628378897905</v>
       </c>
       <c r="H114" s="1">
-        <v>94.334068298339844</v>
+        <v>97.287521362304688</v>
       </c>
       <c r="I114" s="1">
-        <v>95.8778076171875</v>
+        <v>95.947898864746094</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1">
-        <v>6077</v>
+        <v>13171</v>
       </c>
       <c r="B115" t="s">
-        <v>99</v>
+        <v>205</v>
       </c>
       <c r="C115" t="s">
-        <v>186</v>
+        <v>576</v>
       </c>
       <c r="D115" s="1">
-        <v>0.076876625418663025</v>
+        <v>0.14492945373058319</v>
       </c>
       <c r="E115" s="1">
-        <v>0.024749642238020897</v>
+        <v>0.044260572642087936</v>
       </c>
       <c r="F115" s="1">
-        <v>3.1061711311340332</v>
+        <v>3.2744596004486084</v>
       </c>
       <c r="G115" s="1">
-        <v>0.0018952699610963464</v>
+        <v>0.001058642752468586</v>
       </c>
       <c r="H115" s="1">
-        <v>90.949226379394531</v>
+        <v>95.840866088867188</v>
       </c>
       <c r="I115" s="1">
-        <v>95.84100341796875</v>
+        <v>95.911720275878906</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1">
-        <v>4027</v>
+        <v>6065</v>
       </c>
       <c r="B116" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="C116" t="s">
-        <v>629</v>
+        <v>188</v>
       </c>
       <c r="D116" s="1">
-        <v>0.11555098742246628</v>
+        <v>0.098317854106426239</v>
       </c>
       <c r="E116" s="1">
-        <v>0.037607081234455109</v>
+        <v>0.030078686773777008</v>
       </c>
       <c r="F116" s="1">
-        <v>3.0725858211517334</v>
+        <v>3.268688440322876</v>
       </c>
       <c r="G116" s="1">
-        <v>0.0021221279166638851</v>
+        <v>0.0010804720222949982</v>
       </c>
       <c r="H116" s="1">
-        <v>94.297279357910156</v>
+        <v>92.730560302734375</v>
       </c>
       <c r="I116" s="1">
-        <v>95.80419921875</v>
+        <v>95.875541687011719</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1">
-        <v>48219</v>
+        <v>12009</v>
       </c>
       <c r="B117" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="C117" t="s">
-        <v>630</v>
+        <v>189</v>
       </c>
       <c r="D117" s="1">
-        <v>0.020128799602389336</v>
+        <v>0.073807381093502045</v>
       </c>
       <c r="E117" s="1">
-        <v>0.0066858953796327114</v>
+        <v>0.022741802036762238</v>
       </c>
       <c r="F117" s="1">
-        <v>3.0106363296508789</v>
+        <v>3.2454500198364258</v>
       </c>
       <c r="G117" s="1">
-        <v>0.002607008907943964</v>
+        <v>0.0011726514203473926</v>
       </c>
       <c r="H117" s="1">
-        <v>83.22296142578125</v>
+        <v>90.271247863769531</v>
       </c>
       <c r="I117" s="1">
-        <v>95.767387390136719</v>
+        <v>95.839363098144531</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1">
-        <v>42089</v>
+        <v>37053</v>
       </c>
       <c r="B118" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>371</v>
+        <v>626</v>
       </c>
       <c r="D118" s="1">
-        <v>0.11032874882221222</v>
+        <v>0.10937231779098511</v>
       </c>
       <c r="E118" s="1">
-        <v>0.037075579166412354</v>
+        <v>0.034154307097196579</v>
       </c>
       <c r="F118" s="1">
-        <v>2.9757795333862305</v>
+        <v>3.2022993564605713</v>
       </c>
       <c r="G118" s="1">
-        <v>0.0029224487952888012</v>
+        <v>0.0013633524067699909</v>
       </c>
       <c r="H118" s="1">
-        <v>93.708610534667969</v>
+        <v>93.526222229003906</v>
       </c>
       <c r="I118" s="1">
-        <v>95.730583190917969</v>
+        <v>95.803184509277344</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1">
-        <v>29057</v>
+        <v>41057</v>
       </c>
       <c r="B119" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="C119" t="s">
-        <v>410</v>
+        <v>627</v>
       </c>
       <c r="D119" s="1">
-        <v>0.097862325608730316</v>
+        <v>0.13886702060699463</v>
       </c>
       <c r="E119" s="1">
-        <v>0.033186376094818115</v>
+        <v>0.043611034750938416</v>
       </c>
       <c r="F119" s="1">
-        <v>2.9488704204559326</v>
+        <v>3.1842174530029297</v>
       </c>
       <c r="G119" s="1">
-        <v>0.0031893767882138491</v>
+        <v>0.0014514593640342355</v>
       </c>
       <c r="H119" s="1">
-        <v>92.752021789550781</v>
+        <v>95.551536560058594</v>
       </c>
       <c r="I119" s="1">
-        <v>95.693778991699219</v>
+        <v>95.767005920410156</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1">
+        <v>1129</v>
+      </c>
+      <c r="B120" t="s">
+        <v>208</v>
+      </c>
+      <c r="C120" t="s">
+        <v>169</v>
+      </c>
+      <c r="D120" s="1">
+        <v>0.058008730411529541</v>
+      </c>
+      <c r="E120" s="1">
+        <v>0.01824527233839035</v>
+      </c>
+      <c r="F120" s="1">
+        <v>3.1793842315673828</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0.0014758830657228827</v>
+      </c>
+      <c r="H120" s="1">
+        <v>88.318267822265625</v>
+      </c>
+      <c r="I120" s="1">
+        <v>95.730827331542969</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1">
+        <v>13157</v>
+      </c>
+      <c r="B121" t="s">
+        <v>205</v>
+      </c>
+      <c r="C121" t="s">
+        <v>418</v>
+      </c>
+      <c r="D121" s="1">
+        <v>0.10046999156475067</v>
+      </c>
+      <c r="E121" s="1">
+        <v>0.031680602580308914</v>
+      </c>
+      <c r="F121" s="1">
+        <v>3.1713409423828125</v>
+      </c>
+      <c r="G121" s="1">
+        <v>0.0015173694118857384</v>
+      </c>
+      <c r="H121" s="1">
+        <v>92.911392211914063</v>
+      </c>
+      <c r="I121" s="1">
+        <v>95.694648742675781</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1">
+        <v>13291</v>
+      </c>
+      <c r="B122" t="s">
+        <v>205</v>
+      </c>
+      <c r="C122" t="s">
+        <v>356</v>
+      </c>
+      <c r="D122" s="1">
+        <v>0.054337598383426666</v>
+      </c>
+      <c r="E122" s="1">
+        <v>0.017224289476871491</v>
+      </c>
+      <c r="F122" s="1">
+        <v>3.154707670211792</v>
+      </c>
+      <c r="G122" s="1">
+        <v>0.0016065898817032576</v>
+      </c>
+      <c r="H122" s="1">
+        <v>87.775772094726563</v>
+      </c>
+      <c r="I122" s="1">
+        <v>95.658462524414063</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1">
+        <v>24047</v>
+      </c>
+      <c r="B123" t="s">
+        <v>194</v>
+      </c>
+      <c r="C123" t="s">
+        <v>628</v>
+      </c>
+      <c r="D123" s="1">
+        <v>0.11414248496294022</v>
+      </c>
+      <c r="E123" s="1">
+        <v>0.036450985819101334</v>
+      </c>
+      <c r="F123" s="1">
+        <v>3.1313962936401367</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0.0017397721530869603</v>
+      </c>
+      <c r="H123" s="1">
+        <v>93.851715087890625</v>
+      </c>
+      <c r="I123" s="1">
+        <v>95.622283935546875</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1">
+        <v>6001</v>
+      </c>
+      <c r="B124" t="s">
+        <v>99</v>
+      </c>
+      <c r="C124" t="s">
+        <v>156</v>
+      </c>
+      <c r="D124" s="1">
+        <v>0.11582379043102264</v>
+      </c>
+      <c r="E124" s="1">
+        <v>0.0372498519718647</v>
+      </c>
+      <c r="F124" s="1">
+        <v>3.1093759536743164</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0.001874829875305295</v>
+      </c>
+      <c r="H124" s="1">
+        <v>94.21337890625</v>
+      </c>
+      <c r="I124" s="1">
+        <v>95.586105346679688</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1">
+        <v>6077</v>
+      </c>
+      <c r="B125" t="s">
+        <v>99</v>
+      </c>
+      <c r="C125" t="s">
+        <v>186</v>
+      </c>
+      <c r="D125" s="1">
+        <v>0.076876625418663025</v>
+      </c>
+      <c r="E125" s="1">
+        <v>0.024749642238020897</v>
+      </c>
+      <c r="F125" s="1">
+        <v>3.1061711311340332</v>
+      </c>
+      <c r="G125" s="1">
+        <v>0.0018952699610963464</v>
+      </c>
+      <c r="H125" s="1">
+        <v>90.849906921386719</v>
+      </c>
+      <c r="I125" s="1">
+        <v>95.5499267578125</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1">
+        <v>4027</v>
+      </c>
+      <c r="B126" t="s">
+        <v>126</v>
+      </c>
+      <c r="C126" t="s">
+        <v>629</v>
+      </c>
+      <c r="D126" s="1">
+        <v>0.11555098742246628</v>
+      </c>
+      <c r="E126" s="1">
+        <v>0.037607081234455109</v>
+      </c>
+      <c r="F126" s="1">
+        <v>3.0725858211517334</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0.0021221279166638851</v>
+      </c>
+      <c r="H126" s="1">
+        <v>94.177215576171875</v>
+      </c>
+      <c r="I126" s="1">
+        <v>95.513748168945313</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1">
+        <v>48219</v>
+      </c>
+      <c r="B127" t="s">
+        <v>100</v>
+      </c>
+      <c r="C127" t="s">
+        <v>630</v>
+      </c>
+      <c r="D127" s="1">
+        <v>0.020128799602389336</v>
+      </c>
+      <c r="E127" s="1">
+        <v>0.0066858953796327114</v>
+      </c>
+      <c r="F127" s="1">
+        <v>3.0106363296508789</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0.002607008907943964</v>
+      </c>
+      <c r="H127" s="1">
+        <v>83.110305786132813</v>
+      </c>
+      <c r="I127" s="1">
+        <v>95.477569580078125</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1">
+        <v>42089</v>
+      </c>
+      <c r="B128" t="s">
+        <v>132</v>
+      </c>
+      <c r="C128" t="s">
+        <v>371</v>
+      </c>
+      <c r="D128" s="1">
+        <v>0.11032874882221222</v>
+      </c>
+      <c r="E128" s="1">
+        <v>0.037075579166412354</v>
+      </c>
+      <c r="F128" s="1">
+        <v>2.9757795333862305</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0.0029224487952888012</v>
+      </c>
+      <c r="H128" s="1">
+        <v>93.598556518554688</v>
+      </c>
+      <c r="I128" s="1">
+        <v>95.441390991210938</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1">
+        <v>29057</v>
+      </c>
+      <c r="B129" t="s">
+        <v>133</v>
+      </c>
+      <c r="C129" t="s">
+        <v>410</v>
+      </c>
+      <c r="D129" s="1">
+        <v>0.097862325608730316</v>
+      </c>
+      <c r="E129" s="1">
+        <v>0.033186376094818115</v>
+      </c>
+      <c r="F129" s="1">
+        <v>2.9488704204559326</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0.0031893767882138491</v>
+      </c>
+      <c r="H129" s="1">
+        <v>92.658226013183594</v>
+      </c>
+      <c r="I129" s="1">
+        <v>95.40521240234375</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1">
         <v>48317</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B130" t="s">
         <v>100</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C130" t="s">
         <v>237</v>
       </c>
-      <c r="D120" s="1">
+      <c r="D130" s="1">
         <v>0.26359257102012634</v>
       </c>
-      <c r="E120" s="1">
+      <c r="E130" s="1">
         <v>0.090121828019618988</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F130" s="1">
         <v>2.9248471260070801</v>
       </c>
-      <c r="G120" s="1">
+      <c r="G130" s="1">
         <v>0.0034462548792362213</v>
       </c>
-      <c r="H120" s="1">
-        <v>98.969833374023438</v>
-      </c>
-      <c r="I120" s="1">
-        <v>95.656974792480469</v>
+      <c r="H130" s="1">
+        <v>98.87884521484375</v>
+      </c>
+      <c r="I130" s="1">
+        <v>95.369033813476563</v>
       </c>
     </row>
   </sheetData>
@@ -9893,7 +10204,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9927,2670 +10238,2844 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>26013</v>
+        <v>48429</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>212</v>
+        <v>664</v>
       </c>
       <c r="D2" s="1">
-        <v>0.68777406215667725</v>
+        <v>0.69774353504180908</v>
       </c>
       <c r="E2" s="1">
-        <v>0.098883107304573059</v>
+        <v>0.38563916087150574</v>
       </c>
       <c r="F2" s="1">
-        <v>6.9554252624511719</v>
+        <v>1.8093171119689942</v>
       </c>
       <c r="G2" s="1">
-        <v>3.5149660959632456e-12</v>
+        <v>0.070401750504970551</v>
       </c>
       <c r="H2" s="1">
         <v>100</v>
       </c>
       <c r="I2" s="1">
-        <v>97.754875183105469</v>
+        <v>92.402313232421875</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>16085</v>
+        <v>26013</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D3" s="1">
-        <v>0.65754300355911255</v>
+        <v>0.68777406215667725</v>
       </c>
       <c r="E3" s="1">
-        <v>0.16319465637207031</v>
+        <v>0.098883107304573059</v>
       </c>
       <c r="F3" s="1">
-        <v>4.0291943550109863</v>
+        <v>6.9554252624511719</v>
       </c>
       <c r="G3" s="1">
-        <v>5.596833216259256e-05</v>
+        <v>3.5149660959632456e-12</v>
       </c>
       <c r="H3" s="1">
-        <v>99.963211059570313</v>
+        <v>99.963836669921875</v>
       </c>
       <c r="I3" s="1">
-        <v>96.650718688964844</v>
+        <v>97.539794921875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>53055</v>
+        <v>16085</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D4" s="1">
-        <v>0.52950280904769897</v>
+        <v>0.65754300355911255</v>
       </c>
       <c r="E4" s="1">
-        <v>0.19727590680122375</v>
+        <v>0.16319465637207031</v>
       </c>
       <c r="F4" s="1">
-        <v>2.6840722560882568</v>
+        <v>4.0291943550109863</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0072731385007500648</v>
+        <v>5.596833216259256e-05</v>
       </c>
       <c r="H4" s="1">
-        <v>99.926414489746094</v>
+        <v>99.927665710449219</v>
       </c>
       <c r="I4" s="1">
-        <v>95.215309143066406</v>
+        <v>96.382057189941406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>51103</v>
+        <v>29033</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="D5" s="1">
-        <v>0.52496671676635742</v>
+        <v>0.58515948057174683</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0063457945361733437</v>
+        <v>0.007855856791138649</v>
       </c>
       <c r="F5" s="1">
-        <v>82.726715087890625</v>
+        <v>74.487037658691406</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>99.889625549316406</v>
+        <v>99.891502380371094</v>
       </c>
       <c r="I5" s="1">
-        <v>100</v>
+        <v>99.963821411132813</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>46077</v>
+        <v>53055</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="C6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D6" s="1">
-        <v>0.49427169561386108</v>
+        <v>0.52950280904769897</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0089177517220377922</v>
+        <v>0.19727590680122375</v>
       </c>
       <c r="F6" s="1">
-        <v>55.425594329833984</v>
+        <v>2.6840722560882568</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>0.0072731385007500648</v>
       </c>
       <c r="H6" s="1">
-        <v>99.852836608886719</v>
+        <v>99.855331420898438</v>
       </c>
       <c r="I6" s="1">
-        <v>99.815971374511719</v>
+        <v>94.93487548828125</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>5129</v>
+        <v>51103</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D7" s="1">
-        <v>0.44076985120773316</v>
+        <v>0.52496671676635742</v>
       </c>
       <c r="E7" s="1">
-        <v>0.0079335533082485199</v>
+        <v>0.0063457945361733437</v>
       </c>
       <c r="F7" s="1">
-        <v>55.557685852050781</v>
+        <v>82.726715087890625</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>99.8160400390625</v>
+        <v>99.819168090820313</v>
       </c>
       <c r="I7" s="1">
-        <v>99.852775573730469</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>36021</v>
+        <v>46077</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D8" s="1">
-        <v>0.43953016400337219</v>
+        <v>0.49427169561386108</v>
       </c>
       <c r="E8" s="1">
-        <v>0.27799993753433228</v>
+        <v>0.0089177517220377922</v>
       </c>
       <c r="F8" s="1">
-        <v>1.58104407787323</v>
+        <v>55.425594329833984</v>
       </c>
       <c r="G8" s="1">
-        <v>0.11386796087026596</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>99.779251098632813</v>
+        <v>99.783004760742188</v>
       </c>
       <c r="I8" s="1">
-        <v>91.681999206542969</v>
+        <v>99.782920837402344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>20017</v>
+        <v>5129</v>
       </c>
       <c r="B9" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D9" s="1">
-        <v>0.42066857218742371</v>
+        <v>0.44076985120773316</v>
       </c>
       <c r="E9" s="1">
-        <v>0.0064287125132977962</v>
+        <v>0.0079335533082485199</v>
       </c>
       <c r="F9" s="1">
-        <v>65.435897827148438</v>
+        <v>55.557685852050781</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>99.742454528808594</v>
+        <v>99.746833801269531</v>
       </c>
       <c r="I9" s="1">
-        <v>99.96319580078125</v>
+        <v>99.819099426269531</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>25003</v>
+        <v>36021</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="D10" s="1">
-        <v>0.40388906002044678</v>
+        <v>0.43953016400337219</v>
       </c>
       <c r="E10" s="1">
-        <v>0.31419673562049866</v>
+        <v>0.27799993753433228</v>
       </c>
       <c r="F10" s="1">
-        <v>1.2854654788970947</v>
+        <v>1.58104407787323</v>
       </c>
       <c r="G10" s="1">
-        <v>0.19862967729568481</v>
+        <v>0.11386796087026596</v>
       </c>
       <c r="H10" s="1">
-        <v>99.705665588378906</v>
+        <v>99.710670471191406</v>
       </c>
       <c r="I10" s="1">
-        <v>90.025764465332031</v>
+        <v>91.425468444824219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>34009</v>
+        <v>20017</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="C11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D11" s="1">
-        <v>0.38681164383888245</v>
+        <v>0.42066857218742371</v>
       </c>
       <c r="E11" s="1">
-        <v>0.069756634533405304</v>
+        <v>0.0064287125132977962</v>
       </c>
       <c r="F11" s="1">
-        <v>5.5451593399047852</v>
+        <v>65.435897827148438</v>
       </c>
       <c r="G11" s="1">
-        <v>2.9368660392492529e-08</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>99.668876647949219</v>
+        <v>99.67449951171875</v>
       </c>
       <c r="I11" s="1">
-        <v>97.423629760742188</v>
+        <v>99.927642822265625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>13141</v>
+        <v>25003</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="D12" s="1">
-        <v>0.36096420884132385</v>
+        <v>0.40388906002044678</v>
       </c>
       <c r="E12" s="1">
-        <v>0.0061808452010154724</v>
+        <v>0.31419673562049866</v>
       </c>
       <c r="F12" s="1">
-        <v>58.400459289550781</v>
+        <v>1.2854654788970947</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>0.19862967729568481</v>
       </c>
       <c r="H12" s="1">
-        <v>99.632080078125</v>
+        <v>99.638336181640625</v>
       </c>
       <c r="I12" s="1">
-        <v>99.88958740234375</v>
+        <v>89.797393798828125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>36103</v>
+        <v>34009</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="C13" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="D13" s="1">
-        <v>0.35937702655792236</v>
+        <v>0.38681164383888245</v>
       </c>
       <c r="E13" s="1">
-        <v>0.13485310971736908</v>
+        <v>0.069756634533405304</v>
       </c>
       <c r="F13" s="1">
-        <v>2.6649518013000488</v>
+        <v>5.5451593399047852</v>
       </c>
       <c r="G13" s="1">
-        <v>0.0076999356970191002</v>
+        <v>2.9368660392492529e-08</v>
       </c>
       <c r="H13" s="1">
-        <v>99.595291137695313</v>
+        <v>99.6021728515625</v>
       </c>
       <c r="I13" s="1">
-        <v>95.178504943847656</v>
+        <v>97.178001403808594</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>37055</v>
+        <v>13141</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="C14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D14" s="1">
-        <v>0.35068994760513306</v>
+        <v>0.36096420884132385</v>
       </c>
       <c r="E14" s="1">
-        <v>0.074259854853153229</v>
+        <v>0.0061808452010154724</v>
       </c>
       <c r="F14" s="1">
-        <v>4.7224702835083008</v>
+        <v>58.400459289550781</v>
       </c>
       <c r="G14" s="1">
-        <v>2.3299714939639671e-06</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>99.558502197265625</v>
+        <v>99.566001892089844</v>
       </c>
       <c r="I14" s="1">
-        <v>97.018768310546875</v>
+        <v>99.85528564453125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>36105</v>
+        <v>36103</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="D15" s="1">
-        <v>0.34201312065124512</v>
+        <v>0.35937702655792236</v>
       </c>
       <c r="E15" s="1">
-        <v>0.21792246401309967</v>
+        <v>0.13485310971736908</v>
       </c>
       <c r="F15" s="1">
-        <v>1.5694257020950317</v>
+        <v>2.6649518013000488</v>
       </c>
       <c r="G15" s="1">
-        <v>0.11654877662658691</v>
+        <v>0.0076999356970191002</v>
       </c>
       <c r="H15" s="1">
-        <v>99.521705627441406</v>
+        <v>99.529838562011719</v>
       </c>
       <c r="I15" s="1">
-        <v>91.608390808105469</v>
+        <v>94.898696899414063</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>26007</v>
+        <v>37055</v>
       </c>
       <c r="B16" t="s">
-        <v>192</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D16" s="1">
-        <v>0.34037703275680542</v>
+        <v>0.35068994760513306</v>
       </c>
       <c r="E16" s="1">
-        <v>0.1587815135717392</v>
+        <v>0.074259854853153229</v>
       </c>
       <c r="F16" s="1">
-        <v>2.1436817646026611</v>
+        <v>4.7224702835083008</v>
       </c>
       <c r="G16" s="1">
-        <v>0.032058395445346832</v>
+        <v>2.3299714939639671e-06</v>
       </c>
       <c r="H16" s="1">
-        <v>99.484916687011719</v>
+        <v>99.493667602539063</v>
       </c>
       <c r="I16" s="1">
-        <v>93.96392822265625</v>
+        <v>96.780029296875</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>35033</v>
+        <v>36105</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D17" s="1">
-        <v>0.33095294237136841</v>
+        <v>0.34201312065124512</v>
       </c>
       <c r="E17" s="1">
-        <v>0.0060428320430219174</v>
+        <v>0.21792246401309967</v>
       </c>
       <c r="F17" s="1">
-        <v>54.767852783203125</v>
+        <v>1.5694257020950317</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>0.11654877662658691</v>
       </c>
       <c r="H17" s="1">
-        <v>99.4481201171875</v>
+        <v>99.457504272460938</v>
       </c>
       <c r="I17" s="1">
-        <v>99.779167175292969</v>
+        <v>91.353111267089844</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>47061</v>
+        <v>26007</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D18" s="1">
-        <v>0.31874310970306396</v>
+        <v>0.34037703275680542</v>
       </c>
       <c r="E18" s="1">
-        <v>0.1119995042681694</v>
+        <v>0.1587815135717392</v>
       </c>
       <c r="F18" s="1">
-        <v>2.845933198928833</v>
+        <v>2.1436817646026611</v>
       </c>
       <c r="G18" s="1">
-        <v>0.0044281482696533203</v>
+        <v>0.032058395445346832</v>
       </c>
       <c r="H18" s="1">
-        <v>99.411331176757813</v>
+        <v>99.421340942382813</v>
       </c>
       <c r="I18" s="1">
-        <v>95.472946166992188</v>
+        <v>93.70477294921875</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>12065</v>
+        <v>35033</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>206</v>
       </c>
       <c r="C19" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D19" s="1">
-        <v>0.31172969937324524</v>
+        <v>0.33095294237136841</v>
       </c>
       <c r="E19" s="1">
-        <v>0.0049780327826738358</v>
+        <v>0.0060428320430219174</v>
       </c>
       <c r="F19" s="1">
-        <v>62.621063232421875</v>
+        <v>54.767852783203125</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>99.374542236328125</v>
+        <v>99.385169982910156</v>
       </c>
       <c r="I19" s="1">
-        <v>99.9263916015625</v>
+        <v>99.746742248535156</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>17085</v>
+        <v>47061</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D20" s="1">
-        <v>0.30809041857719421</v>
+        <v>0.31874310970306396</v>
       </c>
       <c r="E20" s="1">
-        <v>0.16904479265213013</v>
+        <v>0.1119995042681694</v>
       </c>
       <c r="F20" s="1">
-        <v>1.8225371837615967</v>
+        <v>2.845933198928833</v>
       </c>
       <c r="G20" s="1">
-        <v>0.068373516201972962</v>
+        <v>0.0044281482696533203</v>
       </c>
       <c r="H20" s="1">
-        <v>99.337745666503906</v>
+        <v>99.349006652832031</v>
       </c>
       <c r="I20" s="1">
-        <v>92.749359130859375</v>
+        <v>95.188133239746094</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>6057</v>
+        <v>12065</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D21" s="1">
-        <v>0.30185693502426148</v>
+        <v>0.31172969937324524</v>
       </c>
       <c r="E21" s="1">
-        <v>0.06289903074502945</v>
+        <v>0.0049780327826738358</v>
       </c>
       <c r="F21" s="1">
-        <v>4.7990713119506836</v>
+        <v>62.621063232421875</v>
       </c>
       <c r="G21" s="1">
-        <v>1.5940303228489938e-06</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>99.300956726074219</v>
+        <v>99.312835693359375</v>
       </c>
       <c r="I21" s="1">
-        <v>97.055572509765625</v>
+        <v>99.891464233398438</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>13005</v>
+        <v>17085</v>
       </c>
       <c r="B22" t="s">
-        <v>205</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D22" s="1">
-        <v>0.29503542184829712</v>
+        <v>0.30809041857719421</v>
       </c>
       <c r="E22" s="1">
-        <v>0.12574708461761475</v>
+        <v>0.16904479265213013</v>
       </c>
       <c r="F22" s="1">
-        <v>2.3462605476379395</v>
+        <v>1.8225371837615967</v>
       </c>
       <c r="G22" s="1">
-        <v>0.01896284706890583</v>
+        <v>0.068373516201972962</v>
       </c>
       <c r="H22" s="1">
-        <v>99.264167785644531</v>
+        <v>99.27667236328125</v>
       </c>
       <c r="I22" s="1">
-        <v>94.552818298339844</v>
+        <v>92.510856628417969</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>29149</v>
+        <v>6057</v>
       </c>
       <c r="B23" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D23" s="1">
-        <v>0.29371407628059387</v>
+        <v>0.30185693502426148</v>
       </c>
       <c r="E23" s="1">
-        <v>0.02547084353864193</v>
+        <v>0.06289903074502945</v>
       </c>
       <c r="F23" s="1">
-        <v>11.531383514404297</v>
+        <v>4.7990713119506836</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>1.5940303228489938e-06</v>
       </c>
       <c r="H23" s="1">
-        <v>99.227371215820313</v>
+        <v>99.240509033203125</v>
       </c>
       <c r="I23" s="1">
-        <v>98.454177856445313</v>
+        <v>96.816207885742188</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>25001</v>
+        <v>13005</v>
       </c>
       <c r="B24" t="s">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C24" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D24" s="1">
-        <v>0.29252177476882935</v>
+        <v>0.29503542184829712</v>
       </c>
       <c r="E24" s="1">
-        <v>0.075748614966869354</v>
+        <v>0.12574708461761475</v>
       </c>
       <c r="F24" s="1">
-        <v>3.8617441654205322</v>
+        <v>2.3462605476379395</v>
       </c>
       <c r="G24" s="1">
-        <v>0.00011258042650297284</v>
+        <v>0.01896284706890583</v>
       </c>
       <c r="H24" s="1">
-        <v>99.190582275390625</v>
+        <v>99.204338073730469</v>
       </c>
       <c r="I24" s="1">
-        <v>96.503494262695313</v>
+        <v>94.283645629882813</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>30023</v>
+        <v>29149</v>
       </c>
       <c r="B25" t="s">
-        <v>207</v>
+        <v>133</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D25" s="1">
-        <v>0.27844804525375366</v>
+        <v>0.29371407628059387</v>
       </c>
       <c r="E25" s="1">
-        <v>0.14003899693489075</v>
+        <v>0.02547084353864193</v>
       </c>
       <c r="F25" s="1">
-        <v>1.9883607625961304</v>
+        <v>11.531383514404297</v>
       </c>
       <c r="G25" s="1">
-        <v>0.046771805733442307</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>99.153793334960938</v>
+        <v>99.168174743652344</v>
       </c>
       <c r="I25" s="1">
-        <v>93.448654174804688</v>
+        <v>98.263389587402344</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <v>40053</v>
+        <v>25001</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D26" s="1">
-        <v>0.27423545718193054</v>
+        <v>0.29252177476882935</v>
       </c>
       <c r="E26" s="1">
-        <v>0.0071755941025912762</v>
+        <v>0.075748614966869354</v>
       </c>
       <c r="F26" s="1">
-        <v>38.217803955078125</v>
+        <v>3.8617441654205322</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>0.00011258042650297284</v>
       </c>
       <c r="H26" s="1">
-        <v>99.116996765136719</v>
+        <v>99.132003784179688</v>
       </c>
       <c r="I26" s="1">
-        <v>99.705558776855469</v>
+        <v>96.237335205078125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1">
-        <v>13111</v>
+        <v>30023</v>
       </c>
       <c r="B27" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C27" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D27" s="1">
-        <v>0.27372995018959046</v>
+        <v>0.27844804525375366</v>
       </c>
       <c r="E27" s="1">
-        <v>0.14965757727622986</v>
+        <v>0.14003899693489075</v>
       </c>
       <c r="F27" s="1">
-        <v>1.8290417194366455</v>
+        <v>1.9883607625961304</v>
       </c>
       <c r="G27" s="1">
-        <v>0.067393355071544647</v>
+        <v>0.046771805733442307</v>
       </c>
       <c r="H27" s="1">
-        <v>99.080207824707031</v>
+        <v>99.095840454101563</v>
       </c>
       <c r="I27" s="1">
-        <v>92.933380126953125</v>
+        <v>93.198265075683594</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1">
-        <v>27001</v>
+        <v>31089</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="D28" s="1">
-        <v>0.27365186810493469</v>
+        <v>0.27770248055458069</v>
       </c>
       <c r="E28" s="1">
-        <v>0.032817408442497254</v>
+        <v>0.0076734600588679314</v>
       </c>
       <c r="F28" s="1">
-        <v>8.3386192321777344</v>
+        <v>36.189994812011719</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>99.043411254882813</v>
+        <v>99.059677124023438</v>
       </c>
       <c r="I28" s="1">
-        <v>98.04931640625</v>
+        <v>99.602027893066406</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1">
-        <v>51183</v>
+        <v>40053</v>
       </c>
       <c r="B29" t="s">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>142</v>
+        <v>234</v>
       </c>
       <c r="D29" s="1">
-        <v>0.26708310842514038</v>
+        <v>0.27423545718193054</v>
       </c>
       <c r="E29" s="1">
-        <v>0.0055307513102889061</v>
+        <v>0.0071755941025912762</v>
       </c>
       <c r="F29" s="1">
-        <v>48.290565490722656</v>
+        <v>38.217803955078125</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>99.006622314453125</v>
+        <v>99.023506164550781</v>
       </c>
       <c r="I29" s="1">
-        <v>99.742362976074219</v>
+        <v>99.674385070800781</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1">
-        <v>48317</v>
+        <v>13111</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>205</v>
       </c>
       <c r="C30" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D30" s="1">
-        <v>0.26359257102012634</v>
+        <v>0.27372995018959046</v>
       </c>
       <c r="E30" s="1">
-        <v>0.090121828019618988</v>
+        <v>0.14965757727622986</v>
       </c>
       <c r="F30" s="1">
-        <v>2.9248471260070801</v>
+        <v>1.8290417194366455</v>
       </c>
       <c r="G30" s="1">
-        <v>0.0034462548792362213</v>
+        <v>0.067393355071544647</v>
       </c>
       <c r="H30" s="1">
-        <v>98.969833374023438</v>
+        <v>98.987342834472656</v>
       </c>
       <c r="I30" s="1">
-        <v>95.656974792480469</v>
+        <v>92.691749572753906</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1">
-        <v>37199</v>
+        <v>27001</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D31" s="1">
-        <v>0.26072964072227478</v>
+        <v>0.27365186810493469</v>
       </c>
       <c r="E31" s="1">
-        <v>0.16243934631347656</v>
+        <v>0.032817408442497254</v>
       </c>
       <c r="F31" s="1">
-        <v>1.6050891876220703</v>
+        <v>8.3386192321777344</v>
       </c>
       <c r="G31" s="1">
-        <v>0.10847418010234833</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>98.933036804199219</v>
+        <v>98.951171875</v>
       </c>
       <c r="I31" s="1">
-        <v>91.79241943359375</v>
+        <v>97.865409851074219</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1">
-        <v>4013</v>
+        <v>51183</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>203</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D32" s="1">
-        <v>0.25536218285560608</v>
+        <v>0.26708310842514038</v>
       </c>
       <c r="E32" s="1">
-        <v>0.023844193667173386</v>
+        <v>0.0055307513102889061</v>
       </c>
       <c r="F32" s="1">
-        <v>10.709616661071777</v>
+        <v>48.290565490722656</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>98.896247863769531</v>
+        <v>98.915008544921875</v>
       </c>
       <c r="I32" s="1">
-        <v>98.343765258789063</v>
+        <v>99.710563659667969</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1">
-        <v>13133</v>
+        <v>48317</v>
       </c>
       <c r="B33" t="s">
-        <v>205</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D33" s="1">
-        <v>0.25517496466636658</v>
+        <v>0.26359257102012634</v>
       </c>
       <c r="E33" s="1">
-        <v>0.089638166129589081</v>
+        <v>0.090121828019618988</v>
       </c>
       <c r="F33" s="1">
-        <v>2.8467223644256592</v>
+        <v>2.9248471260070801</v>
       </c>
       <c r="G33" s="1">
-        <v>0.0044171866029500961</v>
+        <v>0.0034462548792362213</v>
       </c>
       <c r="H33" s="1">
-        <v>98.859458923339844</v>
+        <v>98.87884521484375</v>
       </c>
       <c r="I33" s="1">
-        <v>95.509750366210938</v>
+        <v>95.369033813476563</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1">
-        <v>1123</v>
+        <v>37199</v>
       </c>
       <c r="B34" t="s">
-        <v>208</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D34" s="1">
-        <v>0.24323663115501404</v>
+        <v>0.26072964072227478</v>
       </c>
       <c r="E34" s="1">
-        <v>0.12175042927265167</v>
+        <v>0.16243934631347656</v>
       </c>
       <c r="F34" s="1">
-        <v>1.997829794883728</v>
+        <v>1.6050891876220703</v>
       </c>
       <c r="G34" s="1">
-        <v>0.045735117048025131</v>
+        <v>0.10847418010234833</v>
       </c>
       <c r="H34" s="1">
-        <v>98.822662353515625</v>
+        <v>98.842674255371094</v>
       </c>
       <c r="I34" s="1">
-        <v>93.485458374023438</v>
+        <v>91.534011840820313</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1">
-        <v>13241</v>
+        <v>4013</v>
       </c>
       <c r="B35" t="s">
-        <v>205</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="D35" s="1">
-        <v>0.24305488169193268</v>
+        <v>0.25536218285560608</v>
       </c>
       <c r="E35" s="1">
-        <v>0.092782944440841675</v>
+        <v>0.023844193667173386</v>
       </c>
       <c r="F35" s="1">
-        <v>2.6196074485778809</v>
+        <v>10.709616661071777</v>
       </c>
       <c r="G35" s="1">
-        <v>0.008803103119134903</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>98.785873413085938</v>
+        <v>98.806510925292969</v>
       </c>
       <c r="I35" s="1">
-        <v>95.104896545410156</v>
+        <v>98.15484619140625</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1">
-        <v>13035</v>
+        <v>13133</v>
       </c>
       <c r="B36" t="s">
         <v>205</v>
       </c>
       <c r="C36" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D36" s="1">
-        <v>0.24290627241134644</v>
+        <v>0.25517496466636658</v>
       </c>
       <c r="E36" s="1">
-        <v>0.061875645071268082</v>
+        <v>0.089638166129589081</v>
       </c>
       <c r="F36" s="1">
-        <v>3.9257171154022217</v>
+        <v>2.8467223644256592</v>
       </c>
       <c r="G36" s="1">
-        <v>8.6471729446202517e-05</v>
+        <v>0.0044171866029500961</v>
       </c>
       <c r="H36" s="1">
-        <v>98.749076843261719</v>
+        <v>98.770339965820313</v>
       </c>
       <c r="I36" s="1">
-        <v>96.577110290527344</v>
+        <v>95.224311828613281</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1">
-        <v>35037</v>
+        <v>1123</v>
       </c>
       <c r="B37" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C37" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D37" s="1">
-        <v>0.2398313581943512</v>
+        <v>0.24323663115501404</v>
       </c>
       <c r="E37" s="1">
-        <v>0.0064301067031919956</v>
+        <v>0.12175042927265167</v>
       </c>
       <c r="F37" s="1">
-        <v>37.298191070556641</v>
+        <v>1.997829794883728</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>0.045735117048025131</v>
       </c>
       <c r="H37" s="1">
-        <v>98.712287902832031</v>
+        <v>98.734176635742188</v>
       </c>
       <c r="I37" s="1">
-        <v>99.668754577636719</v>
+        <v>93.234443664550781</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1">
-        <v>46025</v>
+        <v>13241</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="C38" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="D38" s="1">
-        <v>0.23947767913341522</v>
+        <v>0.24305488169193268</v>
       </c>
       <c r="E38" s="1">
-        <v>0.019847434014081955</v>
+        <v>0.092782944440841675</v>
       </c>
       <c r="F38" s="1">
-        <v>12.065926551818848</v>
+        <v>2.6196074485778809</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>0.008803103119134903</v>
       </c>
       <c r="H38" s="1">
-        <v>98.675498962402344</v>
+        <v>98.698013305664063</v>
       </c>
       <c r="I38" s="1">
-        <v>98.527786254882813</v>
+        <v>94.826339721679688</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1">
-        <v>30029</v>
+        <v>13035</v>
       </c>
       <c r="B39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C39" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D39" s="1">
-        <v>0.23923836648464203</v>
+        <v>0.24290627241134644</v>
       </c>
       <c r="E39" s="1">
-        <v>0.11796634644269943</v>
+        <v>0.061875645071268082</v>
       </c>
       <c r="F39" s="1">
-        <v>2.0280222892761231</v>
+        <v>3.9257171154022217</v>
       </c>
       <c r="G39" s="1">
-        <v>0.0425579734146595</v>
+        <v>8.6471729446202517e-05</v>
       </c>
       <c r="H39" s="1">
-        <v>98.638702392578125</v>
+        <v>98.661842346191406</v>
       </c>
       <c r="I39" s="1">
-        <v>93.669486999511719</v>
+        <v>96.3096923828125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1">
-        <v>5109</v>
+        <v>35037</v>
       </c>
       <c r="B40" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C40" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D40" s="1">
-        <v>0.23836736381053925</v>
+        <v>0.2398313581943512</v>
       </c>
       <c r="E40" s="1">
-        <v>0.17106682062149048</v>
+        <v>0.0064301067031919956</v>
       </c>
       <c r="F40" s="1">
-        <v>1.3934166431427002</v>
+        <v>37.298191070556641</v>
       </c>
       <c r="G40" s="1">
-        <v>0.16349384188652039</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>98.601913452148438</v>
+        <v>98.625679016113281</v>
       </c>
       <c r="I40" s="1">
-        <v>90.577842712402344</v>
+        <v>99.638206481933594</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1">
-        <v>20157</v>
+        <v>46025</v>
       </c>
       <c r="B41" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
-        <v>246</v>
+        <v>152</v>
       </c>
       <c r="D41" s="1">
-        <v>0.23697632551193237</v>
+        <v>0.23947767913341522</v>
       </c>
       <c r="E41" s="1">
-        <v>0.0085003608837723732</v>
+        <v>0.019847434014081955</v>
       </c>
       <c r="F41" s="1">
-        <v>27.878383636474609</v>
+        <v>12.065926551818848</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>98.56512451171875</v>
+        <v>98.589508056640625</v>
       </c>
       <c r="I41" s="1">
-        <v>99.447921752929688</v>
+        <v>98.371925354003906</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1">
-        <v>29211</v>
+        <v>30029</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>207</v>
       </c>
       <c r="C42" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D42" s="1">
-        <v>0.23478955030441284</v>
+        <v>0.23923836648464203</v>
       </c>
       <c r="E42" s="1">
-        <v>0.007844138890504837</v>
+        <v>0.11796634644269943</v>
       </c>
       <c r="F42" s="1">
-        <v>29.931844711303711</v>
+        <v>2.0280222892761231</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>0.0425579734146595</v>
       </c>
       <c r="H42" s="1">
-        <v>98.528327941894531</v>
+        <v>98.5533447265625</v>
       </c>
       <c r="I42" s="1">
-        <v>99.558334350585938</v>
+        <v>93.415336608886719</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <v>12071</v>
+        <v>5109</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>245</v>
       </c>
       <c r="D43" s="1">
-        <v>0.2340986579656601</v>
+        <v>0.23836736381053925</v>
       </c>
       <c r="E43" s="1">
-        <v>0.024382967501878739</v>
+        <v>0.17106682062149048</v>
       </c>
       <c r="F43" s="1">
-        <v>9.6009092330932617</v>
+        <v>1.3934166431427002</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>0.16349384188652039</v>
       </c>
       <c r="H43" s="1">
-        <v>98.491539001464844</v>
+        <v>98.517181396484375</v>
       </c>
       <c r="I43" s="1">
-        <v>98.233345031738281</v>
+        <v>90.340087890625</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <v>48019</v>
+        <v>20157</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="C44" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D44" s="1">
-        <v>0.23017928004264832</v>
+        <v>0.23697632551193237</v>
       </c>
       <c r="E44" s="1">
-        <v>0.034968111664056778</v>
+        <v>0.0085003608837723732</v>
       </c>
       <c r="F44" s="1">
-        <v>6.5825481414794922</v>
+        <v>27.878383636474609</v>
       </c>
       <c r="G44" s="1">
-        <v>4.6245229867736271e-11</v>
+        <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>98.454742431640625</v>
+        <v>98.481010437011719</v>
       </c>
       <c r="I44" s="1">
-        <v>97.607658386230469</v>
+        <v>99.348770141601563</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <v>5137</v>
+        <v>29211</v>
       </c>
       <c r="B45" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="D45" s="1">
-        <v>0.22867059707641602</v>
+        <v>0.23478955030441284</v>
       </c>
       <c r="E45" s="1">
-        <v>0.010562324896454811</v>
+        <v>0.007844138890504837</v>
       </c>
       <c r="F45" s="1">
-        <v>21.649646759033203</v>
+        <v>29.931844711303711</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>98.417953491210938</v>
+        <v>98.444847106933594</v>
       </c>
       <c r="I45" s="1">
-        <v>99.116676330566406</v>
+        <v>99.457305908203125</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1">
-        <v>48031</v>
+        <v>12071</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="C46" t="s">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="D46" s="1">
-        <v>0.22738555073738098</v>
+        <v>0.2340986579656601</v>
       </c>
       <c r="E46" s="1">
-        <v>0.14745301008224487</v>
+        <v>0.024382967501878739</v>
       </c>
       <c r="F46" s="1">
-        <v>1.5420882701873779</v>
+        <v>9.6009092330932617</v>
       </c>
       <c r="G46" s="1">
-        <v>0.12305214256048203</v>
+        <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>98.38116455078125</v>
+        <v>98.408676147460938</v>
       </c>
       <c r="I46" s="1">
-        <v>91.313949584960938</v>
+        <v>98.046310424804688</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1">
-        <v>17087</v>
+        <v>48019</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D47" s="1">
-        <v>0.22649125754833222</v>
+        <v>0.23017928004264832</v>
       </c>
       <c r="E47" s="1">
-        <v>0.0081684291362762451</v>
+        <v>0.034968111664056778</v>
       </c>
       <c r="F47" s="1">
-        <v>27.727640151977539</v>
+        <v>6.5825481414794922</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>4.6245229867736271e-11</v>
       </c>
       <c r="H47" s="1">
-        <v>98.344367980957031</v>
+        <v>98.372512817382813</v>
       </c>
       <c r="I47" s="1">
-        <v>99.411117553710938</v>
+        <v>97.39508056640625</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1">
-        <v>45053</v>
+        <v>5137</v>
       </c>
       <c r="B48" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C48" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D48" s="1">
-        <v>0.22480261325836182</v>
+        <v>0.22867059707641602</v>
       </c>
       <c r="E48" s="1">
-        <v>0.093074038624763489</v>
+        <v>0.010562324896454811</v>
       </c>
       <c r="F48" s="1">
-        <v>2.4153094291687012</v>
+        <v>21.649646759033203</v>
       </c>
       <c r="G48" s="1">
-        <v>0.015721846371889114</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>98.307579040527344</v>
+        <v>98.336349487304688</v>
       </c>
       <c r="I48" s="1">
-        <v>94.663230895996094</v>
+        <v>98.986976623535156</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1">
-        <v>12119</v>
+        <v>48031</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="C49" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D49" s="1">
-        <v>0.22302302718162537</v>
+        <v>0.22738555073738098</v>
       </c>
       <c r="E49" s="1">
-        <v>0.12605743110179901</v>
+        <v>0.14745301008224487</v>
       </c>
       <c r="F49" s="1">
-        <v>1.7692176103591919</v>
+        <v>1.5420882701873779</v>
       </c>
       <c r="G49" s="1">
-        <v>0.076857566833496094</v>
+        <v>0.12305214256048203</v>
       </c>
       <c r="H49" s="1">
-        <v>98.270790100097656</v>
+        <v>98.300178527832031</v>
       </c>
       <c r="I49" s="1">
-        <v>92.528526306152344</v>
+        <v>91.063674926757813</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1">
-        <v>40077</v>
+        <v>17087</v>
       </c>
       <c r="B50" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="D50" s="1">
-        <v>0.22161218523979187</v>
+        <v>0.22649125754833222</v>
       </c>
       <c r="E50" s="1">
-        <v>0.15940462052822113</v>
+        <v>0.0081684291362762451</v>
       </c>
       <c r="F50" s="1">
-        <v>1.390249490737915</v>
+        <v>27.727640151977539</v>
       </c>
       <c r="G50" s="1">
-        <v>0.16445313394069672</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>98.233993530273438</v>
+        <v>98.264015197753906</v>
       </c>
       <c r="I50" s="1">
-        <v>90.541038513183594</v>
+        <v>99.312591552734375</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1">
-        <v>32031</v>
+        <v>45053</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>209</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>251</v>
       </c>
       <c r="D51" s="1">
-        <v>0.22138416767120361</v>
+        <v>0.22480261325836182</v>
       </c>
       <c r="E51" s="1">
-        <v>0.047240827232599258</v>
+        <v>0.093074038624763489</v>
       </c>
       <c r="F51" s="1">
-        <v>4.6862888336181641</v>
+        <v>2.4153094291687012</v>
       </c>
       <c r="G51" s="1">
-        <v>2.7820358354802011e-06</v>
+        <v>0.015721846371889114</v>
       </c>
       <c r="H51" s="1">
-        <v>98.19720458984375</v>
+        <v>98.227851867675781</v>
       </c>
       <c r="I51" s="1">
-        <v>96.908355712890625</v>
+        <v>94.392189025878906</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1">
-        <v>21175</v>
+        <v>12119</v>
       </c>
       <c r="B52" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D52" s="1">
-        <v>0.21382062137126923</v>
+        <v>0.22302302718162537</v>
       </c>
       <c r="E52" s="1">
-        <v>0.0069077359512448311</v>
+        <v>0.12605743110179901</v>
       </c>
       <c r="F52" s="1">
-        <v>30.953792572021484</v>
+        <v>1.7692176103591919</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>0.076857566833496094</v>
       </c>
       <c r="H52" s="1">
-        <v>98.160415649414063</v>
+        <v>98.191680908203125</v>
       </c>
       <c r="I52" s="1">
-        <v>99.595138549804688</v>
+        <v>92.257598876953125</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1">
-        <v>12115</v>
+        <v>40077</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="D53" s="1">
-        <v>0.21304696798324585</v>
+        <v>0.22161218523979187</v>
       </c>
       <c r="E53" s="1">
-        <v>0.039894048124551773</v>
+        <v>0.15940462052822113</v>
       </c>
       <c r="F53" s="1">
-        <v>5.3403196334838867</v>
+        <v>1.390249490737915</v>
       </c>
       <c r="G53" s="1">
-        <v>9.2782848071237822e-08</v>
+        <v>0.16445313394069672</v>
       </c>
       <c r="H53" s="1">
-        <v>98.123619079589844</v>
+        <v>98.155517578125</v>
       </c>
       <c r="I53" s="1">
-        <v>97.350021362304688</v>
+        <v>90.303909301757813</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1">
-        <v>16077</v>
+        <v>32031</v>
       </c>
       <c r="B54" t="s">
-        <v>202</v>
+        <v>127</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>139</v>
       </c>
       <c r="D54" s="1">
-        <v>0.21255423128604889</v>
+        <v>0.22138416767120361</v>
       </c>
       <c r="E54" s="1">
-        <v>0.0084525709971785545</v>
+        <v>0.047240827232599258</v>
       </c>
       <c r="F54" s="1">
-        <v>25.146696090698242</v>
+        <v>4.6862888336181641</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>2.7820358354802011e-06</v>
       </c>
       <c r="H54" s="1">
-        <v>98.086830139160156</v>
+        <v>98.119346618652344</v>
       </c>
       <c r="I54" s="1">
-        <v>99.337501525878906</v>
+        <v>96.671493530273438</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1">
-        <v>8049</v>
+        <v>20193</v>
       </c>
       <c r="B55" t="s">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="C55" t="s">
-        <v>255</v>
+        <v>665</v>
       </c>
       <c r="D55" s="1">
-        <v>0.2124524712562561</v>
+        <v>0.21395087242126465</v>
       </c>
       <c r="E55" s="1">
-        <v>0.042266871780157089</v>
+        <v>0.011292941868305206</v>
       </c>
       <c r="F55" s="1">
-        <v>5.0264534950256348</v>
+        <v>18.945539474487305</v>
       </c>
       <c r="G55" s="1">
-        <v>4.9963358605964459e-07</v>
+        <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>98.050033569335938</v>
+        <v>98.083183288574219</v>
       </c>
       <c r="I55" s="1">
-        <v>97.239601135253906</v>
+        <v>98.806076049804688</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1">
-        <v>20107</v>
+        <v>21175</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C56" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D56" s="1">
-        <v>0.21158680319786072</v>
+        <v>0.21382062137126923</v>
       </c>
       <c r="E56" s="1">
-        <v>0.11358851194381714</v>
+        <v>0.0069077359512448311</v>
       </c>
       <c r="F56" s="1">
-        <v>1.8627482652664185</v>
+        <v>30.953792572021484</v>
       </c>
       <c r="G56" s="1">
-        <v>0.062497690320014954</v>
+        <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>98.01324462890625</v>
+        <v>98.047019958496094</v>
       </c>
       <c r="I56" s="1">
-        <v>93.043800354003906</v>
+        <v>99.493484497070313</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1">
-        <v>12021</v>
+        <v>12115</v>
       </c>
       <c r="B57" t="s">
         <v>129</v>
       </c>
       <c r="C57" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D57" s="1">
-        <v>0.21074710786342621</v>
+        <v>0.21304696798324585</v>
       </c>
       <c r="E57" s="1">
-        <v>0.040968708693981171</v>
+        <v>0.039894048124551773</v>
       </c>
       <c r="F57" s="1">
-        <v>5.144099235534668</v>
+        <v>5.3403196334838867</v>
       </c>
       <c r="G57" s="1">
-        <v>2.6880741188506363e-07</v>
+        <v>9.2782848071237822e-08</v>
       </c>
       <c r="H57" s="1">
-        <v>97.976455688476563</v>
+        <v>98.010848999023438</v>
       </c>
       <c r="I57" s="1">
-        <v>97.313209533691406</v>
+        <v>97.105644226074219</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1">
-        <v>53033</v>
+        <v>16077</v>
       </c>
       <c r="B58" t="s">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="C58" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
       <c r="D58" s="1">
-        <v>0.20595867931842804</v>
+        <v>0.21255423128604889</v>
       </c>
       <c r="E58" s="1">
-        <v>0.041703503578901291</v>
+        <v>0.0084525709971785545</v>
       </c>
       <c r="F58" s="1">
-        <v>4.9386420249938965</v>
+        <v>25.146696090698242</v>
       </c>
       <c r="G58" s="1">
-        <v>7.8668472269782797e-07</v>
+        <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>97.939659118652344</v>
+        <v>97.974685668945313</v>
       </c>
       <c r="I58" s="1">
-        <v>97.165992736816406</v>
+        <v>99.240234375</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1">
-        <v>13283</v>
+        <v>8049</v>
       </c>
       <c r="B59" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C59" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D59" s="1">
-        <v>0.20553411543369293</v>
+        <v>0.2124524712562561</v>
       </c>
       <c r="E59" s="1">
-        <v>0.0076912203803658485</v>
+        <v>0.042266871780157089</v>
       </c>
       <c r="F59" s="1">
-        <v>26.723213195800781</v>
+        <v>5.0264534950256348</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>4.9963358605964459e-07</v>
       </c>
       <c r="H59" s="1">
-        <v>97.902870178222656</v>
+        <v>97.938514709472656</v>
       </c>
       <c r="I59" s="1">
-        <v>99.374313354492188</v>
+        <v>96.997108459472656</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1">
-        <v>29013</v>
+        <v>20107</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="C60" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D60" s="1">
-        <v>0.20489074289798737</v>
+        <v>0.21158680319786072</v>
       </c>
       <c r="E60" s="1">
-        <v>0.090940475463867188</v>
+        <v>0.11358851194381714</v>
       </c>
       <c r="F60" s="1">
-        <v>2.2530202865600586</v>
+        <v>1.8627482652664185</v>
       </c>
       <c r="G60" s="1">
-        <v>0.024257870391011238</v>
+        <v>0.062497690320014954</v>
       </c>
       <c r="H60" s="1">
-        <v>97.866081237792969</v>
+        <v>97.902351379394531</v>
       </c>
       <c r="I60" s="1">
-        <v>94.368789672851563</v>
+        <v>92.80029296875</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1">
-        <v>19195</v>
+        <v>12021</v>
       </c>
       <c r="B61" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>259</v>
+        <v>141</v>
       </c>
       <c r="D61" s="1">
-        <v>0.20450815558433533</v>
+        <v>0.21074710786342621</v>
       </c>
       <c r="E61" s="1">
-        <v>0.043397333472967148</v>
+        <v>0.040968708693981171</v>
       </c>
       <c r="F61" s="1">
-        <v>4.7124590873718262</v>
+        <v>5.144099235534668</v>
       </c>
       <c r="G61" s="1">
-        <v>2.4474522888340289e-06</v>
+        <v>2.6880741188506363e-07</v>
       </c>
       <c r="H61" s="1">
-        <v>97.82928466796875</v>
+        <v>97.866188049316406</v>
       </c>
       <c r="I61" s="1">
-        <v>96.945159912109375</v>
+        <v>97.069465637207031</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1">
-        <v>33003</v>
+        <v>53033</v>
       </c>
       <c r="B62" t="s">
-        <v>211</v>
+        <v>131</v>
       </c>
       <c r="C62" t="s">
-        <v>260</v>
+        <v>147</v>
       </c>
       <c r="D62" s="1">
-        <v>0.19851087033748627</v>
+        <v>0.20595867931842804</v>
       </c>
       <c r="E62" s="1">
-        <v>0.13798920810222626</v>
+        <v>0.041703503578901291</v>
       </c>
       <c r="F62" s="1">
-        <v>1.4385970830917358</v>
+        <v>4.9386420249938965</v>
       </c>
       <c r="G62" s="1">
-        <v>0.15026471018791199</v>
+        <v>7.8668472269782797e-07</v>
       </c>
       <c r="H62" s="1">
-        <v>97.792495727539063</v>
+        <v>97.83001708984375</v>
       </c>
       <c r="I62" s="1">
-        <v>90.798675537109375</v>
+        <v>96.92474365234375</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1">
-        <v>13123</v>
+        <v>13283</v>
       </c>
       <c r="B63" t="s">
         <v>205</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D63" s="1">
-        <v>0.19808979332447052</v>
+        <v>0.20553411543369293</v>
       </c>
       <c r="E63" s="1">
-        <v>0.093611001968383789</v>
+        <v>0.0076912203803658485</v>
       </c>
       <c r="F63" s="1">
-        <v>2.1160953044891357</v>
+        <v>26.723213195800781</v>
       </c>
       <c r="G63" s="1">
-        <v>0.034336701035499573</v>
+        <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>97.755699157714844</v>
+        <v>97.793853759765625</v>
       </c>
       <c r="I63" s="1">
-        <v>93.89031982421875</v>
+        <v>99.276412963867188</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1">
-        <v>5049</v>
+        <v>29013</v>
       </c>
       <c r="B64" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D64" s="1">
-        <v>0.19724190235137939</v>
+        <v>0.20489074289798737</v>
       </c>
       <c r="E64" s="1">
-        <v>0.068888060748577118</v>
+        <v>0.090940475463867188</v>
       </c>
       <c r="F64" s="1">
-        <v>2.8632233142852783</v>
+        <v>2.2530202865600586</v>
       </c>
       <c r="G64" s="1">
-        <v>0.0041935490444302559</v>
+        <v>0.024257870391011238</v>
       </c>
       <c r="H64" s="1">
-        <v>97.718910217285156</v>
+        <v>97.757682800292969</v>
       </c>
       <c r="I64" s="1">
-        <v>95.546562194824219</v>
+        <v>94.102752685546875</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1">
-        <v>48013</v>
+        <v>19195</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="C65" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D65" s="1">
-        <v>0.19621415436267853</v>
+        <v>0.20450815558433533</v>
       </c>
       <c r="E65" s="1">
-        <v>0.097017161548137665</v>
+        <v>0.043397333472967148</v>
       </c>
       <c r="F65" s="1">
-        <v>2.0224685668945313</v>
+        <v>4.7124590873718262</v>
       </c>
       <c r="G65" s="1">
-        <v>0.043127968907356262</v>
+        <v>2.4474522888340289e-06</v>
       </c>
       <c r="H65" s="1">
-        <v>97.682121276855469</v>
+        <v>97.721519470214844</v>
       </c>
       <c r="I65" s="1">
-        <v>93.632682800292969</v>
+        <v>96.707672119140625</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1">
-        <v>36111</v>
+        <v>33003</v>
       </c>
       <c r="B66" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="C66" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D66" s="1">
-        <v>0.19530317187309265</v>
+        <v>0.19851087033748627</v>
       </c>
       <c r="E66" s="1">
-        <v>0.10041553527116776</v>
+        <v>0.13798920810222626</v>
       </c>
       <c r="F66" s="1">
-        <v>1.944949746131897</v>
+        <v>1.4385970830917358</v>
       </c>
       <c r="G66" s="1">
-        <v>0.051781028509140015</v>
+        <v>0.15026471018791199</v>
       </c>
       <c r="H66" s="1">
-        <v>97.64532470703125</v>
+        <v>97.685356140136719</v>
       </c>
       <c r="I66" s="1">
-        <v>93.301437377929688</v>
+        <v>90.557167053222656</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1">
-        <v>27031</v>
+        <v>13123</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="C67" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D67" s="1">
-        <v>0.19034530222415924</v>
+        <v>0.19808979332447052</v>
       </c>
       <c r="E67" s="1">
-        <v>0.21620504558086395</v>
+        <v>0.093611001968383789</v>
       </c>
       <c r="F67" s="1">
-        <v>0.88039249181747437</v>
+        <v>2.1160953044891357</v>
       </c>
       <c r="G67" s="1">
-        <v>0.37864673137664795</v>
+        <v>0.034336701035499573</v>
       </c>
       <c r="H67" s="1">
-        <v>97.608535766601563</v>
+        <v>97.649185180664063</v>
       </c>
       <c r="I67" s="1">
-        <v>87.449394226074219</v>
+        <v>93.632415771484375</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1">
-        <v>42101</v>
+        <v>5049</v>
       </c>
       <c r="B68" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>262</v>
       </c>
       <c r="D68" s="1">
-        <v>0.18830960988998413</v>
+        <v>0.19724190235137939</v>
       </c>
       <c r="E68" s="1">
-        <v>0.030858449637889862</v>
+        <v>0.068888060748577118</v>
       </c>
       <c r="F68" s="1">
-        <v>6.1023678779602051</v>
+        <v>2.8632233142852783</v>
       </c>
       <c r="G68" s="1">
-        <v>1.0450849075027691e-09</v>
+        <v>0.0041935490444302559</v>
       </c>
       <c r="H68" s="1">
-        <v>97.571746826171875</v>
+        <v>97.613021850585938</v>
       </c>
       <c r="I68" s="1">
-        <v>97.534042358398438</v>
+        <v>95.260490417480469</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1">
-        <v>12089</v>
+        <v>48013</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D69" s="1">
-        <v>0.18766343593597412</v>
+        <v>0.19621415436267853</v>
       </c>
       <c r="E69" s="1">
-        <v>0.068499520421028137</v>
+        <v>0.097017161548137665</v>
       </c>
       <c r="F69" s="1">
-        <v>2.7396314144134522</v>
+        <v>2.0224685668945313</v>
       </c>
       <c r="G69" s="1">
-        <v>0.0061508119106292725</v>
+        <v>0.043127968907356262</v>
       </c>
       <c r="H69" s="1">
-        <v>97.534950256347656</v>
+        <v>97.576850891113281</v>
       </c>
       <c r="I69" s="1">
-        <v>95.325729370117188</v>
+        <v>93.379158020019531</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1">
-        <v>48053</v>
+        <v>36111</v>
       </c>
       <c r="B70" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D70" s="1">
-        <v>0.18735915422439575</v>
+        <v>0.19530317187309265</v>
       </c>
       <c r="E70" s="1">
-        <v>0.15401798486709595</v>
+        <v>0.10041553527116776</v>
       </c>
       <c r="F70" s="1">
-        <v>1.2164758443832397</v>
+        <v>1.944949746131897</v>
       </c>
       <c r="G70" s="1">
-        <v>0.22380371391773224</v>
+        <v>0.051781028509140015</v>
       </c>
       <c r="H70" s="1">
-        <v>97.498161315917969</v>
+        <v>97.540687561035156</v>
       </c>
       <c r="I70" s="1">
-        <v>89.473686218261719</v>
+        <v>93.053543090820313</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1">
-        <v>26129</v>
+        <v>27031</v>
       </c>
       <c r="B71" t="s">
-        <v>192</v>
+        <v>101</v>
       </c>
       <c r="C71" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D71" s="1">
-        <v>0.1870216578245163</v>
+        <v>0.19034530222415924</v>
       </c>
       <c r="E71" s="1">
-        <v>0.12121649831533432</v>
+        <v>0.21620504558086395</v>
       </c>
       <c r="F71" s="1">
-        <v>1.5428729057312012</v>
+        <v>0.88039249181747437</v>
       </c>
       <c r="G71" s="1">
-        <v>0.12286161631345749</v>
+        <v>0.37864673137664795</v>
       </c>
       <c r="H71" s="1">
-        <v>97.461372375488281</v>
+        <v>97.504524230957031</v>
       </c>
       <c r="I71" s="1">
-        <v>91.350753784179688</v>
+        <v>87.26483154296875</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1">
-        <v>8051</v>
+        <v>42101</v>
       </c>
       <c r="B72" t="s">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="C72" t="s">
-        <v>269</v>
+        <v>148</v>
       </c>
       <c r="D72" s="1">
-        <v>0.18589775264263153</v>
+        <v>0.18830960988998413</v>
       </c>
       <c r="E72" s="1">
-        <v>0.095722153782844544</v>
+        <v>0.030858449637889862</v>
       </c>
       <c r="F72" s="1">
-        <v>1.9420557022094727</v>
+        <v>6.1023678779602051</v>
       </c>
       <c r="G72" s="1">
-        <v>0.052130356431007385</v>
+        <v>1.0450849075027691e-09</v>
       </c>
       <c r="H72" s="1">
-        <v>97.424575805664063</v>
+        <v>97.468353271484375</v>
       </c>
       <c r="I72" s="1">
-        <v>93.264633178710938</v>
+        <v>97.322723388671875</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1">
-        <v>47185</v>
+        <v>12089</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D73" s="1">
-        <v>0.18495158851146698</v>
+        <v>0.18766343593597412</v>
       </c>
       <c r="E73" s="1">
-        <v>0.055880848318338394</v>
+        <v>0.068499520421028137</v>
       </c>
       <c r="F73" s="1">
-        <v>3.3097491264343262</v>
+        <v>2.7396314144134522</v>
       </c>
       <c r="G73" s="1">
-        <v>0.00093379628378897905</v>
+        <v>0.0061508119106292725</v>
       </c>
       <c r="H73" s="1">
-        <v>97.387786865234375</v>
+        <v>97.43218994140625</v>
       </c>
       <c r="I73" s="1">
-        <v>96.245857238769531</v>
+        <v>95.043418884277344</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1">
-        <v>8003</v>
+        <v>48053</v>
       </c>
       <c r="B74" t="s">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="C74" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D74" s="1">
-        <v>0.18326082825660706</v>
+        <v>0.18735915422439575</v>
       </c>
       <c r="E74" s="1">
-        <v>0.15023835003376007</v>
+        <v>0.15401798486709595</v>
       </c>
       <c r="F74" s="1">
-        <v>1.219800591468811</v>
+        <v>1.2164758443832397</v>
       </c>
       <c r="G74" s="1">
-        <v>0.222540482878685</v>
+        <v>0.22380371391773224</v>
       </c>
       <c r="H74" s="1">
-        <v>97.350990295410156</v>
+        <v>97.396018981933594</v>
       </c>
       <c r="I74" s="1">
-        <v>89.510490417480469</v>
+        <v>89.25469970703125</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1">
-        <v>48473</v>
+        <v>26129</v>
       </c>
       <c r="B75" t="s">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D75" s="1">
-        <v>0.18152984976768494</v>
+        <v>0.1870216578245163</v>
       </c>
       <c r="E75" s="1">
-        <v>0.16274566948413849</v>
+        <v>0.12121649831533432</v>
       </c>
       <c r="F75" s="1">
-        <v>1.1154204607009888</v>
+        <v>1.5428729057312012</v>
       </c>
       <c r="G75" s="1">
-        <v>0.26467028260231018</v>
+        <v>0.12286161631345749</v>
       </c>
       <c r="H75" s="1">
-        <v>97.314201354980469</v>
+        <v>97.359855651855469</v>
       </c>
       <c r="I75" s="1">
-        <v>88.700775146484375</v>
+        <v>91.099853515625</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1">
-        <v>47027</v>
+        <v>8051</v>
       </c>
       <c r="B76" t="s">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="C76" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D76" s="1">
-        <v>0.18095017969608307</v>
+        <v>0.18589775264263153</v>
       </c>
       <c r="E76" s="1">
-        <v>0.14622843265533447</v>
+        <v>0.095722153782844544</v>
       </c>
       <c r="F76" s="1">
-        <v>1.2374486923217773</v>
+        <v>1.9420557022094727</v>
       </c>
       <c r="G76" s="1">
-        <v>0.21592055261135101</v>
+        <v>0.052130356431007385</v>
       </c>
       <c r="H76" s="1">
-        <v>97.277412414550781</v>
+        <v>97.323692321777344</v>
       </c>
       <c r="I76" s="1">
-        <v>89.620903015136719</v>
+        <v>93.017364501953125</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1">
-        <v>13085</v>
+        <v>47185</v>
       </c>
       <c r="B77" t="s">
-        <v>205</v>
+        <v>128</v>
       </c>
       <c r="C77" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D77" s="1">
-        <v>0.18044465780258179</v>
+        <v>0.18495158851146698</v>
       </c>
       <c r="E77" s="1">
-        <v>0.069176062941551208</v>
+        <v>0.055880848318338394</v>
       </c>
       <c r="F77" s="1">
-        <v>2.6084840297698975</v>
+        <v>3.3097491264343262</v>
       </c>
       <c r="G77" s="1">
-        <v>0.0090944254770874977</v>
+        <v>0.00093379628378897905</v>
       </c>
       <c r="H77" s="1">
-        <v>97.240615844726563</v>
+        <v>97.287521362304688</v>
       </c>
       <c r="I77" s="1">
-        <v>95.031288146972656</v>
+        <v>95.947898864746094</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1">
-        <v>47071</v>
+        <v>8003</v>
       </c>
       <c r="B78" t="s">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="C78" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D78" s="1">
-        <v>0.17726893723011017</v>
+        <v>0.18326082825660706</v>
       </c>
       <c r="E78" s="1">
-        <v>0.11629468202590942</v>
+        <v>0.15023835003376007</v>
       </c>
       <c r="F78" s="1">
-        <v>1.5243082046508789</v>
+        <v>1.219800591468811</v>
       </c>
       <c r="G78" s="1">
-        <v>0.12743173539638519</v>
+        <v>0.222540482878685</v>
       </c>
       <c r="H78" s="1">
-        <v>97.203826904296875</v>
+        <v>97.251358032226563</v>
       </c>
       <c r="I78" s="1">
-        <v>91.277145385742188</v>
+        <v>89.290885925292969</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1">
-        <v>10005</v>
+        <v>48473</v>
       </c>
       <c r="B79" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C79" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="D79" s="1">
-        <v>0.17688572406768799</v>
+        <v>0.18152984976768494</v>
       </c>
       <c r="E79" s="1">
-        <v>0.042678680270910263</v>
+        <v>0.16274566948413849</v>
       </c>
       <c r="F79" s="1">
-        <v>4.14459228515625</v>
+        <v>1.1154204607009888</v>
       </c>
       <c r="G79" s="1">
-        <v>3.4041884646285325e-05</v>
+        <v>0.26467028260231018</v>
       </c>
       <c r="H79" s="1">
-        <v>97.167037963867188</v>
+        <v>97.215187072753906</v>
       </c>
       <c r="I79" s="1">
-        <v>96.687522888183594</v>
+        <v>88.49493408203125</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1">
-        <v>29041</v>
+        <v>47027</v>
       </c>
       <c r="B80" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C80" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D80" s="1">
-        <v>0.17621800303459168</v>
+        <v>0.18095017969608307</v>
       </c>
       <c r="E80" s="1">
-        <v>0.0055939778685569763</v>
+        <v>0.14622843265533447</v>
       </c>
       <c r="F80" s="1">
-        <v>31.501377105712891</v>
+        <v>1.2374486923217773</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>0.21592055261135101</v>
       </c>
       <c r="H80" s="1">
-        <v>97.130241394042969</v>
+        <v>97.179023742675781</v>
       </c>
       <c r="I80" s="1">
-        <v>99.631950378417969</v>
+        <v>89.399421691894531</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1">
-        <v>29087</v>
+        <v>20201</v>
       </c>
       <c r="B81" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="C81" t="s">
-        <v>277</v>
+        <v>169</v>
       </c>
       <c r="D81" s="1">
-        <v>0.17484112083911896</v>
+        <v>0.18078343570232391</v>
       </c>
       <c r="E81" s="1">
-        <v>0.0078979777172207832</v>
+        <v>0.0051077855750918388</v>
       </c>
       <c r="F81" s="1">
-        <v>22.137454986572266</v>
+        <v>35.393699645996094</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
       </c>
       <c r="H81" s="1">
-        <v>97.093452453613281</v>
+        <v>97.142860412597656</v>
       </c>
       <c r="I81" s="1">
-        <v>99.153480529785156</v>
+        <v>99.565849304199219</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1">
-        <v>36039</v>
+        <v>13085</v>
       </c>
       <c r="B82" t="s">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="C82" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="D82" s="1">
-        <v>0.17371524870395661</v>
+        <v>0.18044465780258179</v>
       </c>
       <c r="E82" s="1">
-        <v>0.097507096827030182</v>
+        <v>0.069176062941551208</v>
       </c>
       <c r="F82" s="1">
-        <v>1.7815651893615723</v>
+        <v>2.6084840297698975</v>
       </c>
       <c r="G82" s="1">
-        <v>0.074820168316364288</v>
+        <v>0.0090944254770874977</v>
       </c>
       <c r="H82" s="1">
-        <v>97.056655883789063</v>
+        <v>97.106689453125</v>
       </c>
       <c r="I82" s="1">
-        <v>92.565330505371094</v>
+        <v>94.753982543945313</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1">
-        <v>6025</v>
+        <v>47071</v>
       </c>
       <c r="B83" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C83" t="s">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="D83" s="1">
-        <v>0.17177577316761017</v>
+        <v>0.17726893723011017</v>
       </c>
       <c r="E83" s="1">
-        <v>0.035536270588636398</v>
+        <v>0.11629468202590942</v>
       </c>
       <c r="F83" s="1">
-        <v>4.8338155746459961</v>
+        <v>1.5243082046508789</v>
       </c>
       <c r="G83" s="1">
-        <v>1.3394068218985922e-06</v>
+        <v>0.12743173539638519</v>
       </c>
       <c r="H83" s="1">
-        <v>97.019866943359375</v>
+        <v>97.070526123046875</v>
       </c>
       <c r="I83" s="1">
-        <v>97.092384338378906</v>
+        <v>91.027496337890625</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1">
-        <v>36113</v>
+        <v>10005</v>
       </c>
       <c r="B84" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C84" t="s">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="D84" s="1">
-        <v>0.17172312736511231</v>
+        <v>0.17688572406768799</v>
       </c>
       <c r="E84" s="1">
-        <v>0.15432940423488617</v>
+        <v>0.042678680270910263</v>
       </c>
       <c r="F84" s="1">
-        <v>1.1127052307128906</v>
+        <v>4.14459228515625</v>
       </c>
       <c r="G84" s="1">
-        <v>0.26583504676818848</v>
+        <v>3.4041884646285325e-05</v>
       </c>
       <c r="H84" s="1">
-        <v>96.983078002929688</v>
+        <v>97.034355163574219</v>
       </c>
       <c r="I84" s="1">
-        <v>88.663970947265625</v>
+        <v>96.418235778808594</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1">
-        <v>16001</v>
+        <v>29041</v>
       </c>
       <c r="B85" t="s">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="C85" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D85" s="1">
-        <v>0.17050167918205261</v>
+        <v>0.17621800303459168</v>
       </c>
       <c r="E85" s="1">
-        <v>0.03413931280374527</v>
+        <v>0.0055939778685569763</v>
       </c>
       <c r="F85" s="1">
-        <v>4.9942913055419922</v>
+        <v>31.501377105712891</v>
       </c>
       <c r="G85" s="1">
-        <v>5.9052206324849976e-07</v>
+        <v>0</v>
       </c>
       <c r="H85" s="1">
-        <v>96.946281433105469</v>
+        <v>96.998191833496094</v>
       </c>
       <c r="I85" s="1">
-        <v>97.202796936035156</v>
+        <v>99.529670715332031</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1">
-        <v>12081</v>
+        <v>29087</v>
       </c>
       <c r="B86" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C86" t="s">
-        <v>149</v>
+        <v>277</v>
       </c>
       <c r="D86" s="1">
-        <v>0.17033989727497101</v>
+        <v>0.17484112083911896</v>
       </c>
       <c r="E86" s="1">
-        <v>0.0436834916472435</v>
+        <v>0.0078979777172207832</v>
       </c>
       <c r="F86" s="1">
-        <v>3.8994112014770508</v>
+        <v>22.137454986572266</v>
       </c>
       <c r="G86" s="1">
-        <v>9.6426891104783863e-05</v>
+        <v>0</v>
       </c>
       <c r="H86" s="1">
-        <v>96.909492492675781</v>
+        <v>96.962028503417969</v>
       </c>
       <c r="I86" s="1">
-        <v>96.540298461914063</v>
+        <v>99.023155212402344</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1">
-        <v>48299</v>
+        <v>48197</v>
       </c>
       <c r="B87" t="s">
         <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>280</v>
+        <v>666</v>
       </c>
       <c r="D87" s="1">
-        <v>0.16995133459568024</v>
+        <v>0.17461639642715454</v>
       </c>
       <c r="E87" s="1">
-        <v>0.069826669991016388</v>
+        <v>0.0069649661891162395</v>
       </c>
       <c r="F87" s="1">
-        <v>2.4339029788970947</v>
+        <v>25.070674896240234</v>
       </c>
       <c r="G87" s="1">
-        <v>0.01493699848651886</v>
+        <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>96.872703552246094</v>
+        <v>96.925857543945313</v>
       </c>
       <c r="I87" s="1">
-        <v>94.700035095214844</v>
+        <v>99.204055786132813</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1">
-        <v>6051</v>
+        <v>36039</v>
       </c>
       <c r="B88" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C88" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="D88" s="1">
-        <v>0.16874884068965912</v>
+        <v>0.17371524870395661</v>
       </c>
       <c r="E88" s="1">
-        <v>0.078401677310466766</v>
+        <v>0.097507096827030182</v>
       </c>
       <c r="F88" s="1">
-        <v>2.152362585067749</v>
+        <v>1.7815651893615723</v>
       </c>
       <c r="G88" s="1">
-        <v>0.031368806958198547</v>
+        <v>0.074820168316364288</v>
       </c>
       <c r="H88" s="1">
-        <v>96.835906982421875</v>
+        <v>96.889694213867188</v>
       </c>
       <c r="I88" s="1">
-        <v>94.111152648925781</v>
+        <v>92.293777465820313</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1">
-        <v>26119</v>
+        <v>6025</v>
       </c>
       <c r="B89" t="s">
-        <v>192</v>
+        <v>99</v>
       </c>
       <c r="C89" t="s">
-        <v>282</v>
+        <v>150</v>
       </c>
       <c r="D89" s="1">
-        <v>0.16813819110393524</v>
+        <v>0.17177577316761017</v>
       </c>
       <c r="E89" s="1">
-        <v>0.10402067005634308</v>
+        <v>0.035536270588636398</v>
       </c>
       <c r="F89" s="1">
-        <v>1.6163921356201172</v>
+        <v>4.8338155746459961</v>
       </c>
       <c r="G89" s="1">
-        <v>0.10600955784320831</v>
+        <v>1.3394068218985922e-06</v>
       </c>
       <c r="H89" s="1">
-        <v>96.799118041992188</v>
+        <v>96.853523254394531</v>
       </c>
       <c r="I89" s="1">
-        <v>91.8292236328125</v>
+        <v>96.852386474609375</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1">
-        <v>32005</v>
+        <v>36113</v>
       </c>
       <c r="B90" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C90" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D90" s="1">
-        <v>0.16632890701293945</v>
+        <v>0.17172312736511231</v>
       </c>
       <c r="E90" s="1">
-        <v>0.1293562650680542</v>
+        <v>0.15432940423488617</v>
       </c>
       <c r="F90" s="1">
-        <v>1.2858202457427979</v>
+        <v>1.1127052307128906</v>
       </c>
       <c r="G90" s="1">
-        <v>0.19850580394268036</v>
+        <v>0.26583504676818848</v>
       </c>
       <c r="H90" s="1">
-        <v>96.762321472167969</v>
+        <v>96.817359924316406</v>
       </c>
       <c r="I90" s="1">
-        <v>90.062568664550781</v>
+        <v>88.458755493164063</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1">
-        <v>53051</v>
+        <v>16001</v>
       </c>
       <c r="B91" t="s">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="C91" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D91" s="1">
-        <v>0.16625545918941498</v>
+        <v>0.17050167918205261</v>
       </c>
       <c r="E91" s="1">
-        <v>0.10374018549919128</v>
+        <v>0.03413931280374527</v>
       </c>
       <c r="F91" s="1">
-        <v>1.6026138067245483</v>
+        <v>4.9942913055419922</v>
       </c>
       <c r="G91" s="1">
-        <v>0.10901994258165359</v>
+        <v>5.9052206324849976e-07</v>
       </c>
       <c r="H91" s="1">
-        <v>96.725532531738281</v>
+        <v>96.781196594238281</v>
       </c>
       <c r="I91" s="1">
-        <v>91.755615234375</v>
+        <v>96.960929870605469</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1">
-        <v>47115</v>
+        <v>12081</v>
       </c>
       <c r="B92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C92" t="s">
-        <v>285</v>
+        <v>149</v>
       </c>
       <c r="D92" s="1">
-        <v>0.16327701508998871</v>
+        <v>0.17033989727497101</v>
       </c>
       <c r="E92" s="1">
-        <v>0.11198576539754868</v>
+        <v>0.0436834916472435</v>
       </c>
       <c r="F92" s="1">
-        <v>1.4580157995223999</v>
+        <v>3.8994112014770508</v>
       </c>
       <c r="G92" s="1">
-        <v>0.1448361873626709</v>
+        <v>9.6426891104783863e-05</v>
       </c>
       <c r="H92" s="1">
-        <v>96.688743591308594</v>
+        <v>96.745025634765625</v>
       </c>
       <c r="I92" s="1">
-        <v>90.945899963378906</v>
+        <v>96.273513793945313</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1">
+        <v>48299</v>
+      </c>
+      <c r="B93" t="s">
+        <v>100</v>
+      </c>
+      <c r="C93" t="s">
+        <v>280</v>
+      </c>
+      <c r="D93" s="1">
+        <v>0.16995133459568024</v>
+      </c>
+      <c r="E93" s="1">
+        <v>0.069826669991016388</v>
+      </c>
+      <c r="F93" s="1">
+        <v>2.4339029788970947</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.01493699848651886</v>
+      </c>
+      <c r="H93" s="1">
+        <v>96.7088623046875</v>
+      </c>
+      <c r="I93" s="1">
+        <v>94.428367614746094</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1">
+        <v>6051</v>
+      </c>
+      <c r="B94" t="s">
+        <v>99</v>
+      </c>
+      <c r="C94" t="s">
+        <v>281</v>
+      </c>
+      <c r="D94" s="1">
+        <v>0.16874884068965912</v>
+      </c>
+      <c r="E94" s="1">
+        <v>0.078401677310466766</v>
+      </c>
+      <c r="F94" s="1">
+        <v>2.152362585067749</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0.031368806958198547</v>
+      </c>
+      <c r="H94" s="1">
+        <v>96.672691345214844</v>
+      </c>
+      <c r="I94" s="1">
+        <v>93.849494934082031</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1">
+        <v>26119</v>
+      </c>
+      <c r="B95" t="s">
+        <v>192</v>
+      </c>
+      <c r="C95" t="s">
+        <v>282</v>
+      </c>
+      <c r="D95" s="1">
+        <v>0.16813819110393524</v>
+      </c>
+      <c r="E95" s="1">
+        <v>0.10402067005634308</v>
+      </c>
+      <c r="F95" s="1">
+        <v>1.6163921356201172</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0.10600955784320831</v>
+      </c>
+      <c r="H95" s="1">
+        <v>96.636528015136719</v>
+      </c>
+      <c r="I95" s="1">
+        <v>91.5701904296875</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1">
+        <v>32005</v>
+      </c>
+      <c r="B96" t="s">
+        <v>127</v>
+      </c>
+      <c r="C96" t="s">
+        <v>283</v>
+      </c>
+      <c r="D96" s="1">
+        <v>0.16632890701293945</v>
+      </c>
+      <c r="E96" s="1">
+        <v>0.1293562650680542</v>
+      </c>
+      <c r="F96" s="1">
+        <v>1.2858202457427979</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0.19850580394268036</v>
+      </c>
+      <c r="H96" s="1">
+        <v>96.600364685058594</v>
+      </c>
+      <c r="I96" s="1">
+        <v>89.833572387695313</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1">
+        <v>53051</v>
+      </c>
+      <c r="B97" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97" t="s">
+        <v>284</v>
+      </c>
+      <c r="D97" s="1">
+        <v>0.16625545918941498</v>
+      </c>
+      <c r="E97" s="1">
+        <v>0.10374018549919128</v>
+      </c>
+      <c r="F97" s="1">
+        <v>1.6026138067245483</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0.10901994258165359</v>
+      </c>
+      <c r="H97" s="1">
+        <v>96.564193725585938</v>
+      </c>
+      <c r="I97" s="1">
+        <v>91.497825622558594</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1">
+        <v>47115</v>
+      </c>
+      <c r="B98" t="s">
+        <v>128</v>
+      </c>
+      <c r="C98" t="s">
+        <v>285</v>
+      </c>
+      <c r="D98" s="1">
+        <v>0.16327701508998871</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0.11198576539754868</v>
+      </c>
+      <c r="F98" s="1">
+        <v>1.4580157995223999</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0.1448361873626709</v>
+      </c>
+      <c r="H98" s="1">
+        <v>96.528030395507813</v>
+      </c>
+      <c r="I98" s="1">
+        <v>90.701881408691406</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1">
         <v>29229</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B99" t="s">
         <v>133</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C99" t="s">
         <v>286</v>
       </c>
-      <c r="D93" s="1">
+      <c r="D99" s="1">
         <v>0.16234627366065979</v>
       </c>
-      <c r="E93" s="1">
+      <c r="E99" s="1">
         <v>0.093427650630474091</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F99" s="1">
         <v>1.7376683950424194</v>
       </c>
-      <c r="G93" s="1">
+      <c r="G99" s="1">
         <v>0.082269258797168732</v>
       </c>
-      <c r="H93" s="1">
-        <v>96.651947021484375</v>
-      </c>
-      <c r="I93" s="1">
-        <v>92.344497680664063</v>
+      <c r="H99" s="1">
+        <v>96.491859436035156</v>
+      </c>
+      <c r="I99" s="1">
+        <v>92.076698303222656</v>
       </c>
     </row>
   </sheetData>

--- a/results/flows/flow_analysis_stats.xlsx
+++ b/results/flows/flow_analysis_stats.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="11109" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="16039" uniqueCount="671">
   <si>
     <t>stat_name</t>
   </si>
@@ -2651,7 +2651,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2694,13 +2694,13 @@
         <v>143</v>
       </c>
       <c r="D2" s="1">
-        <v>0.21724884212017059</v>
+        <v>0.21672101318836212</v>
       </c>
       <c r="E2" s="1">
-        <v>0.026260213926434517</v>
+        <v>0.026435522362589836</v>
       </c>
       <c r="F2" s="1">
-        <v>8.2729272842407227</v>
+        <v>8.1980981826782227</v>
       </c>
       <c r="G2" s="1">
         <v>2.2204460492503131e-16</v>
@@ -2723,16 +2723,16 @@
         <v>138</v>
       </c>
       <c r="D3" s="1">
-        <v>0.24804094433784485</v>
+        <v>0.24994240701198578</v>
       </c>
       <c r="E3" s="1">
-        <v>0.031005352735519409</v>
+        <v>0.03115425631403923</v>
       </c>
       <c r="F3" s="1">
-        <v>7.9999394416809082</v>
+        <v>8.0227375030517578</v>
       </c>
       <c r="G3" s="1">
-        <v>1.3322676295501878e-15</v>
+        <v>1.1102230246251565e-15</v>
       </c>
       <c r="H3" s="1">
         <v>99.481864929199219</v>
@@ -2752,19 +2752,19 @@
         <v>158</v>
       </c>
       <c r="D4" s="1">
-        <v>0.11722731590270996</v>
+        <v>0.11963693052530289</v>
       </c>
       <c r="E4" s="1">
-        <v>0.016651337966322899</v>
+        <v>0.016209451481699944</v>
       </c>
       <c r="F4" s="1">
-        <v>7.0401139259338379</v>
+        <v>7.3806896209716797</v>
       </c>
       <c r="G4" s="1">
-        <v>1.9209078772064458e-12</v>
+        <v>1.574296248918472e-13</v>
       </c>
       <c r="H4" s="1">
-        <v>93.782386779785156</v>
+        <v>93.5233154296875</v>
       </c>
       <c r="I4" s="1">
         <v>99.481864929199219</v>
@@ -2781,16 +2781,16 @@
         <v>185</v>
       </c>
       <c r="D5" s="1">
-        <v>0.11261363327503204</v>
+        <v>0.11239766329526901</v>
       </c>
       <c r="E5" s="1">
-        <v>0.016371032223105431</v>
+        <v>0.016347905620932579</v>
       </c>
       <c r="F5" s="1">
-        <v>6.8788352012634277</v>
+        <v>6.8753557205200195</v>
       </c>
       <c r="G5" s="1">
-        <v>6.0342841834426508e-12</v>
+        <v>6.1834981579522719e-12</v>
       </c>
       <c r="H5" s="1">
         <v>92.746116638183594</v>
@@ -2810,19 +2810,19 @@
         <v>153</v>
       </c>
       <c r="D6" s="1">
-        <v>0.12830962240695953</v>
+        <v>0.12935627996921539</v>
       </c>
       <c r="E6" s="1">
-        <v>0.02189142070710659</v>
+        <v>0.022016070783138275</v>
       </c>
       <c r="F6" s="1">
-        <v>5.8611831665039063</v>
+        <v>5.8755388259887695</v>
       </c>
       <c r="G6" s="1">
-        <v>4.5958068461970925e-09</v>
+        <v>4.2147014767124347e-09</v>
       </c>
       <c r="H6" s="1">
-        <v>95.077720642089844</v>
+        <v>94.818649291992188</v>
       </c>
       <c r="I6" s="1">
         <v>98.963729858398438</v>
@@ -2839,16 +2839,16 @@
         <v>148</v>
       </c>
       <c r="D7" s="1">
-        <v>0.16911184787750244</v>
+        <v>0.17124670743942261</v>
       </c>
       <c r="E7" s="1">
-        <v>0.031742807477712631</v>
+        <v>0.032097935676574707</v>
       </c>
       <c r="F7" s="1">
-        <v>5.3275642395019531</v>
+        <v>5.3351316452026367</v>
       </c>
       <c r="G7" s="1">
-        <v>9.9538581821434491e-08</v>
+        <v>9.5475265027289424e-08</v>
       </c>
       <c r="H7" s="1">
         <v>96.632125854492188</v>
@@ -2868,16 +2868,16 @@
         <v>145</v>
       </c>
       <c r="D8" s="1">
-        <v>0.21054258942604065</v>
+        <v>0.21188028156757355</v>
       </c>
       <c r="E8" s="1">
-        <v>0.043704904615879059</v>
+        <v>0.043339543044567108</v>
       </c>
       <c r="F8" s="1">
-        <v>4.8173675537109375</v>
+        <v>4.8888444900512695</v>
       </c>
       <c r="G8" s="1">
-        <v>1.4546458260156214e-06</v>
+        <v>1.0142957762582228e-06</v>
       </c>
       <c r="H8" s="1">
         <v>97.66839599609375</v>
@@ -2897,16 +2897,16 @@
         <v>141</v>
       </c>
       <c r="D9" s="1">
-        <v>0.21965262293815613</v>
+        <v>0.22257435321807861</v>
       </c>
       <c r="E9" s="1">
-        <v>0.045607626438140869</v>
+        <v>0.045636691153049469</v>
       </c>
       <c r="F9" s="1">
-        <v>4.8161377906799316</v>
+        <v>4.8770923614501953</v>
       </c>
       <c r="G9" s="1">
-        <v>1.4636347032137564e-06</v>
+        <v>1.0766103741843835e-06</v>
       </c>
       <c r="H9" s="1">
         <v>98.704666137695313</v>
@@ -2926,16 +2926,16 @@
         <v>147</v>
       </c>
       <c r="D10" s="1">
-        <v>0.1978154182434082</v>
+        <v>0.19799815118312836</v>
       </c>
       <c r="E10" s="1">
-        <v>0.046531513333320618</v>
+        <v>0.046569757163524628</v>
       </c>
       <c r="F10" s="1">
-        <v>4.2512140274047852</v>
+        <v>4.2516465187072754</v>
       </c>
       <c r="G10" s="1">
-        <v>2.126148683601059e-05</v>
+        <v>2.1220461349003017e-05</v>
       </c>
       <c r="H10" s="1">
         <v>97.150260925292969</v>
@@ -2955,16 +2955,16 @@
         <v>142</v>
       </c>
       <c r="D11" s="1">
-        <v>0.21742868423461914</v>
+        <v>0.21992169320583344</v>
       </c>
       <c r="E11" s="1">
-        <v>0.051745396107435226</v>
+        <v>0.052505489438772202</v>
       </c>
       <c r="F11" s="1">
-        <v>4.2018942832946777</v>
+        <v>4.1885466575622559</v>
       </c>
       <c r="G11" s="1">
-        <v>2.646907523740083e-05</v>
+        <v>2.8074658985133283e-05</v>
       </c>
       <c r="H11" s="1">
         <v>98.445594787597656</v>
@@ -2975,28 +2975,28 @@
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>12015</v>
+        <v>32031</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D12" s="1">
-        <v>0.13451862335205078</v>
+        <v>0.24316537380218506</v>
       </c>
       <c r="E12" s="1">
-        <v>0.034165006130933762</v>
+        <v>0.062664009630680084</v>
       </c>
       <c r="F12" s="1">
-        <v>3.9373219013214111</v>
+        <v>3.8804631233215332</v>
       </c>
       <c r="G12" s="1">
-        <v>8.2396043580956757e-05</v>
+        <v>0.00010425774962641299</v>
       </c>
       <c r="H12" s="1">
-        <v>95.595855712890625</v>
+        <v>99.222801208496094</v>
       </c>
       <c r="I12" s="1">
         <v>97.409324645996094</v>
@@ -3004,28 +3004,28 @@
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>32031</v>
+        <v>12015</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D13" s="1">
-        <v>0.24016955494880676</v>
+        <v>0.13320158421993256</v>
       </c>
       <c r="E13" s="1">
-        <v>0.0624723881483078</v>
+        <v>0.034432224929332733</v>
       </c>
       <c r="F13" s="1">
-        <v>3.8444113731384277</v>
+        <v>3.8685152530670166</v>
       </c>
       <c r="G13" s="1">
-        <v>0.00012084214540664107</v>
+        <v>0.00010950008436338976</v>
       </c>
       <c r="H13" s="1">
-        <v>99.222801208496094</v>
+        <v>95.336784362792969</v>
       </c>
       <c r="I13" s="1">
         <v>97.150260925292969</v>
@@ -3042,16 +3042,16 @@
         <v>146</v>
       </c>
       <c r="D14" s="1">
-        <v>0.20878720283508301</v>
+        <v>0.21118472516536713</v>
       </c>
       <c r="E14" s="1">
-        <v>0.05577487125992775</v>
+        <v>0.055974666029214859</v>
       </c>
       <c r="F14" s="1">
-        <v>3.7433919906616211</v>
+        <v>3.7728626728057861</v>
       </c>
       <c r="G14" s="1">
-        <v>0.00018155266297981143</v>
+        <v>0.00016138512000907213</v>
       </c>
       <c r="H14" s="1">
         <v>97.409324645996094</v>
@@ -3071,19 +3071,19 @@
         <v>149</v>
       </c>
       <c r="D15" s="1">
-        <v>0.16660307347774506</v>
+        <v>0.1675233393907547</v>
       </c>
       <c r="E15" s="1">
-        <v>0.046616099774837494</v>
+        <v>0.046382106840610504</v>
       </c>
       <c r="F15" s="1">
-        <v>3.5739386081695557</v>
+        <v>3.6118097305297852</v>
       </c>
       <c r="G15" s="1">
-        <v>0.00035165142617188394</v>
+        <v>0.00030406762380152941</v>
       </c>
       <c r="H15" s="1">
-        <v>96.373054504394531</v>
+        <v>96.113990783691406</v>
       </c>
       <c r="I15" s="1">
         <v>96.632125854492188</v>
@@ -3091,28 +3091,28 @@
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>32003</v>
+        <v>6025</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D16" s="1">
-        <v>0.13273577392101288</v>
+        <v>0.15584227442741394</v>
       </c>
       <c r="E16" s="1">
-        <v>0.038937158882617951</v>
+        <v>0.045350413769483566</v>
       </c>
       <c r="F16" s="1">
-        <v>3.4089744091033936</v>
+        <v>3.4364025592803955</v>
       </c>
       <c r="G16" s="1">
-        <v>0.00065207597799599171</v>
+        <v>0.00058949436061084271</v>
       </c>
       <c r="H16" s="1">
-        <v>95.336784362792969</v>
+        <v>95.85491943359375</v>
       </c>
       <c r="I16" s="1">
         <v>96.373054504394531</v>
@@ -3120,28 +3120,28 @@
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>6025</v>
+        <v>32003</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D17" s="1">
-        <v>0.15443232655525208</v>
+        <v>0.13350202143192291</v>
       </c>
       <c r="E17" s="1">
-        <v>0.04555978998541832</v>
+        <v>0.039008509367704391</v>
       </c>
       <c r="F17" s="1">
-        <v>3.3896627426147461</v>
+        <v>3.422382116317749</v>
       </c>
       <c r="G17" s="1">
-        <v>0.00069978658575564623</v>
+        <v>0.00062075007008388638</v>
       </c>
       <c r="H17" s="1">
-        <v>95.85491943359375</v>
+        <v>95.595855712890625</v>
       </c>
       <c r="I17" s="1">
         <v>96.113990783691406</v>
@@ -3158,16 +3158,16 @@
         <v>144</v>
       </c>
       <c r="D18" s="1">
-        <v>0.21344844996929169</v>
+        <v>0.21399322152137756</v>
       </c>
       <c r="E18" s="1">
-        <v>0.063826940953731537</v>
+        <v>0.063986487686634064</v>
       </c>
       <c r="F18" s="1">
-        <v>3.344174861907959</v>
+        <v>3.3443500995635986</v>
       </c>
       <c r="G18" s="1">
-        <v>0.00082527700578793883</v>
+        <v>0.00082475587259978056</v>
       </c>
       <c r="H18" s="1">
         <v>97.927459716796875</v>
@@ -3187,19 +3187,19 @@
         <v>90</v>
       </c>
       <c r="D19" s="1">
-        <v>0.16549687087535858</v>
+        <v>0.16855885088443756</v>
       </c>
       <c r="E19" s="1">
-        <v>0.051017593592405319</v>
+        <v>0.050971634685993195</v>
       </c>
       <c r="F19" s="1">
-        <v>3.24391770362854</v>
+        <v>3.3069148063659668</v>
       </c>
       <c r="G19" s="1">
-        <v>0.0011789780110120773</v>
+        <v>0.00094329577405005694</v>
       </c>
       <c r="H19" s="1">
-        <v>96.113990783691406</v>
+        <v>96.373054504394531</v>
       </c>
       <c r="I19" s="1">
         <v>95.595855712890625</v>
@@ -3216,19 +3216,19 @@
         <v>156</v>
       </c>
       <c r="D20" s="1">
-        <v>0.12405294924974442</v>
+        <v>0.12574592232704163</v>
       </c>
       <c r="E20" s="1">
-        <v>0.039203166961669922</v>
+        <v>0.038880933076143265</v>
       </c>
       <c r="F20" s="1">
-        <v>3.164360523223877</v>
+        <v>3.2341282367706299</v>
       </c>
       <c r="G20" s="1">
-        <v>0.0015542414039373398</v>
+        <v>0.0012201465433463454</v>
       </c>
       <c r="H20" s="1">
-        <v>94.300521850585938</v>
+        <v>94.559585571289063</v>
       </c>
       <c r="I20" s="1">
         <v>95.336784362792969</v>
@@ -3245,19 +3245,19 @@
         <v>186</v>
       </c>
       <c r="D21" s="1">
-        <v>0.077347613871097565</v>
+        <v>0.081404693424701691</v>
       </c>
       <c r="E21" s="1">
-        <v>0.026810413226485252</v>
+        <v>0.026731139048933983</v>
       </c>
       <c r="F21" s="1">
-        <v>2.884984016418457</v>
+        <v>3.0453133583068848</v>
       </c>
       <c r="G21" s="1">
-        <v>0.0039143352769315243</v>
+        <v>0.0023243799805641174</v>
       </c>
       <c r="H21" s="1">
-        <v>89.37823486328125</v>
+        <v>89.896369934082031</v>
       </c>
       <c r="I21" s="1">
         <v>95.077720642089844</v>
@@ -3274,19 +3274,19 @@
         <v>187</v>
       </c>
       <c r="D22" s="1">
-        <v>0.099755808711051941</v>
+        <v>0.096647061407566071</v>
       </c>
       <c r="E22" s="1">
-        <v>0.035990752279758453</v>
+        <v>0.035863053053617478</v>
       </c>
       <c r="F22" s="1">
-        <v>2.7717065811157227</v>
+        <v>2.6948921680450439</v>
       </c>
       <c r="G22" s="1">
-        <v>0.0055763274431228638</v>
+        <v>0.0070411413908004761</v>
       </c>
       <c r="H22" s="1">
-        <v>92.227981567382813</v>
+        <v>91.450775146484375</v>
       </c>
       <c r="I22" s="1">
         <v>94.818649291992188</v>
@@ -3303,16 +3303,16 @@
         <v>137</v>
       </c>
       <c r="D23" s="1">
-        <v>0.17730148136615753</v>
+        <v>0.18028932809829712</v>
       </c>
       <c r="E23" s="1">
-        <v>0.067209988832473755</v>
+        <v>0.06702781468629837</v>
       </c>
       <c r="F23" s="1">
-        <v>2.6380226612091065</v>
+        <v>2.6897687911987305</v>
       </c>
       <c r="G23" s="1">
-        <v>0.0083391005173325539</v>
+        <v>0.0071501540951430798</v>
       </c>
       <c r="H23" s="1">
         <v>96.891189575195313</v>
@@ -3332,19 +3332,19 @@
         <v>188</v>
       </c>
       <c r="D24" s="1">
-        <v>0.077345326542854309</v>
+        <v>0.077398322522640228</v>
       </c>
       <c r="E24" s="1">
-        <v>0.030236244201660156</v>
+        <v>0.03012334555387497</v>
       </c>
       <c r="F24" s="1">
-        <v>2.5580334663391113</v>
+        <v>2.5693800449371338</v>
       </c>
       <c r="G24" s="1">
-        <v>0.010526596568524837</v>
+        <v>0.010188065469264984</v>
       </c>
       <c r="H24" s="1">
-        <v>89.119171142578125</v>
+        <v>88.860107421875</v>
       </c>
       <c r="I24" s="1">
         <v>94.300521850585938</v>
@@ -3361,19 +3361,19 @@
         <v>154</v>
       </c>
       <c r="D25" s="1">
-        <v>0.12784139811992645</v>
+        <v>0.12942652404308319</v>
       </c>
       <c r="E25" s="1">
-        <v>0.055736925452947617</v>
+        <v>0.055388569831848145</v>
       </c>
       <c r="F25" s="1">
-        <v>2.2936570644378662</v>
+        <v>2.3367009162902832</v>
       </c>
       <c r="G25" s="1">
-        <v>0.021810205653309822</v>
+        <v>0.019454739987850189</v>
       </c>
       <c r="H25" s="1">
-        <v>94.818649291992188</v>
+        <v>95.077720642089844</v>
       </c>
       <c r="I25" s="1">
         <v>94.041450500488281</v>
@@ -3390,19 +3390,19 @@
         <v>189</v>
       </c>
       <c r="D26" s="1">
-        <v>0.056241549551486969</v>
+        <v>0.057353243231773376</v>
       </c>
       <c r="E26" s="1">
-        <v>0.025651665404438973</v>
+        <v>0.02560284361243248</v>
       </c>
       <c r="F26" s="1">
-        <v>2.1925106048583984</v>
+        <v>2.2401123046875</v>
       </c>
       <c r="G26" s="1">
-        <v>0.028342658653855324</v>
+        <v>0.0250836331397295</v>
       </c>
       <c r="H26" s="1">
-        <v>86.269432067871094</v>
+        <v>86.528495788574219</v>
       </c>
       <c r="I26" s="1">
         <v>93.782386779785156</v>
@@ -3419,16 +3419,16 @@
         <v>190</v>
       </c>
       <c r="D27" s="1">
-        <v>0.063818678259849548</v>
+        <v>0.06433270126581192</v>
       </c>
       <c r="E27" s="1">
-        <v>0.029186997562646866</v>
+        <v>0.029035016894340515</v>
       </c>
       <c r="F27" s="1">
-        <v>2.1865448951721191</v>
+        <v>2.2156937122344971</v>
       </c>
       <c r="G27" s="1">
-        <v>0.028775764629244804</v>
+        <v>0.026712486520409584</v>
       </c>
       <c r="H27" s="1">
         <v>87.305702209472656</v>
@@ -3448,22 +3448,51 @@
         <v>191</v>
       </c>
       <c r="D28" s="1">
-        <v>0.098713032901287079</v>
+        <v>0.10031715035438538</v>
       </c>
       <c r="E28" s="1">
-        <v>0.04664897546172142</v>
+        <v>0.046856410801410675</v>
       </c>
       <c r="F28" s="1">
-        <v>2.1160814762115479</v>
+        <v>2.1409482955932617</v>
       </c>
       <c r="G28" s="1">
-        <v>0.034337878227233887</v>
+        <v>0.032278206199407578</v>
       </c>
       <c r="H28" s="1">
-        <v>91.968910217285156</v>
+        <v>92.227981567382813</v>
       </c>
       <c r="I28" s="1">
         <v>93.264251708984375</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1">
+        <v>41051</v>
+      </c>
+      <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.11612220853567123</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.05665009468793869</v>
+      </c>
+      <c r="F29" s="1">
+        <v>2.0498149394989014</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.040382493287324905</v>
+      </c>
+      <c r="H29" s="1">
+        <v>93.264251708984375</v>
+      </c>
+      <c r="I29" s="1">
+        <v>93.005180358886719</v>
       </c>
     </row>
   </sheetData>
@@ -7658,7 +7687,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.11663704365491867</v>
+        <v>0.11612220853567123</v>
       </c>
       <c r="C2" t="s">
         <v>42</v>
@@ -7672,7 +7701,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0.056322645395994187</v>
+        <v>0.05665009468793869</v>
       </c>
       <c r="C3" t="s">
         <v>43</v>
@@ -7686,7 +7715,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>2.0708730220794678</v>
+        <v>2.0498149394989014</v>
       </c>
       <c r="C4" t="s">
         <v>44</v>
@@ -7700,7 +7729,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>0.038370665162801743</v>
+        <v>0.040382493287324905</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
@@ -7728,7 +7757,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.19089731574058533</v>
+        <v>-0.19057168066501617</v>
       </c>
       <c r="C7" t="s">
         <v>47</v>
@@ -7742,7 +7771,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>0.022514812648296356</v>
+        <v>0.022736489772796631</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
@@ -7756,7 +7785,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>-8.4787435531616211</v>
+        <v>-8.3817548751831055</v>
       </c>
       <c r="C9" t="s">
         <v>49</v>
@@ -7840,7 +7869,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
         <v>55</v>
@@ -7854,7 +7883,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
         <v>56</v>
@@ -7868,7 +7897,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
         <v>57</v>
@@ -7882,7 +7911,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
         <v>58</v>
@@ -7924,7 +7953,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>-0.061569496989250183</v>
+        <v>-0.060776829719543457</v>
       </c>
       <c r="C21" t="s">
         <v>61</v>
@@ -7938,7 +7967,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>0.13065558671951294</v>
+        <v>0.13065138459205627</v>
       </c>
       <c r="C22" t="s">
         <v>62</v>
@@ -7952,7 +7981,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>-1.0851960182189941</v>
+        <v>-1.0817304849624634</v>
       </c>
       <c r="C23" t="s">
         <v>63</v>
@@ -7966,7 +7995,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>0.91561716794967651</v>
+        <v>0.91884303092956543</v>
       </c>
       <c r="C24" t="s">
         <v>64</v>
@@ -7980,7 +8009,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>-0.13087238371372223</v>
+        <v>-0.12977954745292664</v>
       </c>
       <c r="C25" t="s">
         <v>65</v>
@@ -7994,7 +8023,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>-0.068173043429851532</v>
+        <v>-0.067383803427219391</v>
       </c>
       <c r="C26" t="s">
         <v>66</v>
@@ -8008,7 +8037,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>0.0033888183534145355</v>
+        <v>0.0031095929443836212</v>
       </c>
       <c r="C27" t="s">
         <v>67</v>
@@ -8022,7 +8051,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>-0.024470433592796326</v>
+        <v>-0.024949463084340096</v>
       </c>
       <c r="C28" t="s">
         <v>68</v>
@@ -8036,7 +8065,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>0.13657465577125549</v>
+        <v>0.13645480573177338</v>
       </c>
       <c r="C29" t="s">
         <v>69</v>
@@ -8050,7 +8079,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>-0.8163297176361084</v>
+        <v>-0.81750279664993286</v>
       </c>
       <c r="C30" t="s">
         <v>70</v>
@@ -8064,7 +8093,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>0.467477947473526</v>
+        <v>0.46617856621742249</v>
       </c>
       <c r="C31" t="s">
         <v>71</v>
@@ -8078,7 +8107,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>-0.10765065252780914</v>
+        <v>-0.10817023366689682</v>
       </c>
       <c r="C32" t="s">
         <v>72</v>
@@ -8092,7 +8121,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>-0.040816567838191986</v>
+        <v>-0.041393790394067764</v>
       </c>
       <c r="C33" t="s">
         <v>73</v>
@@ -8106,7 +8135,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1">
-        <v>0.048869196325540543</v>
+        <v>0.048959400504827499</v>
       </c>
       <c r="C34" t="s">
         <v>74</v>
@@ -8120,7 +8149,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>-1.8679836988449097</v>
+        <v>-1.8449206352233887</v>
       </c>
       <c r="C35" t="s">
         <v>75</v>
@@ -8134,7 +8163,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1">
-        <v>3.4767313003540039</v>
+        <v>3.4713602066040039</v>
       </c>
       <c r="C36" t="s">
         <v>76</v>
@@ -8148,7 +8177,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1">
-        <v>-1.5900273323059082</v>
+        <v>-1.5863807201385498</v>
       </c>
       <c r="C37" t="s">
         <v>77</v>
@@ -8162,7 +8191,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1">
-        <v>-1.1097232103347778</v>
+        <v>-1.1228899955749512</v>
       </c>
       <c r="C38" t="s">
         <v>78</v>
@@ -8176,7 +8205,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1">
-        <v>3.5653283596038818</v>
+        <v>3.5582025051116943</v>
       </c>
       <c r="C39" t="s">
         <v>79</v>
@@ -8190,7 +8219,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1">
-        <v>-0.91767817735671997</v>
+        <v>-0.95073652267456055</v>
       </c>
       <c r="C40" t="s">
         <v>80</v>
@@ -8205,7 +8234,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8248,22 +8277,22 @@
         <v>136</v>
       </c>
       <c r="D2" s="1">
-        <v>0.91561716794967651</v>
+        <v>0.91884303092956543</v>
       </c>
       <c r="E2" s="1">
-        <v>0.48795279860496521</v>
+        <v>0.48892328143119812</v>
       </c>
       <c r="F2" s="1">
-        <v>1.8764461278915405</v>
+        <v>1.879319429397583</v>
       </c>
       <c r="G2" s="1">
-        <v>0.060594044625759125</v>
+        <v>0.06020088866353035</v>
       </c>
       <c r="H2" s="1">
         <v>100</v>
       </c>
       <c r="I2" s="1">
-        <v>91.450775146484375</v>
+        <v>91.709846496582031</v>
       </c>
     </row>
     <row r="3">
@@ -8277,16 +8306,16 @@
         <v>137</v>
       </c>
       <c r="D3" s="1">
-        <v>0.3075692355632782</v>
+        <v>0.31000146269798279</v>
       </c>
       <c r="E3" s="1">
-        <v>0.15502460300922394</v>
+        <v>0.15533691644668579</v>
       </c>
       <c r="F3" s="1">
-        <v>1.9840027093887329</v>
+        <v>1.9956715106964111</v>
       </c>
       <c r="G3" s="1">
-        <v>0.047255538403987885</v>
+        <v>0.045969691127538681</v>
       </c>
       <c r="H3" s="1">
         <v>99.740936279296875</v>
@@ -8306,16 +8335,16 @@
         <v>138</v>
       </c>
       <c r="D4" s="1">
-        <v>0.24804094433784485</v>
+        <v>0.24994240701198578</v>
       </c>
       <c r="E4" s="1">
-        <v>0.031005352735519409</v>
+        <v>0.03115425631403923</v>
       </c>
       <c r="F4" s="1">
-        <v>7.9999394416809082</v>
+        <v>8.0227375030517578</v>
       </c>
       <c r="G4" s="1">
-        <v>1.3322676295501878e-15</v>
+        <v>1.1102230246251565e-15</v>
       </c>
       <c r="H4" s="1">
         <v>99.481864929199219</v>
@@ -8335,22 +8364,22 @@
         <v>139</v>
       </c>
       <c r="D5" s="1">
-        <v>0.24016955494880676</v>
+        <v>0.24316537380218506</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0624723881483078</v>
+        <v>0.062664009630680084</v>
       </c>
       <c r="F5" s="1">
-        <v>3.8444113731384277</v>
+        <v>3.8804631233215332</v>
       </c>
       <c r="G5" s="1">
-        <v>0.00012084214540664107</v>
+        <v>0.00010425774962641299</v>
       </c>
       <c r="H5" s="1">
         <v>99.222801208496094</v>
       </c>
       <c r="I5" s="1">
-        <v>97.150260925292969</v>
+        <v>97.409324645996094</v>
       </c>
     </row>
     <row r="6">
@@ -8364,22 +8393,22 @@
         <v>140</v>
       </c>
       <c r="D6" s="1">
-        <v>0.23071843385696411</v>
+        <v>0.23029787838459015</v>
       </c>
       <c r="E6" s="1">
-        <v>0.16974106431007385</v>
+        <v>0.17023247480392456</v>
       </c>
       <c r="F6" s="1">
-        <v>1.359237551689148</v>
+        <v>1.3528434038162232</v>
       </c>
       <c r="G6" s="1">
-        <v>0.17407132685184479</v>
+        <v>0.17610566318035126</v>
       </c>
       <c r="H6" s="1">
         <v>98.963729858398438</v>
       </c>
       <c r="I6" s="1">
-        <v>87.823837280273438</v>
+        <v>87.564765930175781</v>
       </c>
     </row>
     <row r="7">
@@ -8393,16 +8422,16 @@
         <v>141</v>
       </c>
       <c r="D7" s="1">
-        <v>0.21965262293815613</v>
+        <v>0.22257435321807861</v>
       </c>
       <c r="E7" s="1">
-        <v>0.045607626438140869</v>
+        <v>0.045636691153049469</v>
       </c>
       <c r="F7" s="1">
-        <v>4.8161377906799316</v>
+        <v>4.8770923614501953</v>
       </c>
       <c r="G7" s="1">
-        <v>1.4636347032137564e-06</v>
+        <v>1.0766103741843835e-06</v>
       </c>
       <c r="H7" s="1">
         <v>98.704666137695313</v>
@@ -8422,16 +8451,16 @@
         <v>142</v>
       </c>
       <c r="D8" s="1">
-        <v>0.21742868423461914</v>
+        <v>0.21992169320583344</v>
       </c>
       <c r="E8" s="1">
-        <v>0.051745396107435226</v>
+        <v>0.052505489438772202</v>
       </c>
       <c r="F8" s="1">
-        <v>4.2018942832946777</v>
+        <v>4.1885466575622559</v>
       </c>
       <c r="G8" s="1">
-        <v>2.646907523740083e-05</v>
+        <v>2.8074658985133283e-05</v>
       </c>
       <c r="H8" s="1">
         <v>98.445594787597656</v>
@@ -8451,13 +8480,13 @@
         <v>143</v>
       </c>
       <c r="D9" s="1">
-        <v>0.21724884212017059</v>
+        <v>0.21672101318836212</v>
       </c>
       <c r="E9" s="1">
-        <v>0.026260213926434517</v>
+        <v>0.026435522362589836</v>
       </c>
       <c r="F9" s="1">
-        <v>8.2729272842407227</v>
+        <v>8.1980981826782227</v>
       </c>
       <c r="G9" s="1">
         <v>2.2204460492503131e-16</v>
@@ -8480,16 +8509,16 @@
         <v>144</v>
       </c>
       <c r="D10" s="1">
-        <v>0.21344844996929169</v>
+        <v>0.21399322152137756</v>
       </c>
       <c r="E10" s="1">
-        <v>0.063826940953731537</v>
+        <v>0.063986487686634064</v>
       </c>
       <c r="F10" s="1">
-        <v>3.344174861907959</v>
+        <v>3.3443500995635986</v>
       </c>
       <c r="G10" s="1">
-        <v>0.00082527700578793883</v>
+        <v>0.00082475587259978056</v>
       </c>
       <c r="H10" s="1">
         <v>97.927459716796875</v>
@@ -8509,16 +8538,16 @@
         <v>145</v>
       </c>
       <c r="D11" s="1">
-        <v>0.21054258942604065</v>
+        <v>0.21188028156757355</v>
       </c>
       <c r="E11" s="1">
-        <v>0.043704904615879059</v>
+        <v>0.043339543044567108</v>
       </c>
       <c r="F11" s="1">
-        <v>4.8173675537109375</v>
+        <v>4.8888444900512695</v>
       </c>
       <c r="G11" s="1">
-        <v>1.4546458260156214e-06</v>
+        <v>1.0142957762582228e-06</v>
       </c>
       <c r="H11" s="1">
         <v>97.66839599609375</v>
@@ -8538,16 +8567,16 @@
         <v>146</v>
       </c>
       <c r="D12" s="1">
-        <v>0.20878720283508301</v>
+        <v>0.21118472516536713</v>
       </c>
       <c r="E12" s="1">
-        <v>0.05577487125992775</v>
+        <v>0.055974666029214859</v>
       </c>
       <c r="F12" s="1">
-        <v>3.7433919906616211</v>
+        <v>3.7728626728057861</v>
       </c>
       <c r="G12" s="1">
-        <v>0.00018155266297981143</v>
+        <v>0.00016138512000907213</v>
       </c>
       <c r="H12" s="1">
         <v>97.409324645996094</v>
@@ -8567,16 +8596,16 @@
         <v>147</v>
       </c>
       <c r="D13" s="1">
-        <v>0.1978154182434082</v>
+        <v>0.19799815118312836</v>
       </c>
       <c r="E13" s="1">
-        <v>0.046531513333320618</v>
+        <v>0.046569757163524628</v>
       </c>
       <c r="F13" s="1">
-        <v>4.2512140274047852</v>
+        <v>4.2516465187072754</v>
       </c>
       <c r="G13" s="1">
-        <v>2.126148683601059e-05</v>
+        <v>2.1220461349003017e-05</v>
       </c>
       <c r="H13" s="1">
         <v>97.150260925292969</v>
@@ -8596,16 +8625,16 @@
         <v>137</v>
       </c>
       <c r="D14" s="1">
-        <v>0.17730148136615753</v>
+        <v>0.18028932809829712</v>
       </c>
       <c r="E14" s="1">
-        <v>0.067209988832473755</v>
+        <v>0.06702781468629837</v>
       </c>
       <c r="F14" s="1">
-        <v>2.6380226612091065</v>
+        <v>2.6897687911987305</v>
       </c>
       <c r="G14" s="1">
-        <v>0.0083391005173325539</v>
+        <v>0.0071501540951430798</v>
       </c>
       <c r="H14" s="1">
         <v>96.891189575195313</v>
@@ -8625,16 +8654,16 @@
         <v>148</v>
       </c>
       <c r="D15" s="1">
-        <v>0.16911184787750244</v>
+        <v>0.17124670743942261</v>
       </c>
       <c r="E15" s="1">
-        <v>0.031742807477712631</v>
+        <v>0.032097935676574707</v>
       </c>
       <c r="F15" s="1">
-        <v>5.3275642395019531</v>
+        <v>5.3351316452026367</v>
       </c>
       <c r="G15" s="1">
-        <v>9.9538581821434491e-08</v>
+        <v>9.5475265027289424e-08</v>
       </c>
       <c r="H15" s="1">
         <v>96.632125854492188</v>
@@ -8645,60 +8674,60 @@
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>12081</v>
+        <v>37021</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="D16" s="1">
-        <v>0.16660307347774506</v>
+        <v>0.16855885088443756</v>
       </c>
       <c r="E16" s="1">
-        <v>0.046616099774837494</v>
+        <v>0.050971634685993195</v>
       </c>
       <c r="F16" s="1">
-        <v>3.5739386081695557</v>
+        <v>3.3069148063659668</v>
       </c>
       <c r="G16" s="1">
-        <v>0.00035165142617188394</v>
+        <v>0.00094329577405005694</v>
       </c>
       <c r="H16" s="1">
         <v>96.373054504394531</v>
       </c>
       <c r="I16" s="1">
-        <v>96.632125854492188</v>
+        <v>95.595855712890625</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>37021</v>
+        <v>12081</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="D17" s="1">
-        <v>0.16549687087535858</v>
+        <v>0.1675233393907547</v>
       </c>
       <c r="E17" s="1">
-        <v>0.051017593592405319</v>
+        <v>0.046382106840610504</v>
       </c>
       <c r="F17" s="1">
-        <v>3.24391770362854</v>
+        <v>3.6118097305297852</v>
       </c>
       <c r="G17" s="1">
-        <v>0.0011789780110120773</v>
+        <v>0.00030406762380152941</v>
       </c>
       <c r="H17" s="1">
         <v>96.113990783691406</v>
       </c>
       <c r="I17" s="1">
-        <v>95.595855712890625</v>
+        <v>96.632125854492188</v>
       </c>
     </row>
     <row r="18">
@@ -8712,196 +8741,196 @@
         <v>150</v>
       </c>
       <c r="D18" s="1">
-        <v>0.15443232655525208</v>
+        <v>0.15584227442741394</v>
       </c>
       <c r="E18" s="1">
-        <v>0.04555978998541832</v>
+        <v>0.045350413769483566</v>
       </c>
       <c r="F18" s="1">
-        <v>3.3896627426147461</v>
+        <v>3.4364025592803955</v>
       </c>
       <c r="G18" s="1">
-        <v>0.00069978658575564623</v>
+        <v>0.00058949436061084271</v>
       </c>
       <c r="H18" s="1">
         <v>95.85491943359375</v>
       </c>
       <c r="I18" s="1">
-        <v>96.113990783691406</v>
+        <v>96.373054504394531</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>12015</v>
+        <v>32003</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D19" s="1">
-        <v>0.13451862335205078</v>
+        <v>0.13350202143192291</v>
       </c>
       <c r="E19" s="1">
-        <v>0.034165006130933762</v>
+        <v>0.039008509367704391</v>
       </c>
       <c r="F19" s="1">
-        <v>3.9373219013214111</v>
+        <v>3.422382116317749</v>
       </c>
       <c r="G19" s="1">
-        <v>8.2396043580956757e-05</v>
+        <v>0.00062075007008388638</v>
       </c>
       <c r="H19" s="1">
         <v>95.595855712890625</v>
       </c>
       <c r="I19" s="1">
-        <v>97.409324645996094</v>
+        <v>96.113990783691406</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>32003</v>
+        <v>12015</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D20" s="1">
-        <v>0.13273577392101288</v>
+        <v>0.13320158421993256</v>
       </c>
       <c r="E20" s="1">
-        <v>0.038937158882617951</v>
+        <v>0.034432224929332733</v>
       </c>
       <c r="F20" s="1">
-        <v>3.4089744091033936</v>
+        <v>3.8685152530670166</v>
       </c>
       <c r="G20" s="1">
-        <v>0.00065207597799599171</v>
+        <v>0.00010950008436338976</v>
       </c>
       <c r="H20" s="1">
         <v>95.336784362792969</v>
       </c>
       <c r="I20" s="1">
-        <v>96.373054504394531</v>
+        <v>97.150260925292969</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>12105</v>
+        <v>29510</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D21" s="1">
-        <v>0.12830962240695953</v>
+        <v>0.12942652404308319</v>
       </c>
       <c r="E21" s="1">
-        <v>0.02189142070710659</v>
+        <v>0.055388569831848145</v>
       </c>
       <c r="F21" s="1">
-        <v>5.8611831665039063</v>
+        <v>2.3367009162902832</v>
       </c>
       <c r="G21" s="1">
-        <v>4.5958068461970925e-09</v>
+        <v>0.019454739987850189</v>
       </c>
       <c r="H21" s="1">
         <v>95.077720642089844</v>
       </c>
       <c r="I21" s="1">
-        <v>98.963729858398438</v>
+        <v>94.041450500488281</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>29510</v>
+        <v>12105</v>
       </c>
       <c r="B22" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D22" s="1">
-        <v>0.12784139811992645</v>
+        <v>0.12935627996921539</v>
       </c>
       <c r="E22" s="1">
-        <v>0.055736925452947617</v>
+        <v>0.022016070783138275</v>
       </c>
       <c r="F22" s="1">
-        <v>2.2936570644378662</v>
+        <v>5.8755388259887695</v>
       </c>
       <c r="G22" s="1">
-        <v>0.021810205653309822</v>
+        <v>4.2147014767124347e-09</v>
       </c>
       <c r="H22" s="1">
         <v>94.818649291992188</v>
       </c>
       <c r="I22" s="1">
-        <v>94.041450500488281</v>
+        <v>98.963729858398438</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>6059</v>
+        <v>6001</v>
       </c>
       <c r="B23" t="s">
         <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D23" s="1">
-        <v>0.12598079442977905</v>
+        <v>0.12574592232704163</v>
       </c>
       <c r="E23" s="1">
-        <v>0.072530463337898254</v>
+        <v>0.038880933076143265</v>
       </c>
       <c r="F23" s="1">
-        <v>1.7369363307952881</v>
+        <v>3.2341282367706299</v>
       </c>
       <c r="G23" s="1">
-        <v>0.082398407161235809</v>
+        <v>0.0012201465433463454</v>
       </c>
       <c r="H23" s="1">
         <v>94.559585571289063</v>
       </c>
       <c r="I23" s="1">
-        <v>90.414505004882813</v>
+        <v>95.336784362792969</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>6001</v>
+        <v>6059</v>
       </c>
       <c r="B24" t="s">
         <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D24" s="1">
-        <v>0.12405294924974442</v>
+        <v>0.12398800998926163</v>
       </c>
       <c r="E24" s="1">
-        <v>0.039203166961669922</v>
+        <v>0.072528935968875885</v>
       </c>
       <c r="F24" s="1">
-        <v>3.164360523223877</v>
+        <v>1.7094972133636475</v>
       </c>
       <c r="G24" s="1">
-        <v>0.0015542414039373398</v>
+        <v>0.087358884513378143</v>
       </c>
       <c r="H24" s="1">
         <v>94.300521850585938</v>
       </c>
       <c r="I24" s="1">
-        <v>95.336784362792969</v>
+        <v>89.896369934082031</v>
       </c>
     </row>
     <row r="25">
@@ -8915,16 +8944,16 @@
         <v>157</v>
       </c>
       <c r="D25" s="1">
-        <v>0.12164989858865738</v>
+        <v>0.12233927845954895</v>
       </c>
       <c r="E25" s="1">
-        <v>0.11035013198852539</v>
+        <v>0.11012104153633118</v>
       </c>
       <c r="F25" s="1">
-        <v>1.1023992300033569</v>
+        <v>1.1109527349472046</v>
       </c>
       <c r="G25" s="1">
-        <v>0.2702881395816803</v>
+        <v>0.26658868789672852</v>
       </c>
       <c r="H25" s="1">
         <v>94.041450500488281</v>
@@ -8935,60 +8964,89 @@
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <v>49049</v>
+        <v>34029</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D26" s="1">
-        <v>0.11722731590270996</v>
+        <v>0.11976835876703262</v>
       </c>
       <c r="E26" s="1">
-        <v>0.016651337966322899</v>
+        <v>0.065568253397941589</v>
       </c>
       <c r="F26" s="1">
-        <v>7.0401139259338379</v>
+        <v>1.8266211748123169</v>
       </c>
       <c r="G26" s="1">
-        <v>1.9209078772064458e-12</v>
+        <v>0.06775674968957901</v>
       </c>
       <c r="H26" s="1">
         <v>93.782386779785156</v>
       </c>
       <c r="I26" s="1">
-        <v>99.481864929199219</v>
+        <v>91.19171142578125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1">
-        <v>34029</v>
+        <v>49049</v>
       </c>
       <c r="B27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D27" s="1">
-        <v>0.11670103669166565</v>
+        <v>0.11963693052530289</v>
       </c>
       <c r="E27" s="1">
-        <v>0.065596476197242737</v>
+        <v>0.016209451481699944</v>
       </c>
       <c r="F27" s="1">
-        <v>1.7790747880935669</v>
+        <v>7.3806896209716797</v>
       </c>
       <c r="G27" s="1">
-        <v>0.075227499008178711</v>
+        <v>1.574296248918472e-13</v>
       </c>
       <c r="H27" s="1">
         <v>93.5233154296875</v>
       </c>
       <c r="I27" s="1">
-        <v>90.932640075683594</v>
+        <v>99.481864929199219</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1">
+        <v>41051</v>
+      </c>
+      <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.11612220853567123</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.05665009468793869</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2.0498149394989014</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.040382493287324905</v>
+      </c>
+      <c r="H28" s="1">
+        <v>93.264251708984375</v>
+      </c>
+      <c r="I28" s="1">
+        <v>93.005180358886719</v>
       </c>
     </row>
   </sheetData>
@@ -9040,22 +9098,22 @@
         <v>167</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.8163297176361084</v>
+        <v>-0.81750279664993286</v>
       </c>
       <c r="E2" s="1">
-        <v>0.47526046633720398</v>
+        <v>0.47333124279975891</v>
       </c>
       <c r="F2" s="1">
-        <v>-1.7176469564437866</v>
+        <v>-1.7271262407302857</v>
       </c>
       <c r="G2" s="1">
-        <v>0.085861027240753174</v>
+        <v>0.084144994616508484</v>
       </c>
       <c r="H2" s="1">
         <v>0.2590673565864563</v>
       </c>
       <c r="I2" s="1">
-        <v>40.673576354980469</v>
+        <v>40.414508819580078</v>
       </c>
     </row>
     <row r="3">
@@ -9069,13 +9127,13 @@
         <v>168</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.44695848226547241</v>
+        <v>-0.44541200995445252</v>
       </c>
       <c r="E3" s="1">
-        <v>0.027410661801695824</v>
+        <v>0.027385467663407326</v>
       </c>
       <c r="F3" s="1">
-        <v>-16.306009292602539</v>
+        <v>-16.26453971862793</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -9098,22 +9156,22 @@
         <v>169</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.35822153091430664</v>
+        <v>-0.36180377006530762</v>
       </c>
       <c r="E4" s="1">
-        <v>0.072425708174705505</v>
+        <v>0.071795731782913208</v>
       </c>
       <c r="F4" s="1">
-        <v>-4.9460549354553223</v>
+        <v>-5.0393490791320801</v>
       </c>
       <c r="G4" s="1">
-        <v>7.5732594950750354e-07</v>
+        <v>4.6711781465091917e-07</v>
       </c>
       <c r="H4" s="1">
         <v>0.7772020697593689</v>
       </c>
       <c r="I4" s="1">
-        <v>10.880828857421875</v>
+        <v>10.621761322021484</v>
       </c>
     </row>
     <row r="5">
@@ -9127,22 +9185,22 @@
         <v>103</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.34792426228523254</v>
+        <v>-0.35385185480117798</v>
       </c>
       <c r="E5" s="1">
-        <v>0.13611362874507904</v>
+        <v>0.13699133694171906</v>
       </c>
       <c r="F5" s="1">
-        <v>-2.5561308860778809</v>
+        <v>-2.5830235481262207</v>
       </c>
       <c r="G5" s="1">
-        <v>0.010584330186247826</v>
+        <v>0.0097938636317849159</v>
       </c>
       <c r="H5" s="1">
         <v>1.0362694263458252</v>
       </c>
       <c r="I5" s="1">
-        <v>29.53367805480957</v>
+        <v>29.27461051940918</v>
       </c>
     </row>
     <row r="6">
@@ -9156,22 +9214,22 @@
         <v>170</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.34204638004302979</v>
+        <v>-0.34365653991699219</v>
       </c>
       <c r="E6" s="1">
-        <v>0.05055994912981987</v>
+        <v>0.050519250333309174</v>
       </c>
       <c r="F6" s="1">
-        <v>-6.765164852142334</v>
+        <v>-6.8024868965148926</v>
       </c>
       <c r="G6" s="1">
-        <v>1.3315792912749203e-11</v>
+        <v>1.02828856540782e-11</v>
       </c>
       <c r="H6" s="1">
         <v>1.2953368425369263</v>
       </c>
       <c r="I6" s="1">
-        <v>5.1813473701477051</v>
+        <v>5.4404144287109375</v>
       </c>
     </row>
     <row r="7">
@@ -9185,22 +9243,22 @@
         <v>154</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.29575809836387634</v>
+        <v>-0.29675814509391785</v>
       </c>
       <c r="E7" s="1">
-        <v>0.064674548804759979</v>
+        <v>0.064312443137168884</v>
       </c>
       <c r="F7" s="1">
-        <v>-4.573021411895752</v>
+        <v>-4.6143193244934082</v>
       </c>
       <c r="G7" s="1">
-        <v>4.8074098231154494e-06</v>
+        <v>3.943856881960528e-06</v>
       </c>
       <c r="H7" s="1">
         <v>1.5544041395187378</v>
       </c>
       <c r="I7" s="1">
-        <v>13.212434768676758</v>
+        <v>12.953368186950684</v>
       </c>
     </row>
     <row r="8">
@@ -9214,16 +9272,16 @@
         <v>171</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.27684798836708069</v>
+        <v>-0.28057774901390076</v>
       </c>
       <c r="E8" s="1">
-        <v>0.087276890873908997</v>
+        <v>0.088018849492073059</v>
       </c>
       <c r="F8" s="1">
-        <v>-3.172065258026123</v>
+        <v>-3.1877007484436035</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0015135898720473051</v>
+        <v>0.0014340886846184731</v>
       </c>
       <c r="H8" s="1">
         <v>1.8134715557098389</v>
@@ -9243,22 +9301,22 @@
         <v>172</v>
       </c>
       <c r="D9" s="1">
-        <v>-0.27461495995521546</v>
+        <v>-0.27116039395332336</v>
       </c>
       <c r="E9" s="1">
-        <v>0.058501832187175751</v>
+        <v>0.057459421455860138</v>
       </c>
       <c r="F9" s="1">
-        <v>-4.6941256523132324</v>
+        <v>-4.7191634178161621</v>
       </c>
       <c r="G9" s="1">
-        <v>2.6774941943585873e-06</v>
+        <v>2.3681652692175703e-06</v>
       </c>
       <c r="H9" s="1">
         <v>2.0725388526916504</v>
       </c>
       <c r="I9" s="1">
-        <v>12.435233116149902</v>
+        <v>12.176165580749512</v>
       </c>
     </row>
     <row r="10">
@@ -9272,22 +9330,22 @@
         <v>173</v>
       </c>
       <c r="D10" s="1">
-        <v>-0.25989165902137756</v>
+        <v>-0.26217103004455567</v>
       </c>
       <c r="E10" s="1">
-        <v>0.055590085685253143</v>
+        <v>0.055275682359933853</v>
       </c>
       <c r="F10" s="1">
-        <v>-4.6751441955566406</v>
+        <v>-4.7429723739624024</v>
       </c>
       <c r="G10" s="1">
-        <v>2.9374714358709753e-06</v>
+        <v>2.1060500330349896e-06</v>
       </c>
       <c r="H10" s="1">
         <v>2.3316061496734619</v>
       </c>
       <c r="I10" s="1">
-        <v>12.694300651550293</v>
+        <v>11.917098045349121</v>
       </c>
     </row>
     <row r="11">
@@ -9301,13 +9359,13 @@
         <v>174</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.2534659206867218</v>
+        <v>-0.25761851668357849</v>
       </c>
       <c r="E11" s="1">
-        <v>0.024758756160736084</v>
+        <v>0.024771582335233688</v>
       </c>
       <c r="F11" s="1">
-        <v>-10.237425804138184</v>
+        <v>-10.399760246276855</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -9330,13 +9388,13 @@
         <v>104</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.25040999054908752</v>
+        <v>-0.25368613004684448</v>
       </c>
       <c r="E12" s="1">
-        <v>0.022989967837929726</v>
+        <v>0.023887287825345993</v>
       </c>
       <c r="F12" s="1">
-        <v>-10.892142295837402</v>
+        <v>-10.620131492614746</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -9345,7 +9403,7 @@
         <v>2.8497409820556641</v>
       </c>
       <c r="I12" s="1">
-        <v>1.2953368425369263</v>
+        <v>1.8134715557098389</v>
       </c>
     </row>
     <row r="13">
@@ -9359,16 +9417,16 @@
         <v>175</v>
       </c>
       <c r="D13" s="1">
-        <v>-0.24834203720092774</v>
+        <v>-0.25009986758232117</v>
       </c>
       <c r="E13" s="1">
-        <v>0.068397939205169678</v>
+        <v>0.069406457245349884</v>
       </c>
       <c r="F13" s="1">
-        <v>-3.6308410167694092</v>
+        <v>-3.6034092903137207</v>
       </c>
       <c r="G13" s="1">
-        <v>0.00028249918250367046</v>
+        <v>0.00031407037749886513</v>
       </c>
       <c r="H13" s="1">
         <v>3.1088082790374756</v>
@@ -9388,13 +9446,13 @@
         <v>176</v>
       </c>
       <c r="D14" s="1">
-        <v>-0.23175500333309174</v>
+        <v>-0.23452058434486389</v>
       </c>
       <c r="E14" s="1">
-        <v>0.021354334428906441</v>
+        <v>0.021669816225767136</v>
       </c>
       <c r="F14" s="1">
-        <v>-10.852831840515137</v>
+        <v>-10.822453498840332</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -9403,36 +9461,36 @@
         <v>3.3678755760192871</v>
       </c>
       <c r="I14" s="1">
-        <v>1.5544041395187378</v>
+        <v>1.0362694263458252</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>20209</v>
+        <v>6007</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="D15" s="1">
-        <v>-0.23145805299282074</v>
+        <v>-0.22830396890640259</v>
       </c>
       <c r="E15" s="1">
-        <v>0.049050625413656235</v>
+        <v>0.076829880475997925</v>
       </c>
       <c r="F15" s="1">
-        <v>-4.7187585830688477</v>
+        <v>-2.9715518951416016</v>
       </c>
       <c r="G15" s="1">
-        <v>2.3728821361146402e-06</v>
+        <v>0.0029629878699779511</v>
       </c>
       <c r="H15" s="1">
         <v>3.6269431114196777</v>
       </c>
       <c r="I15" s="1">
-        <v>11.917098045349121</v>
+        <v>24.870466232299805</v>
       </c>
     </row>
     <row r="16">
@@ -9446,22 +9504,22 @@
         <v>178</v>
       </c>
       <c r="D16" s="1">
-        <v>-0.22999566793441773</v>
+        <v>-0.22775939106941223</v>
       </c>
       <c r="E16" s="1">
-        <v>0.048573900014162064</v>
+        <v>0.048512961715459824</v>
       </c>
       <c r="F16" s="1">
-        <v>-4.7349638938903809</v>
+        <v>-4.6948151588439942</v>
       </c>
       <c r="G16" s="1">
-        <v>2.1909409042564221e-06</v>
+        <v>2.6684790555009386e-06</v>
       </c>
       <c r="H16" s="1">
         <v>3.8860104084014893</v>
       </c>
       <c r="I16" s="1">
-        <v>11.658031463623047</v>
+        <v>12.435233116149902</v>
       </c>
     </row>
     <row r="17">
@@ -9475,16 +9533,16 @@
         <v>179</v>
       </c>
       <c r="D17" s="1">
-        <v>-0.22694425284862518</v>
+        <v>-0.22760079801082611</v>
       </c>
       <c r="E17" s="1">
-        <v>0.046341307461261749</v>
+        <v>0.045543722808361054</v>
       </c>
       <c r="F17" s="1">
-        <v>-4.8972344398498535</v>
+        <v>-4.9974131584167481</v>
       </c>
       <c r="G17" s="1">
-        <v>9.71948566075298e-07</v>
+        <v>5.8104490108235041e-07</v>
       </c>
       <c r="H17" s="1">
         <v>4.1450777053833008</v>
@@ -9495,31 +9553,31 @@
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>6007</v>
+        <v>20209</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="D18" s="1">
-        <v>-0.22461669147014618</v>
+        <v>-0.22726954519748688</v>
       </c>
       <c r="E18" s="1">
-        <v>0.076479896903038025</v>
+        <v>0.048608969897031784</v>
       </c>
       <c r="F18" s="1">
-        <v>-2.9369375705718994</v>
+        <v>-4.6754651069641113</v>
       </c>
       <c r="G18" s="1">
-        <v>0.0033147083595395088</v>
+        <v>2.9328814434848027e-06</v>
       </c>
       <c r="H18" s="1">
         <v>4.4041452407836914</v>
       </c>
       <c r="I18" s="1">
-        <v>25.129533767700195</v>
+        <v>12.694300651550293</v>
       </c>
     </row>
     <row r="19">
@@ -9533,22 +9591,22 @@
         <v>106</v>
       </c>
       <c r="D19" s="1">
-        <v>-0.22013211250305176</v>
+        <v>-0.21551015973091126</v>
       </c>
       <c r="E19" s="1">
-        <v>0.039977602660655975</v>
+        <v>0.039256781339645386</v>
       </c>
       <c r="F19" s="1">
-        <v>-5.5063858032226563</v>
+        <v>-5.4897561073303223</v>
       </c>
       <c r="G19" s="1">
-        <v>3.6627536559308282e-08</v>
+        <v>4.0248913535378961e-08</v>
       </c>
       <c r="H19" s="1">
         <v>4.6632122993469238</v>
       </c>
       <c r="I19" s="1">
-        <v>8.5492229461669922</v>
+        <v>8.8082904815673828</v>
       </c>
     </row>
     <row r="20">
@@ -9562,13 +9620,13 @@
         <v>180</v>
       </c>
       <c r="D20" s="1">
-        <v>-0.21303057670593262</v>
+        <v>-0.2155042290687561</v>
       </c>
       <c r="E20" s="1">
-        <v>0.019743118435144425</v>
+        <v>0.01996922492980957</v>
       </c>
       <c r="F20" s="1">
-        <v>-10.790118217468262</v>
+        <v>-10.791817665100098</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -9577,7 +9635,7 @@
         <v>4.9222798347473145</v>
       </c>
       <c r="I20" s="1">
-        <v>1.8134715557098389</v>
+        <v>1.2953368425369263</v>
       </c>
     </row>
     <row r="21">
@@ -9591,13 +9649,13 @@
         <v>107</v>
       </c>
       <c r="D21" s="1">
-        <v>-0.21039088070392609</v>
+        <v>-0.21287812292575836</v>
       </c>
       <c r="E21" s="1">
-        <v>0.023285310715436935</v>
+        <v>0.023424375802278519</v>
       </c>
       <c r="F21" s="1">
-        <v>-9.0353479385375977</v>
+        <v>-9.0878887176513672</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -9611,60 +9669,60 @@
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>22071</v>
+        <v>48451</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D22" s="1">
-        <v>-0.20608890056610108</v>
+        <v>-0.21031133830547333</v>
       </c>
       <c r="E22" s="1">
-        <v>0.051859930157661438</v>
+        <v>0.073736175894737244</v>
       </c>
       <c r="F22" s="1">
-        <v>-3.9739525318145752</v>
+        <v>-2.8522138595581055</v>
       </c>
       <c r="G22" s="1">
-        <v>7.0689660788048059e-05</v>
+        <v>0.0043415878899395466</v>
       </c>
       <c r="H22" s="1">
         <v>5.4404144287109375</v>
       </c>
       <c r="I22" s="1">
-        <v>16.839378356933594</v>
+        <v>26.683937072753906</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>48451</v>
+        <v>22071</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="C23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D23" s="1">
-        <v>-0.20591777563095093</v>
+        <v>-0.20934301614761353</v>
       </c>
       <c r="E23" s="1">
-        <v>0.073872722685337067</v>
+        <v>0.051747865974903107</v>
       </c>
       <c r="F23" s="1">
-        <v>-2.7874670028686524</v>
+        <v>-4.0454425811767578</v>
       </c>
       <c r="G23" s="1">
-        <v>0.0053121862001717091</v>
+        <v>5.2224364480935037e-05</v>
       </c>
       <c r="H23" s="1">
         <v>5.6994819641113281</v>
       </c>
       <c r="I23" s="1">
-        <v>26.683937072753906</v>
+        <v>16.580310821533203</v>
       </c>
     </row>
     <row r="24">
@@ -9678,22 +9736,22 @@
         <v>183</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.20578275620937347</v>
+        <v>-0.20459224283695221</v>
       </c>
       <c r="E24" s="1">
-        <v>0.040864229202270508</v>
+        <v>0.040729232132434845</v>
       </c>
       <c r="F24" s="1">
-        <v>-5.0357675552368164</v>
+        <v>-5.023228645324707</v>
       </c>
       <c r="G24" s="1">
-        <v>4.7593783847332816e-07</v>
+        <v>5.0809995855161105e-07</v>
       </c>
       <c r="H24" s="1">
         <v>5.9585490226745605</v>
       </c>
       <c r="I24" s="1">
-        <v>10.621761322021484</v>
+        <v>10.880828857421875</v>
       </c>
     </row>
     <row r="25">
@@ -9707,22 +9765,22 @@
         <v>184</v>
       </c>
       <c r="D25" s="1">
-        <v>-0.19899110496044159</v>
+        <v>-0.20027035474777222</v>
       </c>
       <c r="E25" s="1">
-        <v>0.084818147122859955</v>
+        <v>0.084915123879909515</v>
       </c>
       <c r="F25" s="1">
-        <v>-2.3460912704467773</v>
+        <v>-2.3584768772125244</v>
       </c>
       <c r="G25" s="1">
-        <v>0.018971461802721024</v>
+        <v>0.018350103870034218</v>
       </c>
       <c r="H25" s="1">
         <v>6.2176165580749512</v>
       </c>
       <c r="I25" s="1">
-        <v>32.124351501464844</v>
+        <v>32.642486572265625</v>
       </c>
     </row>
     <row r="26">
@@ -9736,16 +9794,16 @@
         <v>150</v>
       </c>
       <c r="D26" s="1">
-        <v>-0.19796308875083923</v>
+        <v>-0.19912084937095642</v>
       </c>
       <c r="E26" s="1">
-        <v>0.025834331288933754</v>
+        <v>0.025681247934699059</v>
       </c>
       <c r="F26" s="1">
-        <v>-7.6627912521362305</v>
+        <v>-7.7535505294799805</v>
       </c>
       <c r="G26" s="1">
-        <v>1.8207657603852567e-14</v>
+        <v>8.8817841970012523e-15</v>
       </c>
       <c r="H26" s="1">
         <v>6.4766840934753418</v>
@@ -9832,13 +9890,13 @@
         <v>168</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.44695848226547241</v>
+        <v>-0.44541200995445252</v>
       </c>
       <c r="E2" s="1">
-        <v>0.027410661801695824</v>
+        <v>0.027385467663407326</v>
       </c>
       <c r="F2" s="1">
-        <v>-16.306009292602539</v>
+        <v>-16.26453971862793</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -9861,19 +9919,19 @@
         <v>195</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.17084202170372009</v>
+        <v>-0.1710662841796875</v>
       </c>
       <c r="E3" s="1">
-        <v>0.01160604041069746</v>
+        <v>0.011608581058681011</v>
       </c>
       <c r="F3" s="1">
-        <v>-14.720095634460449</v>
+        <v>-14.73619270324707</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>9.067357063293457</v>
+        <v>8.5492229461669922</v>
       </c>
       <c r="I3" s="1">
         <v>0.5181347131729126</v>
@@ -9890,13 +9948,13 @@
         <v>196</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.18908895552158356</v>
+        <v>-0.18782040476799011</v>
       </c>
       <c r="E4" s="1">
-        <v>0.014627714641392231</v>
+        <v>0.014421283267438412</v>
       </c>
       <c r="F4" s="1">
-        <v>-12.926759719848633</v>
+        <v>-13.023834228515625</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -9910,28 +9968,28 @@
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>26093</v>
+        <v>22005</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="C5" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.17816247045993805</v>
+        <v>-0.23452058434486389</v>
       </c>
       <c r="E5" s="1">
-        <v>0.015953456982970238</v>
+        <v>0.021669816225767136</v>
       </c>
       <c r="F5" s="1">
-        <v>-11.167640686035156</v>
+        <v>-10.822453498840332</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>7.2538862228393555</v>
+        <v>3.3678755760192871</v>
       </c>
       <c r="I5" s="1">
         <v>1.0362694263458252</v>
@@ -9939,28 +9997,28 @@
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>39103</v>
+        <v>21015</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.25040999054908752</v>
+        <v>-0.2155042290687561</v>
       </c>
       <c r="E6" s="1">
-        <v>0.022989967837929726</v>
+        <v>0.01996922492980957</v>
       </c>
       <c r="F6" s="1">
-        <v>-10.892142295837402</v>
+        <v>-10.791817665100098</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>2.8497409820556641</v>
+        <v>4.9222798347473145</v>
       </c>
       <c r="I6" s="1">
         <v>1.2953368425369263</v>
@@ -9968,28 +10026,28 @@
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>22005</v>
+        <v>26093</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.23175500333309174</v>
+        <v>-0.1808193027973175</v>
       </c>
       <c r="E7" s="1">
-        <v>0.021354334428906441</v>
+        <v>0.01697511225938797</v>
       </c>
       <c r="F7" s="1">
-        <v>-10.852831840515137</v>
+        <v>-10.652024269104004</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>3.3678755760192871</v>
+        <v>7.2538862228393555</v>
       </c>
       <c r="I7" s="1">
         <v>1.5544041395187378</v>
@@ -9997,28 +10055,28 @@
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>21015</v>
+        <v>39103</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.21303057670593262</v>
+        <v>-0.25368613004684448</v>
       </c>
       <c r="E8" s="1">
-        <v>0.019743118435144425</v>
+        <v>0.023887287825345993</v>
       </c>
       <c r="F8" s="1">
-        <v>-10.790118217468262</v>
+        <v>-10.620131492614746</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>4.9222798347473145</v>
+        <v>2.8497409820556641</v>
       </c>
       <c r="I8" s="1">
         <v>1.8134715557098389</v>
@@ -10035,13 +10093,13 @@
         <v>174</v>
       </c>
       <c r="D9" s="1">
-        <v>-0.2534659206867218</v>
+        <v>-0.25761851668357849</v>
       </c>
       <c r="E9" s="1">
-        <v>0.024758756160736084</v>
+        <v>0.024771582335233688</v>
       </c>
       <c r="F9" s="1">
-        <v>-10.237425804138184</v>
+        <v>-10.399760246276855</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -10055,28 +10113,28 @@
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>27123</v>
+        <v>18141</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D10" s="1">
-        <v>-0.17004609107971191</v>
+        <v>-0.16719815135002136</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01754547655582428</v>
+        <v>0.017249185591936112</v>
       </c>
       <c r="F10" s="1">
-        <v>-9.6917343139648438</v>
+        <v>-9.6931037902832031</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>9.3264245986938477</v>
+        <v>10.36269474029541</v>
       </c>
       <c r="I10" s="1">
         <v>2.3316061496734619</v>
@@ -10084,28 +10142,28 @@
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>18141</v>
+        <v>27123</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.16557271778583527</v>
+        <v>-0.16742275655269623</v>
       </c>
       <c r="E11" s="1">
-        <v>0.017260193824768067</v>
+        <v>0.01764318160712719</v>
       </c>
       <c r="F11" s="1">
-        <v>-9.5927495956420899</v>
+        <v>-9.4893741607666016</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>10.36269474029541</v>
+        <v>9.8445596694946289</v>
       </c>
       <c r="I11" s="1">
         <v>2.5906736850738525</v>
@@ -10122,19 +10180,19 @@
         <v>200</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.1306353360414505</v>
+        <v>-0.13481755554676056</v>
       </c>
       <c r="E12" s="1">
-        <v>0.013835715129971504</v>
+        <v>0.014302395284175873</v>
       </c>
       <c r="F12" s="1">
-        <v>-9.4418926239013672</v>
+        <v>-9.4262218475341797</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>17.616580963134766</v>
+        <v>17.357513427734375</v>
       </c>
       <c r="I12" s="1">
         <v>2.8497409820556641</v>
@@ -10151,13 +10209,13 @@
         <v>107</v>
       </c>
       <c r="D13" s="1">
-        <v>-0.21039088070392609</v>
+        <v>-0.21287812292575836</v>
       </c>
       <c r="E13" s="1">
-        <v>0.023285310715436935</v>
+        <v>0.023424375802278519</v>
       </c>
       <c r="F13" s="1">
-        <v>-9.0353479385375977</v>
+        <v>-9.0878887176513672</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -10180,19 +10238,19 @@
         <v>201</v>
       </c>
       <c r="D14" s="1">
-        <v>-0.17492793500423431</v>
+        <v>-0.17449924349784851</v>
       </c>
       <c r="E14" s="1">
-        <v>0.02003706619143486</v>
+        <v>0.020729873329401016</v>
       </c>
       <c r="F14" s="1">
-        <v>-8.7302169799804688</v>
+        <v>-8.4177665710449219</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>8.5492229461669922</v>
+        <v>7.7720208168029785</v>
       </c>
       <c r="I14" s="1">
         <v>3.3678755760192871</v>
@@ -31810,34 +31868,34 @@
         <v>150</v>
       </c>
       <c r="D2" s="1">
-        <v>0.15443232655525208</v>
+        <v>0.15584227442741394</v>
       </c>
       <c r="E2" s="1">
-        <v>0.04555978998541832</v>
+        <v>0.045350413769483566</v>
       </c>
       <c r="F2" s="1">
-        <v>3.3896627426147461</v>
+        <v>3.4364025592803955</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00069978658575564623</v>
+        <v>0.00058949436061084271</v>
       </c>
       <c r="H2" s="1">
         <v>95.85491943359375</v>
       </c>
       <c r="I2" s="1">
-        <v>96.113990783691406</v>
+        <v>96.373054504394531</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.19796308875083923</v>
+        <v>-0.19912084937095642</v>
       </c>
       <c r="K2" s="1">
-        <v>0.025834331288933754</v>
+        <v>0.025681247934699059</v>
       </c>
       <c r="L2" s="1">
-        <v>-7.6627912521362305</v>
+        <v>-7.7535505294799805</v>
       </c>
       <c r="M2" s="1">
-        <v>1.8207657603852567e-14</v>
+        <v>8.8817841970012523e-15</v>
       </c>
       <c r="N2" s="1">
         <v>6.4766840934753418</v>
@@ -31857,40 +31915,40 @@
         <v>154</v>
       </c>
       <c r="D3" s="1">
-        <v>0.12784139811992645</v>
+        <v>0.12942652404308319</v>
       </c>
       <c r="E3" s="1">
-        <v>0.055736925452947617</v>
+        <v>0.055388569831848145</v>
       </c>
       <c r="F3" s="1">
-        <v>2.2936570644378662</v>
+        <v>2.3367009162902832</v>
       </c>
       <c r="G3" s="1">
-        <v>0.021810205653309822</v>
+        <v>0.019454739987850189</v>
       </c>
       <c r="H3" s="1">
-        <v>94.818649291992188</v>
+        <v>95.077720642089844</v>
       </c>
       <c r="I3" s="1">
         <v>94.041450500488281</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.29575809836387634</v>
+        <v>-0.29675814509391785</v>
       </c>
       <c r="K3" s="1">
-        <v>0.064674548804759979</v>
+        <v>0.064312443137168884</v>
       </c>
       <c r="L3" s="1">
-        <v>-4.573021411895752</v>
+        <v>-4.6143193244934082</v>
       </c>
       <c r="M3" s="1">
-        <v>4.8074098231154494e-06</v>
+        <v>3.943856881960528e-06</v>
       </c>
       <c r="N3" s="1">
         <v>1.5544041395187378</v>
       </c>
       <c r="O3" s="1">
-        <v>13.212434768676758</v>
+        <v>12.953368186950684</v>
       </c>
     </row>
   </sheetData>
